--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -51,7 +51,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:AJ302"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -274,7 +274,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C1</t>
+          <t>01_Power_Entry/C101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="0">
@@ -284,7 +284,7 @@
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C101</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="0">
@@ -456,7 +456,7 @@
     <row r="3">
       <c r="A3" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C2</t>
+          <t>01_Power_Entry/C102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="0">
@@ -466,7 +466,7 @@
       </c>
       <c r="C3" t="inlineStr" s="0">
         <is>
-          <t>C2</t>
+          <t>C102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="0">
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C3</t>
+          <t>01_Power_Entry/C103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
@@ -648,7 +648,7 @@
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t>C3</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="0">
@@ -820,7 +820,7 @@
     <row r="5">
       <c r="A5" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C4</t>
+          <t>01_Power_Entry/C104</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="0">
@@ -830,7 +830,7 @@
       </c>
       <c r="C5" t="inlineStr" s="0">
         <is>
-          <t>C4</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="0">
@@ -1002,7 +1002,7 @@
     <row r="6">
       <c r="A6" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C5</t>
+          <t>01_Power_Entry/C105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="0">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t>C5</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="0">
@@ -1184,7 +1184,7 @@
     <row r="7">
       <c r="A7" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C6</t>
+          <t>01_Power_Entry/C106</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="0">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C7" t="inlineStr" s="0">
         <is>
-          <t>C6</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="0">
@@ -1366,7 +1366,7 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C7</t>
+          <t>01_Power_Entry/C107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C8" t="inlineStr" s="0">
         <is>
-          <t>C7</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="0">
@@ -1548,7 +1548,7 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C8</t>
+          <t>01_Power_Entry/C108</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C9" t="inlineStr" s="0">
         <is>
-          <t>C8</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="0">
@@ -1730,7 +1730,7 @@
     <row r="10">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/C9</t>
+          <t>01_Power_Entry/C109</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t>C9</t>
+          <t>C109</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="0">
@@ -1912,7 +1912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/D1</t>
+          <t>01_Power_Entry/D101</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr" s="0">
         <is>
-          <t>D1</t>
+          <t>D101</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="0">
@@ -2094,7 +2094,7 @@
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/D2</t>
+          <t>01_Power_Entry/D102</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C12" t="inlineStr" s="0">
         <is>
-          <t>D2</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="0">
@@ -2276,7 +2276,7 @@
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/D3</t>
+          <t>01_Power_Entry/D103</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C13" t="inlineStr" s="0">
         <is>
-          <t>D3</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="0">
@@ -2458,7 +2458,7 @@
     <row r="14">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/D4</t>
+          <t>01_Power_Entry/D104</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C14" t="inlineStr" s="0">
         <is>
-          <t>D4</t>
+          <t>D104</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="0">
@@ -2640,7 +2640,7 @@
     <row r="15">
       <c r="A15" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/F1</t>
+          <t>01_Power_Entry/F101</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="0">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C15" t="inlineStr" s="0">
         <is>
-          <t>F1</t>
+          <t>F101</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="0">
@@ -2822,7 +2822,7 @@
     <row r="16">
       <c r="A16" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/L1</t>
+          <t>01_Power_Entry/L101</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="0">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C16" t="inlineStr" s="0">
         <is>
-          <t>L1</t>
+          <t>L101</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="0">
@@ -3004,7 +3004,7 @@
     <row r="17">
       <c r="A17" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/Q1</t>
+          <t>01_Power_Entry/Q101</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="0">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C17" t="inlineStr" s="0">
         <is>
-          <t>Q1</t>
+          <t>Q101</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="0">
@@ -3186,7 +3186,7 @@
     <row r="18">
       <c r="A18" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/Q2</t>
+          <t>01_Power_Entry/Q102</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="0">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C18" t="inlineStr" s="0">
         <is>
-          <t>Q2</t>
+          <t>Q102</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="0">
@@ -3368,7 +3368,7 @@
     <row r="19">
       <c r="A19" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R1</t>
+          <t>01_Power_Entry/R101</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="0">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C19" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R101</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="0">
@@ -3550,7 +3550,7 @@
     <row r="20">
       <c r="A20" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R10</t>
+          <t>01_Power_Entry/R102</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="0">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C20" t="inlineStr" s="0">
         <is>
-          <t>R10</t>
+          <t>R102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="0">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="E20" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="0">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="J20" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr" s="0">
@@ -3732,7 +3732,7 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R11</t>
+          <t>01_Power_Entry/R103</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="0">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="C21" t="inlineStr" s="0">
         <is>
-          <t>R11</t>
+          <t>R103</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="0">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="E21" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>1.91 MΩ 1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="0">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="J21" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>1.91 MΩ 1%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>1.91 MΩ 1%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="0">
@@ -3914,7 +3914,7 @@
     <row r="22">
       <c r="A22" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R12</t>
+          <t>01_Power_Entry/R104</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="0">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C22" t="inlineStr" s="0">
         <is>
-          <t>R12</t>
+          <t>R104</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="0">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="E22" t="inlineStr" s="0">
         <is>
-          <t>402 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="0">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="J22" t="inlineStr" s="0">
         <is>
-          <t>402 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="0">
         <is>
-          <t>402 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="0">
@@ -4096,7 +4096,7 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R13</t>
+          <t>01_Power_Entry/R105</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="0">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C23" t="inlineStr" s="0">
         <is>
-          <t>R13</t>
+          <t>R105</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="0">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E23" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="0">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="J23" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="K23" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="0">
@@ -4278,7 +4278,7 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R14</t>
+          <t>01_Power_Entry/R106</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="0">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C24" t="inlineStr" s="0">
         <is>
-          <t>R14</t>
+          <t>R106</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="0">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="E24" t="inlineStr" s="0">
         <is>
-          <t>6.65 kΩ 1%</t>
+          <t>9.09 kΩ 1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="0">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="J24" t="inlineStr" s="0">
         <is>
-          <t>6.65 kΩ 1%</t>
+          <t>9.09 kΩ 1%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="0">
         <is>
-          <t>6.65 kΩ 1%</t>
+          <t>9.09 kΩ 1%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="0">
@@ -4460,7 +4460,7 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R15</t>
+          <t>01_Power_Entry/R107</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="0">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C25" t="inlineStr" s="0">
         <is>
-          <t>R15</t>
+          <t>R107</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="0">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E25" t="inlineStr" s="0">
         <is>
-          <t>604 kΩ 1%</t>
+          <t>49.9 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="0">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="J25" t="inlineStr" s="0">
         <is>
-          <t>604 kΩ 1%</t>
+          <t>49.9 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="0">
         <is>
-          <t>604 kΩ 1%</t>
+          <t>49.9 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="0">
@@ -4642,7 +4642,7 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R16</t>
+          <t>01_Power_Entry/R108</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="0">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C26" t="inlineStr" s="0">
         <is>
-          <t>R16</t>
+          <t>R108</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="0">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="E26" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>49.9 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="0">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="J26" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>49.9 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>49.9 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="0">
@@ -4824,7 +4824,7 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R2</t>
+          <t>01_Power_Entry/R109</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="0">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C27" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R109</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="0">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="E27" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>10.0 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="0">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="J27" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>10.0 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>10.0 kΩ 0.1% 25 ppm</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="0">
@@ -5006,7 +5006,7 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R3</t>
+          <t>01_Power_Entry/R110</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="0">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C28" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R110</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="0">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="E28" t="inlineStr" s="0">
         <is>
-          <t>1.91 MΩ 1%</t>
+          <t>1.00 kΩ 1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="0">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="J28" t="inlineStr" s="0">
         <is>
-          <t>1.91 MΩ 1%</t>
+          <t>1.00 kΩ 1%</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="0">
         <is>
-          <t>1.91 MΩ 1%</t>
+          <t>1.00 kΩ 1%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="0">
@@ -5188,7 +5188,7 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R4</t>
+          <t>01_Power_Entry/R111</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="0">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C29" t="inlineStr" s="0">
         <is>
-          <t>R4</t>
+          <t>R111</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="0">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="E29" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="0">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="J29" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 1%</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="0">
@@ -5370,7 +5370,7 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R5</t>
+          <t>01_Power_Entry/R112</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="0">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="C30" t="inlineStr" s="0">
         <is>
-          <t>R5</t>
+          <t>R112</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="0">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="E30" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>402 kΩ 1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="0">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="J30" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>402 kΩ 1%</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>402 kΩ 1%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="0">
@@ -5552,7 +5552,7 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R6</t>
+          <t>01_Power_Entry/R113</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="0">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C31" t="inlineStr" s="0">
         <is>
-          <t>R6</t>
+          <t>R113</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="0">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="E31" t="inlineStr" s="0">
         <is>
-          <t>9.09 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="0">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="J31" t="inlineStr" s="0">
         <is>
-          <t>9.09 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="0">
         <is>
-          <t>9.09 kΩ 1%</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="0">
@@ -5734,7 +5734,7 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R7</t>
+          <t>01_Power_Entry/R114</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="0">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C32" t="inlineStr" s="0">
         <is>
-          <t>R7</t>
+          <t>R114</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="0">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="E32" t="inlineStr" s="0">
         <is>
-          <t>49.9 kΩ 0.1% 25 ppm</t>
+          <t>6.65 kΩ 1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="0">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="J32" t="inlineStr" s="0">
         <is>
-          <t>49.9 kΩ 0.1% 25 ppm</t>
+          <t>6.65 kΩ 1%</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="0">
         <is>
-          <t>49.9 kΩ 0.1% 25 ppm</t>
+          <t>6.65 kΩ 1%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="0">
@@ -5916,7 +5916,7 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R8</t>
+          <t>01_Power_Entry/R115</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="0">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C33" t="inlineStr" s="0">
         <is>
-          <t>R8</t>
+          <t>R115</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="0">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E33" t="inlineStr" s="0">
         <is>
-          <t>49.9 kΩ 0.1% 25 ppm</t>
+          <t>604 kΩ 1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="0">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="J33" t="inlineStr" s="0">
         <is>
-          <t>49.9 kΩ 0.1% 25 ppm</t>
+          <t>604 kΩ 1%</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="0">
         <is>
-          <t>49.9 kΩ 0.1% 25 ppm</t>
+          <t>604 kΩ 1%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="0">
@@ -6098,7 +6098,7 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/R9</t>
+          <t>01_Power_Entry/R116</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="0">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C34" t="inlineStr" s="0">
         <is>
-          <t>R9</t>
+          <t>R116</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="0">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="E34" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ 0.1% 25 ppm</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="0">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="J34" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ 0.1% 25 ppm</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ 0.1% 25 ppm</t>
+          <t>100 kΩ 1%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="0">
@@ -6280,7 +6280,7 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/U1</t>
+          <t>01_Power_Entry/U101</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="0">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C35" t="inlineStr" s="0">
         <is>
-          <t>U1</t>
+          <t>U101</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="0">
@@ -6462,7 +6462,7 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="0">
         <is>
-          <t>01_Power_Entry/U2</t>
+          <t>01_Power_Entry/U102</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="0">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C36" t="inlineStr" s="0">
         <is>
-          <t>U2</t>
+          <t>U102</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="0">
@@ -6644,7 +6644,7 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C1</t>
+          <t>02_Power_Conversion/C201</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="0">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="C37" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C201</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="0">
@@ -6826,7 +6826,7 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C10</t>
+          <t>02_Power_Conversion/C202</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="0">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="C38" t="inlineStr" s="0">
         <is>
-          <t>C10</t>
+          <t>C202</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="0">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="E38" t="inlineStr" s="0">
         <is>
-          <t>10 nF soft start</t>
+          <t>100 nF bootstrap</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="0">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="J38" t="inlineStr" s="0">
         <is>
-          <t>10 nF soft start</t>
+          <t>100 nF bootstrap</t>
         </is>
       </c>
       <c r="K38" t="inlineStr" s="0">
         <is>
-          <t>10 nF soft start</t>
+          <t>100 nF bootstrap</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="0">
@@ -7008,7 +7008,7 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C11</t>
+          <t>02_Power_Conversion/C203</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="0">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="C39" t="inlineStr" s="0">
         <is>
-          <t>C11</t>
+          <t>C203</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="0">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="E39" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="0">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="J39" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="0">
@@ -7190,7 +7190,7 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C12</t>
+          <t>02_Power_Conversion/C204</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="0">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C40" t="inlineStr" s="0">
         <is>
-          <t>C12</t>
+          <t>C204</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="0">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="E40" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="0">
@@ -7235,12 +7235,12 @@
       </c>
       <c r="J40" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="0">
@@ -7372,7 +7372,7 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C13</t>
+          <t>02_Power_Conversion/C205</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="0">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="C41" t="inlineStr" s="0">
         <is>
-          <t>C13</t>
+          <t>C205</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="0">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="E41" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>100 nF soft start</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="0">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="J41" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>100 nF soft start</t>
         </is>
       </c>
       <c r="K41" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>100 nF soft start</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="0">
@@ -7554,7 +7554,7 @@
     <row r="42">
       <c r="A42" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C14</t>
+          <t>02_Power_Conversion/C206</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="0">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="C42" t="inlineStr" s="0">
         <is>
-          <t>C14</t>
+          <t>C206</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="0">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="E42" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>47 µF 10 V mux hold-up</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="0">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="J42" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>47 µF 10 V mux hold-up</t>
         </is>
       </c>
       <c r="K42" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>47 µF 10 V mux hold-up</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="0">
@@ -7736,7 +7736,7 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C15</t>
+          <t>02_Power_Conversion/C207</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="0">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="C43" t="inlineStr" s="0">
         <is>
-          <t>C15</t>
+          <t>C207</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="0">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="E43" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>10 µF 10 V</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="0">
@@ -7781,12 +7781,12 @@
       </c>
       <c r="J43" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>10 µF 10 V</t>
         </is>
       </c>
       <c r="K43" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>10 µF 10 V</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="0">
@@ -7918,7 +7918,7 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C16</t>
+          <t>02_Power_Conversion/C208</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="0">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C44" t="inlineStr" s="0">
         <is>
-          <t>C16</t>
+          <t>C208</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="0">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="E44" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="0">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="J44" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="K44" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="0">
@@ -8100,7 +8100,7 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C17</t>
+          <t>02_Power_Conversion/C209</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="0">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="C45" t="inlineStr" s="0">
         <is>
-          <t>C17</t>
+          <t>C209</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="0">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="E45" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="0">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="J45" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="K45" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>22 µF 10 V</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="0">
@@ -8282,7 +8282,7 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C18</t>
+          <t>02_Power_Conversion/C210</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="0">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C46" t="inlineStr" s="0">
         <is>
-          <t>C18</t>
+          <t>C210</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="0">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="E46" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>10 nF soft start</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="0">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="J46" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>10 nF soft start</t>
         </is>
       </c>
       <c r="K46" t="inlineStr" s="0">
         <is>
-          <t>1 nF slew control</t>
+          <t>10 nF soft start</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="0">
@@ -8464,7 +8464,7 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C19</t>
+          <t>02_Power_Conversion/C211</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="0">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C47" t="inlineStr" s="0">
         <is>
-          <t>C19</t>
+          <t>C211</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="0">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="E47" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="0">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="J47" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="K47" t="inlineStr" s="0">
         <is>
-          <t>4.7 µF branch local</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="0">
@@ -8646,7 +8646,7 @@
     <row r="48">
       <c r="A48" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C2</t>
+          <t>02_Power_Conversion/C212</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="0">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="C48" t="inlineStr" s="0">
         <is>
-          <t>C2</t>
+          <t>C212</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="0">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="E48" t="inlineStr" s="0">
         <is>
-          <t>100 nF bootstrap</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="0">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="J48" t="inlineStr" s="0">
         <is>
-          <t>100 nF bootstrap</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="K48" t="inlineStr" s="0">
         <is>
-          <t>100 nF bootstrap</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="L48" t="inlineStr" s="0">
@@ -8828,7 +8828,7 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C20</t>
+          <t>02_Power_Conversion/C213</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="0">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="C49" t="inlineStr" s="0">
         <is>
-          <t>C20</t>
+          <t>C213</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="0">
@@ -9010,7 +9010,7 @@
     <row r="50">
       <c r="A50" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C21</t>
+          <t>02_Power_Conversion/C214</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="0">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="C50" t="inlineStr" s="0">
         <is>
-          <t>C21</t>
+          <t>C214</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="0">
@@ -9192,7 +9192,7 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C3</t>
+          <t>02_Power_Conversion/C215</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="0">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="C51" t="inlineStr" s="0">
         <is>
-          <t>C3</t>
+          <t>C215</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="0">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="E51" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="0">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="J51" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="K51" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="L51" t="inlineStr" s="0">
@@ -9374,7 +9374,7 @@
     <row r="52">
       <c r="A52" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C4</t>
+          <t>02_Power_Conversion/C216</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="0">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C52" t="inlineStr" s="0">
         <is>
-          <t>C4</t>
+          <t>C216</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="0">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="E52" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="0">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="J52" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="K52" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="0">
@@ -9556,7 +9556,7 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C5</t>
+          <t>02_Power_Conversion/C217</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="0">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="C53" t="inlineStr" s="0">
         <is>
-          <t>C5</t>
+          <t>C217</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="0">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="E53" t="inlineStr" s="0">
         <is>
-          <t>100 nF soft start</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="0">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="J53" t="inlineStr" s="0">
         <is>
-          <t>100 nF soft start</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="K53" t="inlineStr" s="0">
         <is>
-          <t>100 nF soft start</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="0">
@@ -9738,7 +9738,7 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C6</t>
+          <t>02_Power_Conversion/C218</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="0">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="C54" t="inlineStr" s="0">
         <is>
-          <t>C6</t>
+          <t>C218</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="0">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="E54" t="inlineStr" s="0">
         <is>
-          <t>47 µF 10 V mux hold-up</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="0">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="J54" t="inlineStr" s="0">
         <is>
-          <t>47 µF 10 V mux hold-up</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="K54" t="inlineStr" s="0">
         <is>
-          <t>47 µF 10 V mux hold-up</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="0">
@@ -9920,7 +9920,7 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C7</t>
+          <t>02_Power_Conversion/C219</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="0">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="C55" t="inlineStr" s="0">
         <is>
-          <t>C7</t>
+          <t>C219</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="0">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="E55" t="inlineStr" s="0">
         <is>
-          <t>10 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="0">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="J55" t="inlineStr" s="0">
         <is>
-          <t>10 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="K55" t="inlineStr" s="0">
         <is>
-          <t>10 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="0">
@@ -10102,7 +10102,7 @@
     <row r="56">
       <c r="A56" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C8</t>
+          <t>02_Power_Conversion/C220</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="0">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="C56" t="inlineStr" s="0">
         <is>
-          <t>C8</t>
+          <t>C220</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="0">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="E56" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="0">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="J56" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="K56" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>1 nF slew control</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="0">
@@ -10284,7 +10284,7 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/C9</t>
+          <t>02_Power_Conversion/C221</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="0">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C57" t="inlineStr" s="0">
         <is>
-          <t>C9</t>
+          <t>C221</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="0">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="E57" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="0">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="J57" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="K57" t="inlineStr" s="0">
         <is>
-          <t>22 µF 10 V</t>
+          <t>4.7 µF branch local</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="0">
@@ -10466,7 +10466,7 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D1</t>
+          <t>02_Power_Conversion/D201</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="0">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="C58" t="inlineStr" s="0">
         <is>
-          <t>D1</t>
+          <t>D201</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="0">
@@ -10648,7 +10648,7 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D10</t>
+          <t>02_Power_Conversion/D202</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="0">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="C59" t="inlineStr" s="0">
         <is>
-          <t>D10</t>
+          <t>D202</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="0">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E59" t="inlineStr" s="0">
         <is>
-          <t>Schottky reverse-injection block (TBD exact)</t>
+          <t>3.3 V bias clamp</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="0">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="J59" t="inlineStr" s="0">
         <is>
-          <t>Schottky reverse-injection block (TBD exact)</t>
+          <t>3.3 V bias clamp</t>
         </is>
       </c>
       <c r="K59" t="inlineStr" s="0">
         <is>
-          <t>Schottky reverse-injection block (TBD exact)</t>
+          <t>3.3 V bias clamp</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="0">
@@ -10830,7 +10830,7 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D2</t>
+          <t>02_Power_Conversion/D203</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="0">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="C60" t="inlineStr" s="0">
         <is>
-          <t>D2</t>
+          <t>D203</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="0">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="E60" t="inlineStr" s="0">
         <is>
-          <t>3.3 V bias clamp</t>
+          <t>Schottky reverse-injection block (TBD exact)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="0">
@@ -10875,12 +10875,12 @@
       </c>
       <c r="J60" t="inlineStr" s="0">
         <is>
-          <t>3.3 V bias clamp</t>
+          <t>Schottky reverse-injection block (TBD exact)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr" s="0">
         <is>
-          <t>3.3 V bias clamp</t>
+          <t>Schottky reverse-injection block (TBD exact)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="0">
@@ -11012,7 +11012,7 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D3</t>
+          <t>02_Power_Conversion/D204</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="0">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="C61" t="inlineStr" s="0">
         <is>
-          <t>D3</t>
+          <t>D204</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="0">
@@ -11194,7 +11194,7 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D4</t>
+          <t>02_Power_Conversion/D205</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="0">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="C62" t="inlineStr" s="0">
         <is>
-          <t>D4</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="0">
@@ -11376,7 +11376,7 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D5</t>
+          <t>02_Power_Conversion/D206</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="0">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="C63" t="inlineStr" s="0">
         <is>
-          <t>D5</t>
+          <t>D206</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="0">
@@ -11558,7 +11558,7 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D6</t>
+          <t>02_Power_Conversion/D207</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="0">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="C64" t="inlineStr" s="0">
         <is>
-          <t>D6</t>
+          <t>D207</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="0">
@@ -11740,7 +11740,7 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D7</t>
+          <t>02_Power_Conversion/D208</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="0">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="C65" t="inlineStr" s="0">
         <is>
-          <t>D7</t>
+          <t>D208</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="0">
@@ -11922,7 +11922,7 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D8</t>
+          <t>02_Power_Conversion/D209</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="0">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="C66" t="inlineStr" s="0">
         <is>
-          <t>D8</t>
+          <t>D209</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="0">
@@ -12104,7 +12104,7 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/D9</t>
+          <t>02_Power_Conversion/D210</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="0">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C67" t="inlineStr" s="0">
         <is>
-          <t>D9</t>
+          <t>D210</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="0">
@@ -12286,7 +12286,7 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/L1</t>
+          <t>02_Power_Conversion/L201</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="0">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="C68" t="inlineStr" s="0">
         <is>
-          <t>L1</t>
+          <t>L201</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="0">
@@ -12468,7 +12468,7 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/L2</t>
+          <t>02_Power_Conversion/L202</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="0">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="C69" t="inlineStr" s="0">
         <is>
-          <t>L2</t>
+          <t>L202</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="0">
@@ -12650,7 +12650,7 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R1</t>
+          <t>02_Power_Conversion/R201</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="0">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="C70" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R201</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="0">
@@ -12832,7 +12832,7 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R10</t>
+          <t>02_Power_Conversion/R202</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="0">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="C71" t="inlineStr" s="0">
         <is>
-          <t>R10</t>
+          <t>R202</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="0">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="E71" t="inlineStr" s="0">
         <is>
-          <t>316 kΩ 0.1%</t>
+          <t>100 kΩ 0.1%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="0">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="J71" t="inlineStr" s="0">
         <is>
-          <t>316 kΩ 0.1%</t>
+          <t>100 kΩ 0.1%</t>
         </is>
       </c>
       <c r="K71" t="inlineStr" s="0">
         <is>
-          <t>316 kΩ 0.1%</t>
+          <t>100 kΩ 0.1%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="0">
@@ -13014,7 +13014,7 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R11</t>
+          <t>02_Power_Conversion/R203</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="0">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="C72" t="inlineStr" s="0">
         <is>
-          <t>R11</t>
+          <t>R203</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="0">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="E72" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 0.1%</t>
+          <t>24.9 kΩ 0.1%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="0">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="J72" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 0.1%</t>
+          <t>24.9 kΩ 0.1%</t>
         </is>
       </c>
       <c r="K72" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 0.1%</t>
+          <t>24.9 kΩ 0.1%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="0">
@@ -13196,7 +13196,7 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R12</t>
+          <t>02_Power_Conversion/R204</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="0">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="C73" t="inlineStr" s="0">
         <is>
-          <t>R12</t>
+          <t>R204</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="0">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E73" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ enable</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="0">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="J73" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ enable</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="K73" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ enable</t>
+          <t>100 kΩ</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="0">
@@ -13378,7 +13378,7 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R13</t>
+          <t>02_Power_Conversion/R205</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="0">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C74" t="inlineStr" s="0">
         <is>
-          <t>R13</t>
+          <t>R205</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="0">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="E74" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ PGOOD pull-up</t>
+          <t>10.2 kΩ 1%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="0">
@@ -13423,12 +13423,12 @@
       </c>
       <c r="J74" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ PGOOD pull-up</t>
+          <t>10.2 kΩ 1%</t>
         </is>
       </c>
       <c r="K74" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ PGOOD pull-up</t>
+          <t>10.2 kΩ 1%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr" s="0">
@@ -13560,7 +13560,7 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R14</t>
+          <t>02_Power_Conversion/R206</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="0">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="C75" t="inlineStr" s="0">
         <is>
-          <t>R14</t>
+          <t>R206</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="0">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="E75" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="0">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="J75" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="K75" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr" s="0">
@@ -13742,7 +13742,7 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R15</t>
+          <t>02_Power_Conversion/R207</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="0">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="C76" t="inlineStr" s="0">
         <is>
-          <t>R15</t>
+          <t>R207</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="0">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="E76" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ main-bias pull-up</t>
+          <t>23.7 kΩ 1%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="0">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="J76" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ main-bias pull-up</t>
+          <t>23.7 kΩ 1%</t>
         </is>
       </c>
       <c r="K76" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ main-bias pull-up</t>
+          <t>23.7 kΩ 1%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr" s="0">
@@ -13924,7 +13924,7 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R16</t>
+          <t>02_Power_Conversion/R208</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="0">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="C77" t="inlineStr" s="0">
         <is>
-          <t>R16</t>
+          <t>R208</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="0">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="E77" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ bias feed</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="0">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="J77" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ bias feed</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="K77" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ bias feed</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr" s="0">
@@ -14106,7 +14106,7 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R17</t>
+          <t>02_Power_Conversion/R209</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="0">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="C78" t="inlineStr" s="0">
         <is>
-          <t>R17</t>
+          <t>R209</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="0">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="E78" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ PGOOD pull-up</t>
+          <t>60.4 kΩ 1% — ≈2 A limit (verify)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="0">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="J78" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ PGOOD pull-up</t>
+          <t>60.4 kΩ 1% — ≈2 A limit (verify)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ PGOOD pull-up</t>
+          <t>60.4 kΩ 1% — ≈2 A limit (verify)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr" s="0">
@@ -14288,7 +14288,7 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R18</t>
+          <t>02_Power_Conversion/R210</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="0">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="C79" t="inlineStr" s="0">
         <is>
-          <t>R18</t>
+          <t>R210</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="0">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="E79" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>316 kΩ 0.1%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="0">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="J79" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>316 kΩ 0.1%</t>
         </is>
       </c>
       <c r="K79" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>316 kΩ 0.1%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr" s="0">
@@ -14470,7 +14470,7 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R19</t>
+          <t>02_Power_Conversion/R211</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="0">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="C80" t="inlineStr" s="0">
         <is>
-          <t>R19</t>
+          <t>R211</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="0">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="E80" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>100 kΩ 0.1%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="0">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="J80" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>100 kΩ 0.1%</t>
         </is>
       </c>
       <c r="K80" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>100 kΩ 0.1%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr" s="0">
@@ -14652,7 +14652,7 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R2</t>
+          <t>02_Power_Conversion/R212</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="0">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="C81" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R212</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="0">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="E81" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 0.1%</t>
+          <t>100 kΩ enable</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="0">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="J81" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 0.1%</t>
+          <t>100 kΩ enable</t>
         </is>
       </c>
       <c r="K81" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ 0.1%</t>
+          <t>100 kΩ enable</t>
         </is>
       </c>
       <c r="L81" t="inlineStr" s="0">
@@ -14834,7 +14834,7 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R20</t>
+          <t>02_Power_Conversion/R213</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="0">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="C82" t="inlineStr" s="0">
         <is>
-          <t>R20</t>
+          <t>R213</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="0">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="E82" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>10 kΩ PGOOD pull-up</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="0">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="J82" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>10 kΩ PGOOD pull-up</t>
         </is>
       </c>
       <c r="K82" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-low</t>
+          <t>10 kΩ PGOOD pull-up</t>
         </is>
       </c>
       <c r="L82" t="inlineStr" s="0">
@@ -15016,7 +15016,7 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R21</t>
+          <t>02_Power_Conversion/R214</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="0">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C83" t="inlineStr" s="0">
         <is>
-          <t>R21</t>
+          <t>R214</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="0">
@@ -15198,7 +15198,7 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R22</t>
+          <t>02_Power_Conversion/R215</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="0">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="C84" t="inlineStr" s="0">
         <is>
-          <t>R22</t>
+          <t>R215</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="0">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="E84" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>10 kΩ main-bias pull-up</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="0">
@@ -15243,12 +15243,12 @@
       </c>
       <c r="J84" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>10 kΩ main-bias pull-up</t>
         </is>
       </c>
       <c r="K84" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>10 kΩ main-bias pull-up</t>
         </is>
       </c>
       <c r="L84" t="inlineStr" s="0">
@@ -15380,7 +15380,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R23</t>
+          <t>02_Power_Conversion/R216</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="0">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="C85" t="inlineStr" s="0">
         <is>
-          <t>R23</t>
+          <t>R216</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="0">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="E85" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>100 kΩ bias feed</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="0">
@@ -15425,12 +15425,12 @@
       </c>
       <c r="J85" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>100 kΩ bias feed</t>
         </is>
       </c>
       <c r="K85" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>100 kΩ bias feed</t>
         </is>
       </c>
       <c r="L85" t="inlineStr" s="0">
@@ -15562,7 +15562,7 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R24</t>
+          <t>02_Power_Conversion/R217</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="0">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C86" t="inlineStr" s="0">
         <is>
-          <t>R24</t>
+          <t>R217</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="0">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="E86" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>10 kΩ PGOOD pull-up</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="0">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="J86" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>10 kΩ PGOOD pull-up</t>
         </is>
       </c>
       <c r="K86" t="inlineStr" s="0">
         <is>
-          <t>287 kΩ 1% — 100 mA target (verify)</t>
+          <t>10 kΩ PGOOD pull-up</t>
         </is>
       </c>
       <c r="L86" t="inlineStr" s="0">
@@ -15744,7 +15744,7 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R25</t>
+          <t>02_Power_Conversion/R218</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="0">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="C87" t="inlineStr" s="0">
         <is>
-          <t>R25</t>
+          <t>R218</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="0">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="E87" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="0">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="J87" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="K87" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="L87" t="inlineStr" s="0">
@@ -15926,7 +15926,7 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R26</t>
+          <t>02_Power_Conversion/R219</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="0">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="C88" t="inlineStr" s="0">
         <is>
-          <t>R26</t>
+          <t>R219</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="0">
@@ -15946,7 +15946,7 @@
       </c>
       <c r="E88" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="0">
@@ -15971,12 +15971,12 @@
       </c>
       <c r="J88" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="K88" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="L88" t="inlineStr" s="0">
@@ -16108,7 +16108,7 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R27</t>
+          <t>02_Power_Conversion/R220</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="0">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="C89" t="inlineStr" s="0">
         <is>
-          <t>R27</t>
+          <t>R220</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="0">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="E89" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="0">
@@ -16153,12 +16153,12 @@
       </c>
       <c r="J89" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="K89" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="L89" t="inlineStr" s="0">
@@ -16290,7 +16290,7 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R28</t>
+          <t>02_Power_Conversion/R221</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="0">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="C90" t="inlineStr" s="0">
         <is>
-          <t>R28</t>
+          <t>R221</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="0">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="E90" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="0">
@@ -16335,12 +16335,12 @@
       </c>
       <c r="J90" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>100 kΩ fail-low</t>
         </is>
       </c>
       <c r="L90" t="inlineStr" s="0">
@@ -16472,7 +16472,7 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R29</t>
+          <t>02_Power_Conversion/R222</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="0">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C91" t="inlineStr" s="0">
         <is>
-          <t>R29</t>
+          <t>R222</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="0">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="E91" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="0">
@@ -16517,12 +16517,12 @@
       </c>
       <c r="J91" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="0">
         <is>
-          <t>1 kΩ QOD limit</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr" s="0">
@@ -16654,7 +16654,7 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R3</t>
+          <t>02_Power_Conversion/R223</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="0">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="C92" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R223</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="0">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E92" t="inlineStr" s="0">
         <is>
-          <t>24.9 kΩ 0.1%</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="0">
@@ -16699,12 +16699,12 @@
       </c>
       <c r="J92" t="inlineStr" s="0">
         <is>
-          <t>24.9 kΩ 0.1%</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr" s="0">
         <is>
-          <t>24.9 kΩ 0.1%</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr" s="0">
@@ -16836,7 +16836,7 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R30</t>
+          <t>02_Power_Conversion/R224</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="0">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="C93" t="inlineStr" s="0">
         <is>
-          <t>R30</t>
+          <t>R224</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="0">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="E93" t="inlineStr" s="0">
         <is>
-          <t>23.7 kΩ 1% — USB OV2</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="0">
@@ -16881,12 +16881,12 @@
       </c>
       <c r="J93" t="inlineStr" s="0">
         <is>
-          <t>23.7 kΩ 1% — USB OV2</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr" s="0">
         <is>
-          <t>23.7 kΩ 1% — USB OV2</t>
+          <t>287 kΩ 1% — 100 mA target (verify)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr" s="0">
@@ -17018,7 +17018,7 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R31</t>
+          <t>02_Power_Conversion/R225</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="0">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="C94" t="inlineStr" s="0">
         <is>
-          <t>R31</t>
+          <t>R225</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="0">
@@ -17038,7 +17038,7 @@
       </c>
       <c r="E94" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="0">
@@ -17063,12 +17063,12 @@
       </c>
       <c r="J94" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="K94" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="L94" t="inlineStr" s="0">
@@ -17200,7 +17200,7 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R4</t>
+          <t>02_Power_Conversion/R226</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="0">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="C95" t="inlineStr" s="0">
         <is>
-          <t>R4</t>
+          <t>R226</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="0">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="E95" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="0">
@@ -17245,12 +17245,12 @@
       </c>
       <c r="J95" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="K95" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="L95" t="inlineStr" s="0">
@@ -17382,7 +17382,7 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R5</t>
+          <t>02_Power_Conversion/R227</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="0">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="C96" t="inlineStr" s="0">
         <is>
-          <t>R5</t>
+          <t>R227</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="0">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="E96" t="inlineStr" s="0">
         <is>
-          <t>10.2 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="0">
@@ -17427,12 +17427,12 @@
       </c>
       <c r="J96" t="inlineStr" s="0">
         <is>
-          <t>10.2 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="0">
         <is>
-          <t>10.2 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="L96" t="inlineStr" s="0">
@@ -17564,7 +17564,7 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R6</t>
+          <t>02_Power_Conversion/R228</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="0">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="C97" t="inlineStr" s="0">
         <is>
-          <t>R6</t>
+          <t>R228</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="0">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="E97" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="0">
@@ -17609,12 +17609,12 @@
       </c>
       <c r="J97" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="K97" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="L97" t="inlineStr" s="0">
@@ -17746,7 +17746,7 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R7</t>
+          <t>02_Power_Conversion/R229</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="0">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="C98" t="inlineStr" s="0">
         <is>
-          <t>R7</t>
+          <t>R229</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="0">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="E98" t="inlineStr" s="0">
         <is>
-          <t>23.7 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="0">
@@ -17791,12 +17791,12 @@
       </c>
       <c r="J98" t="inlineStr" s="0">
         <is>
-          <t>23.7 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="0">
         <is>
-          <t>23.7 kΩ 1%</t>
+          <t>1 kΩ QOD limit</t>
         </is>
       </c>
       <c r="L98" t="inlineStr" s="0">
@@ -17928,7 +17928,7 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R8</t>
+          <t>02_Power_Conversion/R230</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="0">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="C99" t="inlineStr" s="0">
         <is>
-          <t>R8</t>
+          <t>R230</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="0">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="E99" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>23.7 kΩ 1% — USB OV2</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="0">
@@ -17973,12 +17973,12 @@
       </c>
       <c r="J99" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>23.7 kΩ 1% — USB OV2</t>
         </is>
       </c>
       <c r="K99" t="inlineStr" s="0">
         <is>
-          <t>5.00 kΩ 1%</t>
+          <t>23.7 kΩ 1% — USB OV2</t>
         </is>
       </c>
       <c r="L99" t="inlineStr" s="0">
@@ -18110,7 +18110,7 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/R9</t>
+          <t>02_Power_Conversion/R231</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="0">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="C100" t="inlineStr" s="0">
         <is>
-          <t>R9</t>
+          <t>R231</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="0">
@@ -18130,7 +18130,7 @@
       </c>
       <c r="E100" t="inlineStr" s="0">
         <is>
-          <t>60.4 kΩ 1% — ≈2 A limit (verify)</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="0">
@@ -18155,12 +18155,12 @@
       </c>
       <c r="J100" t="inlineStr" s="0">
         <is>
-          <t>60.4 kΩ 1% — ≈2 A limit (verify)</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="0">
         <is>
-          <t>60.4 kΩ 1% — ≈2 A limit (verify)</t>
+          <t>5.00 kΩ 1%</t>
         </is>
       </c>
       <c r="L100" t="inlineStr" s="0">
@@ -18292,7 +18292,7 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U1</t>
+          <t>02_Power_Conversion/U201</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="0">
@@ -18302,7 +18302,7 @@
       </c>
       <c r="C101" t="inlineStr" s="0">
         <is>
-          <t>U1</t>
+          <t>U201</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="0">
@@ -18474,7 +18474,7 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U10</t>
+          <t>02_Power_Conversion/U202</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="0">
@@ -18484,17 +18484,17 @@
       </c>
       <c r="C102" t="inlineStr" s="0">
         <is>
-          <t>U10</t>
+          <t>U202</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="0">
         <is>
-          <t>I2C</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 RELAY logic branch</t>
+          <t>TPS2121RUXR priority power mux</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="0">
@@ -18519,12 +18519,12 @@
       </c>
       <c r="J102" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 RELAY logic branch</t>
+          <t>TPS2121RUXR priority power mux</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 RELAY logic branch</t>
+          <t>TPS2121RUXR priority power mux</t>
         </is>
       </c>
       <c r="L102" t="inlineStr" s="0">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="Y102" t="inlineStr" s="0">
         <is>
-          <t>Normal</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr" s="0">
@@ -18656,7 +18656,7 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U11</t>
+          <t>02_Power_Conversion/U203</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="0">
@@ -18666,17 +18666,17 @@
       </c>
       <c r="C103" t="inlineStr" s="0">
         <is>
-          <t>U11</t>
+          <t>U203</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="0">
         <is>
-          <t>I2C</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 FIELD-SENSE branch</t>
+          <t>TPS62130RGTR adjustable 3 A buck</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="0">
@@ -18701,12 +18701,12 @@
       </c>
       <c r="J103" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 FIELD-SENSE branch</t>
+          <t>TPS62130RGTR adjustable 3 A buck</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 FIELD-SENSE branch</t>
+          <t>TPS62130RGTR adjustable 3 A buck</t>
         </is>
       </c>
       <c r="L103" t="inlineStr" s="0">
@@ -18776,7 +18776,7 @@
       </c>
       <c r="Y103" t="inlineStr" s="0">
         <is>
-          <t>Normal</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr" s="0">
@@ -18838,7 +18838,7 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U12</t>
+          <t>02_Power_Conversion/U204</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="0">
@@ -18848,17 +18848,17 @@
       </c>
       <c r="C104" t="inlineStr" s="0">
         <is>
-          <t>U12</t>
+          <t>U204</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="0">
         <is>
-          <t>Power</t>
+          <t>Logic</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
+          <t>SN74LVC1G08-Q1 — MAIN_INPUT_VALID AND MAIN_5V_PGOOD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="0">
@@ -18883,12 +18883,12 @@
       </c>
       <c r="J104" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
+          <t>SN74LVC1G08-Q1 — MAIN_INPUT_VALID AND MAIN_5V_PGOOD</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
+          <t>SN74LVC1G08-Q1 — MAIN_INPUT_VALID AND MAIN_5V_PGOOD</t>
         </is>
       </c>
       <c r="L104" t="inlineStr" s="0">
@@ -19020,7 +19020,7 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U13</t>
+          <t>02_Power_Conversion/U205</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="0">
@@ -19030,22 +19030,22 @@
       </c>
       <c r="C105" t="inlineStr" s="0">
         <is>
-          <t>U13</t>
+          <t>U205</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="0">
         <is>
-          <t>Power</t>
+          <t>Logic</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
+          <t>SN74LVC08A-Q1 quad AND — request × MAIN_POWER_GOOD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="0">
         <is>
-          <t>IPC100:IC10</t>
+          <t>IPC100:QUAL4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="0">
@@ -19065,12 +19065,12 @@
       </c>
       <c r="J105" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
+          <t>SN74LVC08A-Q1 quad AND — request × MAIN_POWER_GOOD</t>
         </is>
       </c>
       <c r="K105" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
+          <t>SN74LVC08A-Q1 quad AND — request × MAIN_POWER_GOOD</t>
         </is>
       </c>
       <c r="L105" t="inlineStr" s="0">
@@ -19202,7 +19202,7 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U2</t>
+          <t>02_Power_Conversion/U206</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="0">
@@ -19212,17 +19212,17 @@
       </c>
       <c r="C106" t="inlineStr" s="0">
         <is>
-          <t>U2</t>
+          <t>U206</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="0">
         <is>
-          <t>Power</t>
+          <t>Displays</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="0">
         <is>
-          <t>TPS2121RUXR priority power mux</t>
+          <t>TPS22918-Q1 OLED load switch</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="0">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="J106" t="inlineStr" s="0">
         <is>
-          <t>TPS2121RUXR priority power mux</t>
+          <t>TPS22918-Q1 OLED load switch</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="0">
         <is>
-          <t>TPS2121RUXR priority power mux</t>
+          <t>TPS22918-Q1 OLED load switch</t>
         </is>
       </c>
       <c r="L106" t="inlineStr" s="0">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="Y106" t="inlineStr" s="0">
         <is>
-          <t>Major</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr" s="0">
@@ -19384,7 +19384,7 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U3</t>
+          <t>02_Power_Conversion/U207</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="0">
@@ -19394,17 +19394,17 @@
       </c>
       <c r="C107" t="inlineStr" s="0">
         <is>
-          <t>U3</t>
+          <t>U207</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="0">
         <is>
-          <t>Power</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="0">
         <is>
-          <t>TPS62130RGTR adjustable 3 A buck</t>
+          <t>TPS22918-Q1 SENSOR load switch</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="0">
@@ -19429,12 +19429,12 @@
       </c>
       <c r="J107" t="inlineStr" s="0">
         <is>
-          <t>TPS62130RGTR adjustable 3 A buck</t>
+          <t>TPS22918-Q1 SENSOR load switch</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="0">
         <is>
-          <t>TPS62130RGTR adjustable 3 A buck</t>
+          <t>TPS22918-Q1 SENSOR load switch</t>
         </is>
       </c>
       <c r="L107" t="inlineStr" s="0">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="Y107" t="inlineStr" s="0">
         <is>
-          <t>Major</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr" s="0">
@@ -19566,7 +19566,7 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U4</t>
+          <t>02_Power_Conversion/U208</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="0">
@@ -19576,17 +19576,17 @@
       </c>
       <c r="C108" t="inlineStr" s="0">
         <is>
-          <t>U4</t>
+          <t>U208</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="0">
         <is>
-          <t>Logic</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="0">
         <is>
-          <t>SN74LVC1G08-Q1 — MAIN_INPUT_VALID AND MAIN_5V_PGOOD</t>
+          <t>TPS22918-Q1 UI load switch</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="0">
@@ -19611,12 +19611,12 @@
       </c>
       <c r="J108" t="inlineStr" s="0">
         <is>
-          <t>SN74LVC1G08-Q1 — MAIN_INPUT_VALID AND MAIN_5V_PGOOD</t>
+          <t>TPS22918-Q1 UI load switch</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="0">
         <is>
-          <t>SN74LVC1G08-Q1 — MAIN_INPUT_VALID AND MAIN_5V_PGOOD</t>
+          <t>TPS22918-Q1 UI load switch</t>
         </is>
       </c>
       <c r="L108" t="inlineStr" s="0">
@@ -19748,7 +19748,7 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U5</t>
+          <t>02_Power_Conversion/U209</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="0">
@@ -19758,22 +19758,22 @@
       </c>
       <c r="C109" t="inlineStr" s="0">
         <is>
-          <t>U5</t>
+          <t>U209</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="0">
         <is>
-          <t>Logic</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="0">
         <is>
-          <t>SN74LVC08A-Q1 quad AND — request × MAIN_POWER_GOOD</t>
+          <t>TPS2553-Q1 EXPANSION 100 mA protected switch — OPTIONAL/DNP</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="0">
         <is>
-          <t>IPC100:QUAL4</t>
+          <t>IPC100:IC10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="0">
@@ -19793,12 +19793,12 @@
       </c>
       <c r="J109" t="inlineStr" s="0">
         <is>
-          <t>SN74LVC08A-Q1 quad AND — request × MAIN_POWER_GOOD</t>
+          <t>TPS2553-Q1 EXPANSION 100 mA protected switch — OPTIONAL/DNP</t>
         </is>
       </c>
       <c r="K109" t="inlineStr" s="0">
         <is>
-          <t>SN74LVC08A-Q1 quad AND — request × MAIN_POWER_GOOD</t>
+          <t>TPS2553-Q1 EXPANSION 100 mA protected switch — OPTIONAL/DNP</t>
         </is>
       </c>
       <c r="L109" t="inlineStr" s="0">
@@ -19930,7 +19930,7 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U6</t>
+          <t>02_Power_Conversion/U210</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="0">
@@ -19940,17 +19940,17 @@
       </c>
       <c r="C110" t="inlineStr" s="0">
         <is>
-          <t>U6</t>
+          <t>U210</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="0">
         <is>
-          <t>Displays</t>
+          <t>I2C</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 OLED load switch</t>
+          <t>TPS22918-Q1 RELAY logic branch</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="0">
@@ -19975,12 +19975,12 @@
       </c>
       <c r="J110" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 OLED load switch</t>
+          <t>TPS22918-Q1 RELAY logic branch</t>
         </is>
       </c>
       <c r="K110" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 OLED load switch</t>
+          <t>TPS22918-Q1 RELAY logic branch</t>
         </is>
       </c>
       <c r="L110" t="inlineStr" s="0">
@@ -20112,7 +20112,7 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U7</t>
+          <t>02_Power_Conversion/U211</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="0">
@@ -20122,17 +20122,17 @@
       </c>
       <c r="C111" t="inlineStr" s="0">
         <is>
-          <t>U7</t>
+          <t>U211</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="0">
         <is>
-          <t>Sensors</t>
+          <t>I2C</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 SENSOR load switch</t>
+          <t>TPS22918-Q1 FIELD-SENSE branch</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="0">
@@ -20157,12 +20157,12 @@
       </c>
       <c r="J111" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 SENSOR load switch</t>
+          <t>TPS22918-Q1 FIELD-SENSE branch</t>
         </is>
       </c>
       <c r="K111" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 SENSOR load switch</t>
+          <t>TPS22918-Q1 FIELD-SENSE branch</t>
         </is>
       </c>
       <c r="L111" t="inlineStr" s="0">
@@ -20294,7 +20294,7 @@
     <row r="112">
       <c r="A112" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U8</t>
+          <t>02_Power_Conversion/U212</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="0">
@@ -20304,7 +20304,7 @@
       </c>
       <c r="C112" t="inlineStr" s="0">
         <is>
-          <t>U8</t>
+          <t>U212</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="0">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="E112" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 UI load switch</t>
+          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="0">
@@ -20339,12 +20339,12 @@
       </c>
       <c r="J112" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 UI load switch</t>
+          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
         </is>
       </c>
       <c r="K112" t="inlineStr" s="0">
         <is>
-          <t>TPS22918-Q1 UI load switch</t>
+          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr" s="0">
@@ -20476,7 +20476,7 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="0">
         <is>
-          <t>02_Power_Conversion/U9</t>
+          <t>02_Power_Conversion/U213</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="0">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="C113" t="inlineStr" s="0">
         <is>
-          <t>U9</t>
+          <t>U213</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="0">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="E113" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 EXPANSION 100 mA protected switch — OPTIONAL/DNP</t>
+          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="0">
@@ -20521,12 +20521,12 @@
       </c>
       <c r="J113" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 EXPANSION 100 mA protected switch — OPTIONAL/DNP</t>
+          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
         </is>
       </c>
       <c r="K113" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 EXPANSION 100 mA protected switch — OPTIONAL/DNP</t>
+          <t>TPS2553-Q1 100 mA motor-logic protected switch (provisional)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr" s="0">
@@ -20658,7 +20658,7 @@
     <row r="114">
       <c r="A114" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/C1</t>
+          <t>03_ESP32_Core/C301</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="0">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="C114" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C301</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="0">
@@ -20840,7 +20840,7 @@
     <row r="115">
       <c r="A115" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/C2</t>
+          <t>03_ESP32_Core/C302</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="0">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="C115" t="inlineStr" s="0">
         <is>
-          <t>C2</t>
+          <t>C302</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="0">
@@ -21022,7 +21022,7 @@
     <row r="116">
       <c r="A116" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/C3</t>
+          <t>03_ESP32_Core/C303</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="0">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="C116" t="inlineStr" s="0">
         <is>
-          <t>C3</t>
+          <t>C303</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="0">
@@ -21204,7 +21204,7 @@
     <row r="117">
       <c r="A117" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/C4</t>
+          <t>03_ESP32_Core/C304</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="0">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="C117" t="inlineStr" s="0">
         <is>
-          <t>C4</t>
+          <t>C304</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="0">
@@ -21386,7 +21386,7 @@
     <row r="118">
       <c r="A118" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/C5</t>
+          <t>03_ESP32_Core/C305</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="0">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="C118" t="inlineStr" s="0">
         <is>
-          <t>C5</t>
+          <t>C305</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="0">
@@ -21568,7 +21568,7 @@
     <row r="119">
       <c r="A119" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/C6</t>
+          <t>03_ESP32_Core/C306</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="0">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="C119" t="inlineStr" s="0">
         <is>
-          <t>C6</t>
+          <t>C306</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="0">
@@ -21750,7 +21750,7 @@
     <row r="120">
       <c r="A120" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/R1</t>
+          <t>03_ESP32_Core/R301</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="0">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="C120" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R301</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="0">
@@ -21932,7 +21932,7 @@
     <row r="121">
       <c r="A121" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/R2</t>
+          <t>03_ESP32_Core/R302</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="0">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="C121" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R302</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="0">
@@ -22114,7 +22114,7 @@
     <row r="122">
       <c r="A122" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/R3</t>
+          <t>03_ESP32_Core/R303</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="0">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C122" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R303</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="0">
@@ -22296,7 +22296,7 @@
     <row r="123">
       <c r="A123" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/R4</t>
+          <t>03_ESP32_Core/R304</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="0">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="C123" t="inlineStr" s="0">
         <is>
-          <t>R4</t>
+          <t>R304</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="0">
@@ -22478,7 +22478,7 @@
     <row r="124">
       <c r="A124" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/R5</t>
+          <t>03_ESP32_Core/R305</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="0">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="C124" t="inlineStr" s="0">
         <is>
-          <t>R5</t>
+          <t>R305</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="0">
@@ -22660,7 +22660,7 @@
     <row r="125">
       <c r="A125" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/SW1</t>
+          <t>03_ESP32_Core/SW301</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="0">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C125" t="inlineStr" s="0">
         <is>
-          <t>SW1</t>
+          <t>SW301</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="0">
@@ -22842,7 +22842,7 @@
     <row r="126">
       <c r="A126" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/SW2</t>
+          <t>03_ESP32_Core/SW302</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="0">
@@ -22852,7 +22852,7 @@
       </c>
       <c r="C126" t="inlineStr" s="0">
         <is>
-          <t>SW2</t>
+          <t>SW302</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="0">
@@ -23024,7 +23024,7 @@
     <row r="127">
       <c r="A127" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/U1</t>
+          <t>03_ESP32_Core/U301</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="0">
@@ -23034,7 +23034,7 @@
       </c>
       <c r="C127" t="inlineStr" s="0">
         <is>
-          <t>U1</t>
+          <t>U301</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="0">
@@ -23206,7 +23206,7 @@
     <row r="128">
       <c r="A128" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/U2</t>
+          <t>03_ESP32_Core/U302</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="0">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="C128" t="inlineStr" s="0">
         <is>
-          <t>U2</t>
+          <t>U302</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="0">
@@ -23388,7 +23388,7 @@
     <row r="129">
       <c r="A129" t="inlineStr" s="0">
         <is>
-          <t>03_ESP32_Core/U3</t>
+          <t>03_ESP32_Core/U303</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="0">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="C129" t="inlineStr" s="0">
         <is>
-          <t>U3</t>
+          <t>U303</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="0">
@@ -23570,7 +23570,7 @@
     <row r="130">
       <c r="A130" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C1</t>
+          <t>04_Safety_Inputs/C401</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="0">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="C130" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C401</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="0">
@@ -23752,7 +23752,7 @@
     <row r="131">
       <c r="A131" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C10</t>
+          <t>04_Safety_Inputs/C402</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="0">
@@ -23762,7 +23762,7 @@
       </c>
       <c r="C131" t="inlineStr" s="0">
         <is>
-          <t>C10</t>
+          <t>C402</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="0">
@@ -23772,7 +23772,7 @@
       </c>
       <c r="E131" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R 10 V</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="0">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="J131" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R 10 V</t>
         </is>
       </c>
       <c r="K131" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R 10 V</t>
         </is>
       </c>
       <c r="L131" t="inlineStr" s="0">
@@ -23934,7 +23934,7 @@
     <row r="132">
       <c r="A132" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C11</t>
+          <t>04_Safety_Inputs/C403</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="0">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="C132" t="inlineStr" s="0">
         <is>
-          <t>C11</t>
+          <t>C403</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="0">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="E132" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="0">
@@ -23979,12 +23979,12 @@
       </c>
       <c r="J132" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="K132" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="L132" t="inlineStr" s="0">
@@ -24116,7 +24116,7 @@
     <row r="133">
       <c r="A133" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C12</t>
+          <t>04_Safety_Inputs/C404</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="0">
@@ -24126,7 +24126,7 @@
       </c>
       <c r="C133" t="inlineStr" s="0">
         <is>
-          <t>C12</t>
+          <t>C404</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="0">
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E133" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="0">
@@ -24161,12 +24161,12 @@
       </c>
       <c r="J133" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="K133" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R LM339B-Q1 local bypass</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="L133" t="inlineStr" s="0">
@@ -24298,7 +24298,7 @@
     <row r="134">
       <c r="A134" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C13</t>
+          <t>04_Safety_Inputs/C405</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="0">
@@ -24308,7 +24308,7 @@
       </c>
       <c r="C134" t="inlineStr" s="0">
         <is>
-          <t>C13</t>
+          <t>C405</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="0">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="E134" t="inlineStr" s="0">
         <is>
-          <t>1 µF X7R local logic bulk</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="0">
@@ -24343,12 +24343,12 @@
       </c>
       <c r="J134" t="inlineStr" s="0">
         <is>
-          <t>1 µF X7R local logic bulk</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="K134" t="inlineStr" s="0">
         <is>
-          <t>1 µF X7R local logic bulk</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="L134" t="inlineStr" s="0">
@@ -24480,7 +24480,7 @@
     <row r="135">
       <c r="A135" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C2</t>
+          <t>04_Safety_Inputs/C406</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="0">
@@ -24490,7 +24490,7 @@
       </c>
       <c r="C135" t="inlineStr" s="0">
         <is>
-          <t>C2</t>
+          <t>C406</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="0">
@@ -24500,7 +24500,7 @@
       </c>
       <c r="E135" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R 10 V</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="0">
@@ -24525,12 +24525,12 @@
       </c>
       <c r="J135" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R 10 V</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="K135" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R 10 V</t>
+          <t>100 nF X7R/C0G, τ=100 µs</t>
         </is>
       </c>
       <c r="L135" t="inlineStr" s="0">
@@ -24662,7 +24662,7 @@
     <row r="136">
       <c r="A136" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C3</t>
+          <t>04_Safety_Inputs/C407</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="0">
@@ -24672,7 +24672,7 @@
       </c>
       <c r="C136" t="inlineStr" s="0">
         <is>
-          <t>C3</t>
+          <t>C407</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="0">
@@ -24844,7 +24844,7 @@
     <row r="137">
       <c r="A137" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C4</t>
+          <t>04_Safety_Inputs/C408</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="0">
@@ -24854,7 +24854,7 @@
       </c>
       <c r="C137" t="inlineStr" s="0">
         <is>
-          <t>C4</t>
+          <t>C408</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="0">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="E137" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R, τ=100 µs</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="0">
@@ -24889,12 +24889,12 @@
       </c>
       <c r="J137" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R, τ=100 µs</t>
         </is>
       </c>
       <c r="K137" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R, τ=100 µs</t>
         </is>
       </c>
       <c r="L137" t="inlineStr" s="0">
@@ -25026,7 +25026,7 @@
     <row r="138">
       <c r="A138" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C5</t>
+          <t>04_Safety_Inputs/C409</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="0">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="C138" t="inlineStr" s="0">
         <is>
-          <t>C5</t>
+          <t>C409</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="0">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="E138" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R, τ=100 µs</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="0">
@@ -25071,12 +25071,12 @@
       </c>
       <c r="J138" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R, τ=100 µs</t>
         </is>
       </c>
       <c r="K138" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R, τ=100 µs</t>
         </is>
       </c>
       <c r="L138" t="inlineStr" s="0">
@@ -25208,7 +25208,7 @@
     <row r="139">
       <c r="A139" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C6</t>
+          <t>04_Safety_Inputs/C410</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="0">
@@ -25218,7 +25218,7 @@
       </c>
       <c r="C139" t="inlineStr" s="0">
         <is>
-          <t>C6</t>
+          <t>C410</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="0">
@@ -25228,7 +25228,7 @@
       </c>
       <c r="E139" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="0">
@@ -25253,12 +25253,12 @@
       </c>
       <c r="J139" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="K139" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="L139" t="inlineStr" s="0">
@@ -25390,7 +25390,7 @@
     <row r="140">
       <c r="A140" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C7</t>
+          <t>04_Safety_Inputs/C411</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="0">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="C140" t="inlineStr" s="0">
         <is>
-          <t>C7</t>
+          <t>C411</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="0">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="E140" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="0">
@@ -25435,12 +25435,12 @@
       </c>
       <c r="J140" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="K140" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R/C0G, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="L140" t="inlineStr" s="0">
@@ -25572,7 +25572,7 @@
     <row r="141">
       <c r="A141" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C8</t>
+          <t>04_Safety_Inputs/C412</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="0">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="C141" t="inlineStr" s="0">
         <is>
-          <t>C8</t>
+          <t>C412</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="0">
@@ -25592,7 +25592,7 @@
       </c>
       <c r="E141" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="0">
@@ -25617,12 +25617,12 @@
       </c>
       <c r="J141" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="K141" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R, τ=100 µs</t>
+          <t>100 nF X7R LM339B-Q1 local bypass</t>
         </is>
       </c>
       <c r="L141" t="inlineStr" s="0">
@@ -25754,7 +25754,7 @@
     <row r="142">
       <c r="A142" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/C9</t>
+          <t>04_Safety_Inputs/C413</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="0">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C142" t="inlineStr" s="0">
         <is>
-          <t>C9</t>
+          <t>C413</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="0">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="E142" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R, τ=100 µs</t>
+          <t>1 µF X7R local logic bulk</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="0">
@@ -25799,12 +25799,12 @@
       </c>
       <c r="J142" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R, τ=100 µs</t>
+          <t>1 µF X7R local logic bulk</t>
         </is>
       </c>
       <c r="K142" t="inlineStr" s="0">
         <is>
-          <t>100 nF X7R, τ=100 µs</t>
+          <t>1 µF X7R local logic bulk</t>
         </is>
       </c>
       <c r="L142" t="inlineStr" s="0">
@@ -25936,7 +25936,7 @@
     <row r="143">
       <c r="A143" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/D1</t>
+          <t>04_Safety_Inputs/D401</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="0">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="C143" t="inlineStr" s="0">
         <is>
-          <t>D1</t>
+          <t>D401</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="0">
@@ -26118,7 +26118,7 @@
     <row r="144">
       <c r="A144" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/D2</t>
+          <t>04_Safety_Inputs/D402</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="0">
@@ -26128,7 +26128,7 @@
       </c>
       <c r="C144" t="inlineStr" s="0">
         <is>
-          <t>D2</t>
+          <t>D402</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="0">
@@ -26300,7 +26300,7 @@
     <row r="145">
       <c r="A145" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/D3</t>
+          <t>04_Safety_Inputs/D403</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="0">
@@ -26310,7 +26310,7 @@
       </c>
       <c r="C145" t="inlineStr" s="0">
         <is>
-          <t>D3</t>
+          <t>D403</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="0">
@@ -26482,7 +26482,7 @@
     <row r="146">
       <c r="A146" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/D4</t>
+          <t>04_Safety_Inputs/D404</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="0">
@@ -26492,7 +26492,7 @@
       </c>
       <c r="C146" t="inlineStr" s="0">
         <is>
-          <t>D4</t>
+          <t>D404</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="0">
@@ -26664,7 +26664,7 @@
     <row r="147">
       <c r="A147" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/D5</t>
+          <t>04_Safety_Inputs/D405</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="0">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="C147" t="inlineStr" s="0">
         <is>
-          <t>D5</t>
+          <t>D405</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="0">
@@ -26846,7 +26846,7 @@
     <row r="148">
       <c r="A148" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/D6</t>
+          <t>04_Safety_Inputs/D406</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="0">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="C148" t="inlineStr" s="0">
         <is>
-          <t>D6</t>
+          <t>D406</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="0">
@@ -27028,7 +27028,7 @@
     <row r="149">
       <c r="A149" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/D7</t>
+          <t>04_Safety_Inputs/D407</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="0">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C149" t="inlineStr" s="0">
         <is>
-          <t>D7</t>
+          <t>D407</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="0">
@@ -27210,7 +27210,7 @@
     <row r="150">
       <c r="A150" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R1</t>
+          <t>04_Safety_Inputs/R401</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="0">
@@ -27220,7 +27220,7 @@
       </c>
       <c r="C150" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R401</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="0">
@@ -27392,7 +27392,7 @@
     <row r="151">
       <c r="A151" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R10</t>
+          <t>04_Safety_Inputs/R402</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="0">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="C151" t="inlineStr" s="0">
         <is>
-          <t>R10</t>
+          <t>R402</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="0">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="E151" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="0">
@@ -27437,12 +27437,12 @@
       </c>
       <c r="J151" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="K151" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="L151" t="inlineStr" s="0">
@@ -27574,7 +27574,7 @@
     <row r="152">
       <c r="A152" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R11</t>
+          <t>04_Safety_Inputs/R403</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="0">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="C152" t="inlineStr" s="0">
         <is>
-          <t>R11</t>
+          <t>R403</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="0">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="E152" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="0">
@@ -27619,12 +27619,12 @@
       </c>
       <c r="J152" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="K152" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="L152" t="inlineStr" s="0">
@@ -27756,7 +27756,7 @@
     <row r="153">
       <c r="A153" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R12</t>
+          <t>04_Safety_Inputs/R404</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="0">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="C153" t="inlineStr" s="0">
         <is>
-          <t>R12</t>
+          <t>R404</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="0">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="E153" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="0">
@@ -27801,12 +27801,12 @@
       </c>
       <c r="J153" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="K153" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="L153" t="inlineStr" s="0">
@@ -27938,7 +27938,7 @@
     <row r="154">
       <c r="A154" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R13</t>
+          <t>04_Safety_Inputs/R405</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="0">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="C154" t="inlineStr" s="0">
         <is>
-          <t>R13</t>
+          <t>R405</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="0">
@@ -27958,7 +27958,7 @@
       </c>
       <c r="E154" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="0">
@@ -27983,12 +27983,12 @@
       </c>
       <c r="J154" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="K154" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>10.0 kΩ ±0.1%</t>
         </is>
       </c>
       <c r="L154" t="inlineStr" s="0">
@@ -28120,7 +28120,7 @@
     <row r="155">
       <c r="A155" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R14</t>
+          <t>04_Safety_Inputs/R406</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="0">
@@ -28130,7 +28130,7 @@
       </c>
       <c r="C155" t="inlineStr" s="0">
         <is>
-          <t>R14</t>
+          <t>R406</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="0">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="E155" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±1% field detector top</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="0">
@@ -28165,12 +28165,12 @@
       </c>
       <c r="J155" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±1% field detector top</t>
         </is>
       </c>
       <c r="K155" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>10.0 kΩ ±1% field detector top</t>
         </is>
       </c>
       <c r="L155" t="inlineStr" s="0">
@@ -28302,7 +28302,7 @@
     <row r="156">
       <c r="A156" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R15</t>
+          <t>04_Safety_Inputs/R407</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="0">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="C156" t="inlineStr" s="0">
         <is>
-          <t>R15</t>
+          <t>R407</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="0">
@@ -28322,7 +28322,7 @@
       </c>
       <c r="E156" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>20.0 kΩ ±1% field detector bottom</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="0">
@@ -28347,12 +28347,12 @@
       </c>
       <c r="J156" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>20.0 kΩ ±1% field detector bottom</t>
         </is>
       </c>
       <c r="K156" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>20.0 kΩ ±1% field detector bottom</t>
         </is>
       </c>
       <c r="L156" t="inlineStr" s="0">
@@ -28484,7 +28484,7 @@
     <row r="157">
       <c r="A157" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R16</t>
+          <t>04_Safety_Inputs/R408</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="0">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="C157" t="inlineStr" s="0">
         <is>
-          <t>R16</t>
+          <t>R408</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="0">
@@ -28666,7 +28666,7 @@
     <row r="158">
       <c r="A158" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R17</t>
+          <t>04_Safety_Inputs/R409</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="0">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="C158" t="inlineStr" s="0">
         <is>
-          <t>R17</t>
+          <t>R409</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="0">
@@ -28848,7 +28848,7 @@
     <row r="159">
       <c r="A159" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R18</t>
+          <t>04_Safety_Inputs/R410</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="0">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="C159" t="inlineStr" s="0">
         <is>
-          <t>R18</t>
+          <t>R410</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="0">
@@ -28868,7 +28868,7 @@
       </c>
       <c r="E159" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-high bias</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="0">
@@ -28893,12 +28893,12 @@
       </c>
       <c r="J159" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-high bias</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="K159" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ fail-high bias</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="L159" t="inlineStr" s="0">
@@ -29030,7 +29030,7 @@
     <row r="160">
       <c r="A160" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R19</t>
+          <t>04_Safety_Inputs/R411</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="0">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="C160" t="inlineStr" s="0">
         <is>
-          <t>R19</t>
+          <t>R411</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="0">
@@ -29050,7 +29050,7 @@
       </c>
       <c r="E160" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% main-only wetting/bias</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="0">
@@ -29075,12 +29075,12 @@
       </c>
       <c r="J160" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% main-only wetting/bias</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="K160" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% main-only wetting/bias</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="L160" t="inlineStr" s="0">
@@ -29212,7 +29212,7 @@
     <row r="161">
       <c r="A161" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R2</t>
+          <t>04_Safety_Inputs/R412</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="0">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="C161" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R412</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="0">
@@ -29232,7 +29232,7 @@
       </c>
       <c r="E161" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="0">
@@ -29257,12 +29257,12 @@
       </c>
       <c r="J161" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="K161" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="L161" t="inlineStr" s="0">
@@ -29394,7 +29394,7 @@
     <row r="162">
       <c r="A162" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R20</t>
+          <t>04_Safety_Inputs/R413</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="0">
@@ -29404,7 +29404,7 @@
       </c>
       <c r="C162" t="inlineStr" s="0">
         <is>
-          <t>R20</t>
+          <t>R413</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="0">
@@ -29576,7 +29576,7 @@
     <row r="163">
       <c r="A163" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R21</t>
+          <t>04_Safety_Inputs/R414</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="0">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="C163" t="inlineStr" s="0">
         <is>
-          <t>R21</t>
+          <t>R414</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="0">
@@ -29596,7 +29596,7 @@
       </c>
       <c r="E163" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ deterministic field-off pull-down</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="0">
@@ -29621,12 +29621,12 @@
       </c>
       <c r="J163" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ deterministic field-off pull-down</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="K163" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ deterministic field-off pull-down</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="L163" t="inlineStr" s="0">
@@ -29758,7 +29758,7 @@
     <row r="164">
       <c r="A164" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R22</t>
+          <t>04_Safety_Inputs/R415</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="0">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="C164" t="inlineStr" s="0">
         <is>
-          <t>R22</t>
+          <t>R415</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="0">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="E164" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% main-only wetting/bias</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="0">
@@ -29803,12 +29803,12 @@
       </c>
       <c r="J164" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% main-only wetting/bias</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="K164" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% main-only wetting/bias</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="L164" t="inlineStr" s="0">
@@ -29940,7 +29940,7 @@
     <row r="165">
       <c r="A165" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R23</t>
+          <t>04_Safety_Inputs/R416</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="0">
@@ -29950,7 +29950,7 @@
       </c>
       <c r="C165" t="inlineStr" s="0">
         <is>
-          <t>R23</t>
+          <t>R416</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="0">
@@ -29960,7 +29960,7 @@
       </c>
       <c r="E165" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="0">
@@ -29985,12 +29985,12 @@
       </c>
       <c r="J165" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="K165" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>2.20 kΩ ±1% loop excitation</t>
         </is>
       </c>
       <c r="L165" t="inlineStr" s="0">
@@ -30122,7 +30122,7 @@
     <row r="166">
       <c r="A166" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R24</t>
+          <t>04_Safety_Inputs/R417</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="0">
@@ -30132,7 +30132,7 @@
       </c>
       <c r="C166" t="inlineStr" s="0">
         <is>
-          <t>R24</t>
+          <t>R417</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="0">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="E166" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ deterministic field-off pull-down</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="0">
@@ -30167,12 +30167,12 @@
       </c>
       <c r="J166" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ deterministic field-off pull-down</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="K166" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ deterministic field-off pull-down</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="L166" t="inlineStr" s="0">
@@ -30304,7 +30304,7 @@
     <row r="167">
       <c r="A167" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R3</t>
+          <t>04_Safety_Inputs/R418</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="0">
@@ -30314,7 +30314,7 @@
       </c>
       <c r="C167" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R418</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="0">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="E167" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>100 kΩ fail-high bias</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="0">
@@ -30349,12 +30349,12 @@
       </c>
       <c r="J167" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>100 kΩ fail-high bias</t>
         </is>
       </c>
       <c r="K167" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>100 kΩ fail-high bias</t>
         </is>
       </c>
       <c r="L167" t="inlineStr" s="0">
@@ -30486,7 +30486,7 @@
     <row r="168">
       <c r="A168" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R4</t>
+          <t>04_Safety_Inputs/R419</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="0">
@@ -30496,7 +30496,7 @@
       </c>
       <c r="C168" t="inlineStr" s="0">
         <is>
-          <t>R4</t>
+          <t>R419</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="0">
@@ -30506,7 +30506,7 @@
       </c>
       <c r="E168" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>10.0 kΩ ±1% main-only wetting/bias</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="0">
@@ -30531,12 +30531,12 @@
       </c>
       <c r="J168" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>10.0 kΩ ±1% main-only wetting/bias</t>
         </is>
       </c>
       <c r="K168" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>10.0 kΩ ±1% main-only wetting/bias</t>
         </is>
       </c>
       <c r="L168" t="inlineStr" s="0">
@@ -30668,7 +30668,7 @@
     <row r="169">
       <c r="A169" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R5</t>
+          <t>04_Safety_Inputs/R420</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="0">
@@ -30678,7 +30678,7 @@
       </c>
       <c r="C169" t="inlineStr" s="0">
         <is>
-          <t>R5</t>
+          <t>R420</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="0">
@@ -30688,7 +30688,7 @@
       </c>
       <c r="E169" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="0">
@@ -30713,12 +30713,12 @@
       </c>
       <c r="J169" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="K169" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±0.1%</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="L169" t="inlineStr" s="0">
@@ -30850,7 +30850,7 @@
     <row r="170">
       <c r="A170" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R6</t>
+          <t>04_Safety_Inputs/R421</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="0">
@@ -30860,7 +30860,7 @@
       </c>
       <c r="C170" t="inlineStr" s="0">
         <is>
-          <t>R6</t>
+          <t>R421</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="0">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="E170" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% field detector top</t>
+          <t>100 kΩ deterministic field-off pull-down</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="0">
@@ -30895,12 +30895,12 @@
       </c>
       <c r="J170" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% field detector top</t>
+          <t>100 kΩ deterministic field-off pull-down</t>
         </is>
       </c>
       <c r="K170" t="inlineStr" s="0">
         <is>
-          <t>10.0 kΩ ±1% field detector top</t>
+          <t>100 kΩ deterministic field-off pull-down</t>
         </is>
       </c>
       <c r="L170" t="inlineStr" s="0">
@@ -31032,7 +31032,7 @@
     <row r="171">
       <c r="A171" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R7</t>
+          <t>04_Safety_Inputs/R422</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="0">
@@ -31042,7 +31042,7 @@
       </c>
       <c r="C171" t="inlineStr" s="0">
         <is>
-          <t>R7</t>
+          <t>R422</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="0">
@@ -31052,7 +31052,7 @@
       </c>
       <c r="E171" t="inlineStr" s="0">
         <is>
-          <t>20.0 kΩ ±1% field detector bottom</t>
+          <t>10.0 kΩ ±1% main-only wetting/bias</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="0">
@@ -31077,12 +31077,12 @@
       </c>
       <c r="J171" t="inlineStr" s="0">
         <is>
-          <t>20.0 kΩ ±1% field detector bottom</t>
+          <t>10.0 kΩ ±1% main-only wetting/bias</t>
         </is>
       </c>
       <c r="K171" t="inlineStr" s="0">
         <is>
-          <t>20.0 kΩ ±1% field detector bottom</t>
+          <t>10.0 kΩ ±1% main-only wetting/bias</t>
         </is>
       </c>
       <c r="L171" t="inlineStr" s="0">
@@ -31214,7 +31214,7 @@
     <row r="172">
       <c r="A172" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R8</t>
+          <t>04_Safety_Inputs/R423</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="0">
@@ -31224,7 +31224,7 @@
       </c>
       <c r="C172" t="inlineStr" s="0">
         <is>
-          <t>R8</t>
+          <t>R423</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="0">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="E172" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="0">
@@ -31259,12 +31259,12 @@
       </c>
       <c r="J172" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="K172" t="inlineStr" s="0">
         <is>
-          <t>2.20 kΩ ±1% loop excitation</t>
+          <t>1.00 kΩ ±1% protected series</t>
         </is>
       </c>
       <c r="L172" t="inlineStr" s="0">
@@ -31396,7 +31396,7 @@
     <row r="173">
       <c r="A173" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/R9</t>
+          <t>04_Safety_Inputs/R424</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="0">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="C173" t="inlineStr" s="0">
         <is>
-          <t>R9</t>
+          <t>R424</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="0">
@@ -31416,7 +31416,7 @@
       </c>
       <c r="E173" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>100 kΩ deterministic field-off pull-down</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="0">
@@ -31441,12 +31441,12 @@
       </c>
       <c r="J173" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>100 kΩ deterministic field-off pull-down</t>
         </is>
       </c>
       <c r="K173" t="inlineStr" s="0">
         <is>
-          <t>1.00 kΩ ±1% protected series</t>
+          <t>100 kΩ deterministic field-off pull-down</t>
         </is>
       </c>
       <c r="L173" t="inlineStr" s="0">
@@ -31578,7 +31578,7 @@
     <row r="174">
       <c r="A174" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U1AB</t>
+          <t>04_Safety_Inputs/U401AB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="0">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="C174" t="inlineStr" s="0">
         <is>
-          <t>U1AB</t>
+          <t>U401AB</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="0">
@@ -31760,7 +31760,7 @@
     <row r="175">
       <c r="A175" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U1CD</t>
+          <t>04_Safety_Inputs/U401CD</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="0">
@@ -31770,7 +31770,7 @@
       </c>
       <c r="C175" t="inlineStr" s="0">
         <is>
-          <t>U1CD</t>
+          <t>U401CD</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="0">
@@ -31942,7 +31942,7 @@
     <row r="176">
       <c r="A176" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U2AB</t>
+          <t>04_Safety_Inputs/U402AB</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="0">
@@ -31952,7 +31952,7 @@
       </c>
       <c r="C176" t="inlineStr" s="0">
         <is>
-          <t>U2AB</t>
+          <t>U402AB</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="0">
@@ -32124,7 +32124,7 @@
     <row r="177">
       <c r="A177" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U2CD</t>
+          <t>04_Safety_Inputs/U402CD</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="0">
@@ -32134,7 +32134,7 @@
       </c>
       <c r="C177" t="inlineStr" s="0">
         <is>
-          <t>U2CD</t>
+          <t>U402CD</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="0">
@@ -32306,7 +32306,7 @@
     <row r="178">
       <c r="A178" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U3AB</t>
+          <t>04_Safety_Inputs/U403AB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="0">
@@ -32316,7 +32316,7 @@
       </c>
       <c r="C178" t="inlineStr" s="0">
         <is>
-          <t>U3AB</t>
+          <t>U403AB</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="0">
@@ -32488,7 +32488,7 @@
     <row r="179">
       <c r="A179" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U3C</t>
+          <t>04_Safety_Inputs/U403C</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="0">
@@ -32498,7 +32498,7 @@
       </c>
       <c r="C179" t="inlineStr" s="0">
         <is>
-          <t>U3C</t>
+          <t>U403C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="0">
@@ -32670,7 +32670,7 @@
     <row r="180">
       <c r="A180" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U3D</t>
+          <t>04_Safety_Inputs/U403D</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="0">
@@ -32680,7 +32680,7 @@
       </c>
       <c r="C180" t="inlineStr" s="0">
         <is>
-          <t>U3D</t>
+          <t>U403D</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="0">
@@ -32852,7 +32852,7 @@
     <row r="181">
       <c r="A181" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U4</t>
+          <t>04_Safety_Inputs/U404</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="0">
@@ -32862,7 +32862,7 @@
       </c>
       <c r="C181" t="inlineStr" s="0">
         <is>
-          <t>U4</t>
+          <t>U404</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="0">
@@ -33034,7 +33034,7 @@
     <row r="182">
       <c r="A182" t="inlineStr" s="0">
         <is>
-          <t>04_Safety_Inputs/U5</t>
+          <t>04_Safety_Inputs/U405</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="0">
@@ -33044,7 +33044,7 @@
       </c>
       <c r="C182" t="inlineStr" s="0">
         <is>
-          <t>U5</t>
+          <t>U405</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="0">
@@ -33216,7 +33216,7 @@
     <row r="183">
       <c r="A183" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/C1</t>
+          <t>05_Motor_Interfaces/C501</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="0">
@@ -33226,7 +33226,7 @@
       </c>
       <c r="C183" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C501</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="0">
@@ -33398,7 +33398,7 @@
     <row r="184">
       <c r="A184" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/C2</t>
+          <t>05_Motor_Interfaces/C502</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="0">
@@ -33408,7 +33408,7 @@
       </c>
       <c r="C184" t="inlineStr" s="0">
         <is>
-          <t>C2</t>
+          <t>C502</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="0">
@@ -33580,7 +33580,7 @@
     <row r="185">
       <c r="A185" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/C3</t>
+          <t>05_Motor_Interfaces/C503</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="0">
@@ -33590,7 +33590,7 @@
       </c>
       <c r="C185" t="inlineStr" s="0">
         <is>
-          <t>C3</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="0">
@@ -33762,7 +33762,7 @@
     <row r="186">
       <c r="A186" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/C4</t>
+          <t>05_Motor_Interfaces/C504</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="0">
@@ -33772,7 +33772,7 @@
       </c>
       <c r="C186" t="inlineStr" s="0">
         <is>
-          <t>C4</t>
+          <t>C504</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="0">
@@ -33944,7 +33944,7 @@
     <row r="187">
       <c r="A187" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/C5</t>
+          <t>05_Motor_Interfaces/C505</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="0">
@@ -33954,7 +33954,7 @@
       </c>
       <c r="C187" t="inlineStr" s="0">
         <is>
-          <t>C5</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="0">
@@ -34126,7 +34126,7 @@
     <row r="188">
       <c r="A188" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/C6</t>
+          <t>05_Motor_Interfaces/C506</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="0">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="C188" t="inlineStr" s="0">
         <is>
-          <t>C6</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="0">
@@ -34308,7 +34308,7 @@
     <row r="189">
       <c r="A189" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/D1</t>
+          <t>05_Motor_Interfaces/D501</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="0">
@@ -34318,7 +34318,7 @@
       </c>
       <c r="C189" t="inlineStr" s="0">
         <is>
-          <t>D1</t>
+          <t>D501</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="0">
@@ -34490,7 +34490,7 @@
     <row r="190">
       <c r="A190" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/D2</t>
+          <t>05_Motor_Interfaces/D502</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="0">
@@ -34500,7 +34500,7 @@
       </c>
       <c r="C190" t="inlineStr" s="0">
         <is>
-          <t>D2</t>
+          <t>D502</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="0">
@@ -34672,7 +34672,7 @@
     <row r="191">
       <c r="A191" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/D3</t>
+          <t>05_Motor_Interfaces/D503</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="0">
@@ -34682,7 +34682,7 @@
       </c>
       <c r="C191" t="inlineStr" s="0">
         <is>
-          <t>D3</t>
+          <t>D503</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="0">
@@ -34854,7 +34854,7 @@
     <row r="192">
       <c r="A192" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/D4</t>
+          <t>05_Motor_Interfaces/D504</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="0">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="C192" t="inlineStr" s="0">
         <is>
-          <t>D4</t>
+          <t>D504</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="0">
@@ -35036,7 +35036,7 @@
     <row r="193">
       <c r="A193" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/D5</t>
+          <t>05_Motor_Interfaces/D505</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="0">
@@ -35046,7 +35046,7 @@
       </c>
       <c r="C193" t="inlineStr" s="0">
         <is>
-          <t>D5</t>
+          <t>D505</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="0">
@@ -35218,7 +35218,7 @@
     <row r="194">
       <c r="A194" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/D6</t>
+          <t>05_Motor_Interfaces/D506</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="0">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C194" t="inlineStr" s="0">
         <is>
-          <t>D6</t>
+          <t>D506</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="0">
@@ -35400,7 +35400,7 @@
     <row r="195">
       <c r="A195" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/D7</t>
+          <t>05_Motor_Interfaces/D507</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="0">
@@ -35410,7 +35410,7 @@
       </c>
       <c r="C195" t="inlineStr" s="0">
         <is>
-          <t>D7</t>
+          <t>D507</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="0">
@@ -35582,7 +35582,7 @@
     <row r="196">
       <c r="A196" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/D8</t>
+          <t>05_Motor_Interfaces/D508</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="0">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C196" t="inlineStr" s="0">
         <is>
-          <t>D8</t>
+          <t>D508</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="0">
@@ -35764,7 +35764,7 @@
     <row r="197">
       <c r="A197" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R1</t>
+          <t>05_Motor_Interfaces/R501</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="0">
@@ -35774,7 +35774,7 @@
       </c>
       <c r="C197" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R501</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="0">
@@ -35946,7 +35946,7 @@
     <row r="198">
       <c r="A198" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R10</t>
+          <t>05_Motor_Interfaces/R502</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="0">
@@ -35956,7 +35956,7 @@
       </c>
       <c r="C198" t="inlineStr" s="0">
         <is>
-          <t>R10</t>
+          <t>R502</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="0">
@@ -35966,7 +35966,7 @@
       </c>
       <c r="E198" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>100 kΩ authorization default off</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="0">
@@ -35991,12 +35991,12 @@
       </c>
       <c r="J198" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>100 kΩ authorization default off</t>
         </is>
       </c>
       <c r="K198" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>100 kΩ authorization default off</t>
         </is>
       </c>
       <c r="L198" t="inlineStr" s="0">
@@ -36128,7 +36128,7 @@
     <row r="199">
       <c r="A199" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R11</t>
+          <t>05_Motor_Interfaces/R503</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="0">
@@ -36138,7 +36138,7 @@
       </c>
       <c r="C199" t="inlineStr" s="0">
         <is>
-          <t>R11</t>
+          <t>R503</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="0">
@@ -36148,7 +36148,7 @@
       </c>
       <c r="E199" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="0">
@@ -36173,12 +36173,12 @@
       </c>
       <c r="J199" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="K199" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="L199" t="inlineStr" s="0">
@@ -36310,7 +36310,7 @@
     <row r="200">
       <c r="A200" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R12</t>
+          <t>05_Motor_Interfaces/R504</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="0">
@@ -36320,7 +36320,7 @@
       </c>
       <c r="C200" t="inlineStr" s="0">
         <is>
-          <t>R12</t>
+          <t>R504</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="0">
@@ -36330,7 +36330,7 @@
       </c>
       <c r="E200" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="0">
@@ -36355,12 +36355,12 @@
       </c>
       <c r="J200" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="K200" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="L200" t="inlineStr" s="0">
@@ -36492,7 +36492,7 @@
     <row r="201">
       <c r="A201" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R13</t>
+          <t>05_Motor_Interfaces/R505</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="0">
@@ -36502,7 +36502,7 @@
       </c>
       <c r="C201" t="inlineStr" s="0">
         <is>
-          <t>R13</t>
+          <t>R505</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="0">
@@ -36512,7 +36512,7 @@
       </c>
       <c r="E201" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="0">
@@ -36537,12 +36537,12 @@
       </c>
       <c r="J201" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="K201" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="L201" t="inlineStr" s="0">
@@ -36674,7 +36674,7 @@
     <row r="202">
       <c r="A202" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R14</t>
+          <t>05_Motor_Interfaces/R506</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="0">
@@ -36684,7 +36684,7 @@
       </c>
       <c r="C202" t="inlineStr" s="0">
         <is>
-          <t>R14</t>
+          <t>R506</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="0">
@@ -36694,7 +36694,7 @@
       </c>
       <c r="E202" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="0">
@@ -36719,12 +36719,12 @@
       </c>
       <c r="J202" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="K202" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="L202" t="inlineStr" s="0">
@@ -36856,7 +36856,7 @@
     <row r="203">
       <c r="A203" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R15</t>
+          <t>05_Motor_Interfaces/R507</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="0">
@@ -36866,7 +36866,7 @@
       </c>
       <c r="C203" t="inlineStr" s="0">
         <is>
-          <t>R15</t>
+          <t>R507</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="0">
@@ -36876,7 +36876,7 @@
       </c>
       <c r="E203" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="0">
@@ -36901,12 +36901,12 @@
       </c>
       <c r="J203" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="K203" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="L203" t="inlineStr" s="0">
@@ -37038,7 +37038,7 @@
     <row r="204">
       <c r="A204" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R16</t>
+          <t>05_Motor_Interfaces/R508</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="0">
@@ -37048,7 +37048,7 @@
       </c>
       <c r="C204" t="inlineStr" s="0">
         <is>
-          <t>R16</t>
+          <t>R508</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="0">
@@ -37058,7 +37058,7 @@
       </c>
       <c r="E204" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="0">
@@ -37083,12 +37083,12 @@
       </c>
       <c r="J204" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="K204" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="L204" t="inlineStr" s="0">
@@ -37220,7 +37220,7 @@
     <row r="205">
       <c r="A205" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R17</t>
+          <t>05_Motor_Interfaces/R509</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="0">
@@ -37230,7 +37230,7 @@
       </c>
       <c r="C205" t="inlineStr" s="0">
         <is>
-          <t>R17</t>
+          <t>R509</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="0">
@@ -37240,7 +37240,7 @@
       </c>
       <c r="E205" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="0">
@@ -37265,12 +37265,12 @@
       </c>
       <c r="J205" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="K205" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="L205" t="inlineStr" s="0">
@@ -37402,7 +37402,7 @@
     <row r="206">
       <c r="A206" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R18</t>
+          <t>05_Motor_Interfaces/R510</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="0">
@@ -37412,7 +37412,7 @@
       </c>
       <c r="C206" t="inlineStr" s="0">
         <is>
-          <t>R18</t>
+          <t>R510</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="0">
@@ -37422,7 +37422,7 @@
       </c>
       <c r="E206" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="0">
@@ -37447,12 +37447,12 @@
       </c>
       <c r="J206" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="K206" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="L206" t="inlineStr" s="0">
@@ -37584,7 +37584,7 @@
     <row r="207">
       <c r="A207" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R19</t>
+          <t>05_Motor_Interfaces/R511</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="0">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C207" t="inlineStr" s="0">
         <is>
-          <t>R19</t>
+          <t>R511</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="0">
@@ -37766,7 +37766,7 @@
     <row r="208">
       <c r="A208" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R2</t>
+          <t>05_Motor_Interfaces/R512</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="0">
@@ -37776,7 +37776,7 @@
       </c>
       <c r="C208" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R512</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="0">
@@ -37786,7 +37786,7 @@
       </c>
       <c r="E208" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ authorization default off</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="0">
@@ -37811,12 +37811,12 @@
       </c>
       <c r="J208" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ authorization default off</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="K208" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ authorization default off</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="L208" t="inlineStr" s="0">
@@ -37948,7 +37948,7 @@
     <row r="209">
       <c r="A209" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R20</t>
+          <t>05_Motor_Interfaces/R513</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="0">
@@ -37958,7 +37958,7 @@
       </c>
       <c r="C209" t="inlineStr" s="0">
         <is>
-          <t>R20</t>
+          <t>R513</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="0">
@@ -37968,7 +37968,7 @@
       </c>
       <c r="E209" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="0">
@@ -37993,12 +37993,12 @@
       </c>
       <c r="J209" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="K209" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="L209" t="inlineStr" s="0">
@@ -38130,7 +38130,7 @@
     <row r="210">
       <c r="A210" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R21</t>
+          <t>05_Motor_Interfaces/R514</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="0">
@@ -38140,7 +38140,7 @@
       </c>
       <c r="C210" t="inlineStr" s="0">
         <is>
-          <t>R21</t>
+          <t>R514</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="0">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="E210" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="0">
@@ -38175,12 +38175,12 @@
       </c>
       <c r="J210" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="K210" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="L210" t="inlineStr" s="0">
@@ -38312,7 +38312,7 @@
     <row r="211">
       <c r="A211" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R22</t>
+          <t>05_Motor_Interfaces/R515</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="0">
@@ -38322,7 +38322,7 @@
       </c>
       <c r="C211" t="inlineStr" s="0">
         <is>
-          <t>R22</t>
+          <t>R515</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="0">
@@ -38332,7 +38332,7 @@
       </c>
       <c r="E211" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="0">
@@ -38357,12 +38357,12 @@
       </c>
       <c r="J211" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="K211" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="L211" t="inlineStr" s="0">
@@ -38494,7 +38494,7 @@
     <row r="212">
       <c r="A212" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R23</t>
+          <t>05_Motor_Interfaces/R516</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="0">
@@ -38504,7 +38504,7 @@
       </c>
       <c r="C212" t="inlineStr" s="0">
         <is>
-          <t>R23</t>
+          <t>R516</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="0">
@@ -38514,7 +38514,7 @@
       </c>
       <c r="E212" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="0">
@@ -38539,12 +38539,12 @@
       </c>
       <c r="J212" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="K212" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="L212" t="inlineStr" s="0">
@@ -38676,7 +38676,7 @@
     <row r="213">
       <c r="A213" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R24</t>
+          <t>05_Motor_Interfaces/R517</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="0">
@@ -38686,7 +38686,7 @@
       </c>
       <c r="C213" t="inlineStr" s="0">
         <is>
-          <t>R24</t>
+          <t>R517</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="0">
@@ -38696,7 +38696,7 @@
       </c>
       <c r="E213" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="0">
@@ -38721,12 +38721,12 @@
       </c>
       <c r="J213" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="K213" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="L213" t="inlineStr" s="0">
@@ -38858,7 +38858,7 @@
     <row r="214">
       <c r="A214" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R25</t>
+          <t>05_Motor_Interfaces/R518</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="0">
@@ -38868,7 +38868,7 @@
       </c>
       <c r="C214" t="inlineStr" s="0">
         <is>
-          <t>R25</t>
+          <t>R518</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="0">
@@ -38878,7 +38878,7 @@
       </c>
       <c r="E214" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="0">
@@ -38903,12 +38903,12 @@
       </c>
       <c r="J214" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="K214" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>47 kΩ MCU-side inactive default</t>
         </is>
       </c>
       <c r="L214" t="inlineStr" s="0">
@@ -39040,7 +39040,7 @@
     <row r="215">
       <c r="A215" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R26</t>
+          <t>05_Motor_Interfaces/R519</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="0">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="C215" t="inlineStr" s="0">
         <is>
-          <t>R26</t>
+          <t>R519</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="0">
@@ -39060,7 +39060,7 @@
       </c>
       <c r="E215" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="0">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="J215" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="K215" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="L215" t="inlineStr" s="0">
@@ -39222,7 +39222,7 @@
     <row r="216">
       <c r="A216" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R27</t>
+          <t>05_Motor_Interfaces/R520</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="0">
@@ -39232,7 +39232,7 @@
       </c>
       <c r="C216" t="inlineStr" s="0">
         <is>
-          <t>R27</t>
+          <t>R520</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="0">
@@ -39242,7 +39242,7 @@
       </c>
       <c r="E216" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ U3 PERMIT fail-low input bias</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="0">
@@ -39267,12 +39267,12 @@
       </c>
       <c r="J216" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ U3 PERMIT fail-low input bias</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="K216" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ U3 PERMIT fail-low input bias</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="L216" t="inlineStr" s="0">
@@ -39404,7 +39404,7 @@
     <row r="217">
       <c r="A217" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R28</t>
+          <t>05_Motor_Interfaces/R521</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="0">
@@ -39414,7 +39414,7 @@
       </c>
       <c r="C217" t="inlineStr" s="0">
         <is>
-          <t>R28</t>
+          <t>R521</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="0">
@@ -39424,7 +39424,7 @@
       </c>
       <c r="E217" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ U3 INHIBIT fail-high input bias</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="0">
@@ -39449,12 +39449,12 @@
       </c>
       <c r="J217" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ U3 INHIBIT fail-high input bias</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="K217" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ U3 INHIBIT fail-high input bias</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="L217" t="inlineStr" s="0">
@@ -39586,7 +39586,7 @@
     <row r="218">
       <c r="A218" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R3</t>
+          <t>05_Motor_Interfaces/R522</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="0">
@@ -39596,7 +39596,7 @@
       </c>
       <c r="C218" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R522</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="0">
@@ -39606,7 +39606,7 @@
       </c>
       <c r="E218" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="0">
@@ -39631,12 +39631,12 @@
       </c>
       <c r="J218" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="K218" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="L218" t="inlineStr" s="0">
@@ -39768,7 +39768,7 @@
     <row r="219">
       <c r="A219" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R4</t>
+          <t>05_Motor_Interfaces/R523</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="0">
@@ -39778,7 +39778,7 @@
       </c>
       <c r="C219" t="inlineStr" s="0">
         <is>
-          <t>R4</t>
+          <t>R523</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="0">
@@ -39788,7 +39788,7 @@
       </c>
       <c r="E219" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="0">
@@ -39813,12 +39813,12 @@
       </c>
       <c r="J219" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="K219" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="L219" t="inlineStr" s="0">
@@ -39950,7 +39950,7 @@
     <row r="220">
       <c r="A220" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R5</t>
+          <t>05_Motor_Interfaces/R524</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="0">
@@ -39960,7 +39960,7 @@
       </c>
       <c r="C220" t="inlineStr" s="0">
         <is>
-          <t>R5</t>
+          <t>R524</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="0">
@@ -39970,7 +39970,7 @@
       </c>
       <c r="E220" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="0">
@@ -39995,12 +39995,12 @@
       </c>
       <c r="J220" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="K220" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="L220" t="inlineStr" s="0">
@@ -40132,7 +40132,7 @@
     <row r="221">
       <c r="A221" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R6</t>
+          <t>05_Motor_Interfaces/R525</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="0">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="C221" t="inlineStr" s="0">
         <is>
-          <t>R6</t>
+          <t>R525</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="0">
@@ -40152,7 +40152,7 @@
       </c>
       <c r="E221" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="0">
@@ -40177,12 +40177,12 @@
       </c>
       <c r="J221" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="K221" t="inlineStr" s="0">
         <is>
-          <t>47 kΩ MCU-side inactive default</t>
+          <t>33 Ω series damping</t>
         </is>
       </c>
       <c r="L221" t="inlineStr" s="0">
@@ -40314,7 +40314,7 @@
     <row r="222">
       <c r="A222" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R7</t>
+          <t>05_Motor_Interfaces/R526</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="0">
@@ -40324,7 +40324,7 @@
       </c>
       <c r="C222" t="inlineStr" s="0">
         <is>
-          <t>R7</t>
+          <t>R526</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="0">
@@ -40334,7 +40334,7 @@
       </c>
       <c r="E222" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="0">
@@ -40359,12 +40359,12 @@
       </c>
       <c r="J222" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="K222" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>10 kΩ safe-side inactive default</t>
         </is>
       </c>
       <c r="L222" t="inlineStr" s="0">
@@ -40496,7 +40496,7 @@
     <row r="223">
       <c r="A223" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R8</t>
+          <t>05_Motor_Interfaces/R527</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="0">
@@ -40506,7 +40506,7 @@
       </c>
       <c r="C223" t="inlineStr" s="0">
         <is>
-          <t>R8</t>
+          <t>R527</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="0">
@@ -40516,7 +40516,7 @@
       </c>
       <c r="E223" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>100 kΩ U503 PERMIT fail-low input bias</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="0">
@@ -40541,12 +40541,12 @@
       </c>
       <c r="J223" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>100 kΩ U503 PERMIT fail-low input bias</t>
         </is>
       </c>
       <c r="K223" t="inlineStr" s="0">
         <is>
-          <t>10 kΩ safe-side inactive default</t>
+          <t>100 kΩ U503 PERMIT fail-low input bias</t>
         </is>
       </c>
       <c r="L223" t="inlineStr" s="0">
@@ -40678,7 +40678,7 @@
     <row r="224">
       <c r="A224" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/R9</t>
+          <t>05_Motor_Interfaces/R528</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="0">
@@ -40688,7 +40688,7 @@
       </c>
       <c r="C224" t="inlineStr" s="0">
         <is>
-          <t>R9</t>
+          <t>R528</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="0">
@@ -40698,7 +40698,7 @@
       </c>
       <c r="E224" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>100 kΩ U503 INHIBIT fail-high input bias</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="0">
@@ -40723,12 +40723,12 @@
       </c>
       <c r="J224" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>100 kΩ U503 INHIBIT fail-high input bias</t>
         </is>
       </c>
       <c r="K224" t="inlineStr" s="0">
         <is>
-          <t>33 Ω series damping</t>
+          <t>100 kΩ U503 INHIBIT fail-high input bias</t>
         </is>
       </c>
       <c r="L224" t="inlineStr" s="0">
@@ -40860,7 +40860,7 @@
     <row r="225">
       <c r="A225" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/U1</t>
+          <t>05_Motor_Interfaces/U501</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="0">
@@ -40870,7 +40870,7 @@
       </c>
       <c r="C225" t="inlineStr" s="0">
         <is>
-          <t>U1</t>
+          <t>U501</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="0">
@@ -41042,7 +41042,7 @@
     <row r="226">
       <c r="A226" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/U2</t>
+          <t>05_Motor_Interfaces/U502</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="0">
@@ -41052,7 +41052,7 @@
       </c>
       <c r="C226" t="inlineStr" s="0">
         <is>
-          <t>U2</t>
+          <t>U502</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="0">
@@ -41224,7 +41224,7 @@
     <row r="227">
       <c r="A227" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/U3</t>
+          <t>05_Motor_Interfaces/U503</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="0">
@@ -41234,7 +41234,7 @@
       </c>
       <c r="C227" t="inlineStr" s="0">
         <is>
-          <t>U3</t>
+          <t>U503</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="0">
@@ -41406,7 +41406,7 @@
     <row r="228">
       <c r="A228" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/U4</t>
+          <t>05_Motor_Interfaces/U504</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="0">
@@ -41416,7 +41416,7 @@
       </c>
       <c r="C228" t="inlineStr" s="0">
         <is>
-          <t>U4</t>
+          <t>U504</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="0">
@@ -41588,7 +41588,7 @@
     <row r="229">
       <c r="A229" t="inlineStr" s="0">
         <is>
-          <t>05_Motor_Interfaces/U5</t>
+          <t>05_Motor_Interfaces/U505</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="0">
@@ -41598,7 +41598,7 @@
       </c>
       <c r="C229" t="inlineStr" s="0">
         <is>
-          <t>U5</t>
+          <t>U505</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="0">
@@ -41770,7 +41770,7 @@
     <row r="230">
       <c r="A230" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/C1</t>
+          <t>06_Relay_MasterInhibit/C601</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="0">
@@ -41780,7 +41780,7 @@
       </c>
       <c r="C230" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C601</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="0">
@@ -41952,7 +41952,7 @@
     <row r="231">
       <c r="A231" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/D1</t>
+          <t>06_Relay_MasterInhibit/D601</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="0">
@@ -41962,7 +41962,7 @@
       </c>
       <c r="C231" t="inlineStr" s="0">
         <is>
-          <t>D1</t>
+          <t>D601</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="0">
@@ -42134,7 +42134,7 @@
     <row r="232">
       <c r="A232" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/K1</t>
+          <t>06_Relay_MasterInhibit/K601</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="0">
@@ -42144,7 +42144,7 @@
       </c>
       <c r="C232" t="inlineStr" s="0">
         <is>
-          <t>K1</t>
+          <t>K601</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="0">
@@ -42316,7 +42316,7 @@
     <row r="233">
       <c r="A233" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/Q1</t>
+          <t>06_Relay_MasterInhibit/Q601</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="0">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="C233" t="inlineStr" s="0">
         <is>
-          <t>Q1</t>
+          <t>Q601</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="0">
@@ -42498,7 +42498,7 @@
     <row r="234">
       <c r="A234" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R1</t>
+          <t>06_Relay_MasterInhibit/R601</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="0">
@@ -42508,7 +42508,7 @@
       </c>
       <c r="C234" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R601</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="0">
@@ -42680,7 +42680,7 @@
     <row r="235">
       <c r="A235" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R10</t>
+          <t>06_Relay_MasterInhibit/R602</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="0">
@@ -42690,7 +42690,7 @@
       </c>
       <c r="C235" t="inlineStr" s="0">
         <is>
-          <t>R10</t>
+          <t>R602</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="0">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="E235" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MASTER_INHIBIT fail-high</t>
+          <t>100 Ω gate resistor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="0">
@@ -42725,12 +42725,12 @@
       </c>
       <c r="J235" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MASTER_INHIBIT fail-high</t>
+          <t>100 Ω gate resistor</t>
         </is>
       </c>
       <c r="K235" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MASTER_INHIBIT fail-high</t>
+          <t>100 Ω gate resistor</t>
         </is>
       </c>
       <c r="L235" t="inlineStr" s="0">
@@ -42862,7 +42862,7 @@
     <row r="236">
       <c r="A236" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R2</t>
+          <t>06_Relay_MasterInhibit/R603</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="0">
@@ -42872,7 +42872,7 @@
       </c>
       <c r="C236" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R603</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="0">
@@ -42882,7 +42882,7 @@
       </c>
       <c r="E236" t="inlineStr" s="0">
         <is>
-          <t>100 Ω gate resistor</t>
+          <t>100 kΩ MOSFET gate default-OFF bias</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="0">
@@ -42907,12 +42907,12 @@
       </c>
       <c r="J236" t="inlineStr" s="0">
         <is>
-          <t>100 Ω gate resistor</t>
+          <t>100 kΩ MOSFET gate default-OFF bias</t>
         </is>
       </c>
       <c r="K236" t="inlineStr" s="0">
         <is>
-          <t>100 Ω gate resistor</t>
+          <t>100 kΩ MOSFET gate default-OFF bias</t>
         </is>
       </c>
       <c r="L236" t="inlineStr" s="0">
@@ -43044,7 +43044,7 @@
     <row r="237">
       <c r="A237" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R3</t>
+          <t>06_Relay_MasterInhibit/R604</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="0">
@@ -43054,7 +43054,7 @@
       </c>
       <c r="C237" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R604</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="0">
@@ -43064,7 +43064,7 @@
       </c>
       <c r="E237" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MOSFET gate default-OFF bias</t>
+          <t>100 kΩ MAIN_POWER_GOOD fail-low</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="0">
@@ -43089,12 +43089,12 @@
       </c>
       <c r="J237" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MOSFET gate default-OFF bias</t>
+          <t>100 kΩ MAIN_POWER_GOOD fail-low</t>
         </is>
       </c>
       <c r="K237" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MOSFET gate default-OFF bias</t>
+          <t>100 kΩ MAIN_POWER_GOOD fail-low</t>
         </is>
       </c>
       <c r="L237" t="inlineStr" s="0">
@@ -43226,7 +43226,7 @@
     <row r="238">
       <c r="A238" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R4</t>
+          <t>06_Relay_MasterInhibit/R605</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="0">
@@ -43236,7 +43236,7 @@
       </c>
       <c r="C238" t="inlineStr" s="0">
         <is>
-          <t>R4</t>
+          <t>R605</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="0">
@@ -43246,7 +43246,7 @@
       </c>
       <c r="E238" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MAIN_POWER_GOOD fail-low</t>
+          <t>100 kΩ RESET_VALID fail-low</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="0">
@@ -43271,12 +43271,12 @@
       </c>
       <c r="J238" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MAIN_POWER_GOOD fail-low</t>
+          <t>100 kΩ RESET_VALID fail-low</t>
         </is>
       </c>
       <c r="K238" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ MAIN_POWER_GOOD fail-low</t>
+          <t>100 kΩ RESET_VALID fail-low</t>
         </is>
       </c>
       <c r="L238" t="inlineStr" s="0">
@@ -43408,7 +43408,7 @@
     <row r="239">
       <c r="A239" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R5</t>
+          <t>06_Relay_MasterInhibit/R606</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="0">
@@ -43418,7 +43418,7 @@
       </c>
       <c r="C239" t="inlineStr" s="0">
         <is>
-          <t>R5</t>
+          <t>R606</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="0">
@@ -43428,7 +43428,7 @@
       </c>
       <c r="E239" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ RESET_VALID fail-low</t>
+          <t>100 kΩ STOP_HW_INHIBIT fail-high</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="0">
@@ -43453,12 +43453,12 @@
       </c>
       <c r="J239" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ RESET_VALID fail-low</t>
+          <t>100 kΩ STOP_HW_INHIBIT fail-high</t>
         </is>
       </c>
       <c r="K239" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ RESET_VALID fail-low</t>
+          <t>100 kΩ STOP_HW_INHIBIT fail-high</t>
         </is>
       </c>
       <c r="L239" t="inlineStr" s="0">
@@ -43590,7 +43590,7 @@
     <row r="240">
       <c r="A240" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R6</t>
+          <t>06_Relay_MasterInhibit/R607</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="0">
@@ -43600,7 +43600,7 @@
       </c>
       <c r="C240" t="inlineStr" s="0">
         <is>
-          <t>R6</t>
+          <t>R607</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="0">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="E240" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ STOP_HW_INHIBIT fail-high</t>
+          <t>100 kΩ RELAY_CMD_MCU fail-low</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="0">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="J240" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ STOP_HW_INHIBIT fail-high</t>
+          <t>100 kΩ RELAY_CMD_MCU fail-low</t>
         </is>
       </c>
       <c r="K240" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ STOP_HW_INHIBIT fail-high</t>
+          <t>100 kΩ RELAY_CMD_MCU fail-low</t>
         </is>
       </c>
       <c r="L240" t="inlineStr" s="0">
@@ -43772,7 +43772,7 @@
     <row r="241">
       <c r="A241" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R7</t>
+          <t>06_Relay_MasterInhibit/R608</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="0">
@@ -43782,7 +43782,7 @@
       </c>
       <c r="C241" t="inlineStr" s="0">
         <is>
-          <t>R7</t>
+          <t>R608</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="0">
@@ -43792,7 +43792,7 @@
       </c>
       <c r="E241" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ RELAY_CMD_MCU fail-low</t>
+          <t>100 kΩ WATCHDOG_VALID fail-low</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="0">
@@ -43817,12 +43817,12 @@
       </c>
       <c r="J241" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ RELAY_CMD_MCU fail-low</t>
+          <t>100 kΩ WATCHDOG_VALID fail-low</t>
         </is>
       </c>
       <c r="K241" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ RELAY_CMD_MCU fail-low</t>
+          <t>100 kΩ WATCHDOG_VALID fail-low</t>
         </is>
       </c>
       <c r="L241" t="inlineStr" s="0">
@@ -43954,7 +43954,7 @@
     <row r="242">
       <c r="A242" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R8</t>
+          <t>06_Relay_MasterInhibit/R609</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="0">
@@ -43964,7 +43964,7 @@
       </c>
       <c r="C242" t="inlineStr" s="0">
         <is>
-          <t>R8</t>
+          <t>R609</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="0">
@@ -43974,7 +43974,7 @@
       </c>
       <c r="E242" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ WATCHDOG_VALID fail-low</t>
+          <t>100 kΩ ACTUATOR_PERMIT fail-low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="0">
@@ -43999,12 +43999,12 @@
       </c>
       <c r="J242" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ WATCHDOG_VALID fail-low</t>
+          <t>100 kΩ ACTUATOR_PERMIT fail-low</t>
         </is>
       </c>
       <c r="K242" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ WATCHDOG_VALID fail-low</t>
+          <t>100 kΩ ACTUATOR_PERMIT fail-low</t>
         </is>
       </c>
       <c r="L242" t="inlineStr" s="0">
@@ -44136,7 +44136,7 @@
     <row r="243">
       <c r="A243" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/R9</t>
+          <t>06_Relay_MasterInhibit/R610</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="0">
@@ -44146,7 +44146,7 @@
       </c>
       <c r="C243" t="inlineStr" s="0">
         <is>
-          <t>R9</t>
+          <t>R610</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="0">
@@ -44156,7 +44156,7 @@
       </c>
       <c r="E243" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ ACTUATOR_PERMIT fail-low</t>
+          <t>100 kΩ MASTER_INHIBIT fail-high</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="0">
@@ -44181,12 +44181,12 @@
       </c>
       <c r="J243" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ ACTUATOR_PERMIT fail-low</t>
+          <t>100 kΩ MASTER_INHIBIT fail-high</t>
         </is>
       </c>
       <c r="K243" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ ACTUATOR_PERMIT fail-low</t>
+          <t>100 kΩ MASTER_INHIBIT fail-high</t>
         </is>
       </c>
       <c r="L243" t="inlineStr" s="0">
@@ -44318,7 +44318,7 @@
     <row r="244">
       <c r="A244" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/U1</t>
+          <t>06_Relay_MasterInhibit/U601</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="0">
@@ -44328,7 +44328,7 @@
       </c>
       <c r="C244" t="inlineStr" s="0">
         <is>
-          <t>U1</t>
+          <t>U601</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="0">
@@ -44500,7 +44500,7 @@
     <row r="245">
       <c r="A245" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/U2</t>
+          <t>06_Relay_MasterInhibit/U602</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="0">
@@ -44510,7 +44510,7 @@
       </c>
       <c r="C245" t="inlineStr" s="0">
         <is>
-          <t>U2</t>
+          <t>U602</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="0">
@@ -44682,7 +44682,7 @@
     <row r="246">
       <c r="A246" t="inlineStr" s="0">
         <is>
-          <t>06_Relay_MasterInhibit/U3</t>
+          <t>06_Relay_MasterInhibit/U603</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="0">
@@ -44692,7 +44692,7 @@
       </c>
       <c r="C246" t="inlineStr" s="0">
         <is>
-          <t>U3</t>
+          <t>U603</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="0">
@@ -44864,7 +44864,7 @@
     <row r="247">
       <c r="A247" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/C1</t>
+          <t>07_UI_Peripherals/C701</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="0">
@@ -44874,7 +44874,7 @@
       </c>
       <c r="C247" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C701</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="0">
@@ -45046,7 +45046,7 @@
     <row r="248">
       <c r="A248" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/Q1</t>
+          <t>07_UI_Peripherals/Q701</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="0">
@@ -45056,7 +45056,7 @@
       </c>
       <c r="C248" t="inlineStr" s="0">
         <is>
-          <t>Q1</t>
+          <t>Q701</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="0">
@@ -45228,7 +45228,7 @@
     <row r="249">
       <c r="A249" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/R1</t>
+          <t>07_UI_Peripherals/R701</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="0">
@@ -45238,7 +45238,7 @@
       </c>
       <c r="C249" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R701</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="0">
@@ -45410,7 +45410,7 @@
     <row r="250">
       <c r="A250" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/R2</t>
+          <t>07_UI_Peripherals/R702</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="0">
@@ -45420,7 +45420,7 @@
       </c>
       <c r="C250" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R702</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="0">
@@ -45592,7 +45592,7 @@
     <row r="251">
       <c r="A251" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/R3</t>
+          <t>07_UI_Peripherals/R703</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="0">
@@ -45602,7 +45602,7 @@
       </c>
       <c r="C251" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R703</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="0">
@@ -45774,7 +45774,7 @@
     <row r="252">
       <c r="A252" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/TP1</t>
+          <t>07_UI_Peripherals/TP701</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="0">
@@ -45784,7 +45784,7 @@
       </c>
       <c r="C252" t="inlineStr" s="0">
         <is>
-          <t>TP1</t>
+          <t>TP701</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="0">
@@ -45956,7 +45956,7 @@
     <row r="253">
       <c r="A253" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/TP2</t>
+          <t>07_UI_Peripherals/TP702</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="0">
@@ -45966,7 +45966,7 @@
       </c>
       <c r="C253" t="inlineStr" s="0">
         <is>
-          <t>TP2</t>
+          <t>TP702</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="0">
@@ -46138,7 +46138,7 @@
     <row r="254">
       <c r="A254" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/TP3</t>
+          <t>07_UI_Peripherals/TP703</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="0">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="C254" t="inlineStr" s="0">
         <is>
-          <t>TP3</t>
+          <t>TP703</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="0">
@@ -46320,7 +46320,7 @@
     <row r="255">
       <c r="A255" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/TP4</t>
+          <t>07_UI_Peripherals/TP704</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="0">
@@ -46330,7 +46330,7 @@
       </c>
       <c r="C255" t="inlineStr" s="0">
         <is>
-          <t>TP4</t>
+          <t>TP704</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="0">
@@ -46502,7 +46502,7 @@
     <row r="256">
       <c r="A256" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/TP5</t>
+          <t>07_UI_Peripherals/TP705</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="0">
@@ -46512,7 +46512,7 @@
       </c>
       <c r="C256" t="inlineStr" s="0">
         <is>
-          <t>TP5</t>
+          <t>TP705</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="0">
@@ -46684,7 +46684,7 @@
     <row r="257">
       <c r="A257" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/U1</t>
+          <t>07_UI_Peripherals/U701</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="0">
@@ -46694,7 +46694,7 @@
       </c>
       <c r="C257" t="inlineStr" s="0">
         <is>
-          <t>U1</t>
+          <t>U701</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="0">
@@ -46866,7 +46866,7 @@
     <row r="258">
       <c r="A258" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/U2</t>
+          <t>07_UI_Peripherals/U702</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="0">
@@ -46876,7 +46876,7 @@
       </c>
       <c r="C258" t="inlineStr" s="0">
         <is>
-          <t>U2</t>
+          <t>U702</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="0">
@@ -47048,7 +47048,7 @@
     <row r="259">
       <c r="A259" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/U3</t>
+          <t>07_UI_Peripherals/U703</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="0">
@@ -47058,7 +47058,7 @@
       </c>
       <c r="C259" t="inlineStr" s="0">
         <is>
-          <t>U3</t>
+          <t>U703</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="0">
@@ -47230,7 +47230,7 @@
     <row r="260">
       <c r="A260" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/U4</t>
+          <t>07_UI_Peripherals/U704</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="0">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="C260" t="inlineStr" s="0">
         <is>
-          <t>U4</t>
+          <t>U704</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="0">
@@ -47412,7 +47412,7 @@
     <row r="261">
       <c r="A261" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/U5</t>
+          <t>07_UI_Peripherals/U705</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="0">
@@ -47422,7 +47422,7 @@
       </c>
       <c r="C261" t="inlineStr" s="0">
         <is>
-          <t>U5</t>
+          <t>U705</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="0">
@@ -47594,7 +47594,7 @@
     <row r="262">
       <c r="A262" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/U6</t>
+          <t>07_UI_Peripherals/U706</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="0">
@@ -47604,7 +47604,7 @@
       </c>
       <c r="C262" t="inlineStr" s="0">
         <is>
-          <t>U6</t>
+          <t>U706</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="0">
@@ -47776,7 +47776,7 @@
     <row r="263">
       <c r="A263" t="inlineStr" s="0">
         <is>
-          <t>07_UI_Peripherals/U7</t>
+          <t>07_UI_Peripherals/U707</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="0">
@@ -47786,7 +47786,7 @@
       </c>
       <c r="C263" t="inlineStr" s="0">
         <is>
-          <t>U7</t>
+          <t>U707</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="0">
@@ -47958,7 +47958,7 @@
     <row r="264">
       <c r="A264" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/C1</t>
+          <t>08_Expansion/C801</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="0">
@@ -47968,7 +47968,7 @@
       </c>
       <c r="C264" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C801</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="0">
@@ -48140,7 +48140,7 @@
     <row r="265">
       <c r="A265" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/C2</t>
+          <t>08_Expansion/C802</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="0">
@@ -48150,7 +48150,7 @@
       </c>
       <c r="C265" t="inlineStr" s="0">
         <is>
-          <t>C2</t>
+          <t>C802</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="0">
@@ -48322,7 +48322,7 @@
     <row r="266">
       <c r="A266" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/C3</t>
+          <t>08_Expansion/C803</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="0">
@@ -48332,7 +48332,7 @@
       </c>
       <c r="C266" t="inlineStr" s="0">
         <is>
-          <t>C3</t>
+          <t>C803</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="0">
@@ -48504,7 +48504,7 @@
     <row r="267">
       <c r="A267" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/D1</t>
+          <t>08_Expansion/D801</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="0">
@@ -48514,7 +48514,7 @@
       </c>
       <c r="C267" t="inlineStr" s="0">
         <is>
-          <t>D1</t>
+          <t>D801</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="0">
@@ -48686,7 +48686,7 @@
     <row r="268">
       <c r="A268" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/D2</t>
+          <t>08_Expansion/D802</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="0">
@@ -48696,7 +48696,7 @@
       </c>
       <c r="C268" t="inlineStr" s="0">
         <is>
-          <t>D2</t>
+          <t>D802</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="0">
@@ -48868,7 +48868,7 @@
     <row r="269">
       <c r="A269" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/D3</t>
+          <t>08_Expansion/D803</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="0">
@@ -48878,7 +48878,7 @@
       </c>
       <c r="C269" t="inlineStr" s="0">
         <is>
-          <t>D3</t>
+          <t>D803</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="0">
@@ -49050,7 +49050,7 @@
     <row r="270">
       <c r="A270" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/FB1</t>
+          <t>08_Expansion/FB801</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="0">
@@ -49060,7 +49060,7 @@
       </c>
       <c r="C270" t="inlineStr" s="0">
         <is>
-          <t>FB1</t>
+          <t>FB801</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="0">
@@ -49232,7 +49232,7 @@
     <row r="271">
       <c r="A271" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R1</t>
+          <t>08_Expansion/R801</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="0">
@@ -49242,7 +49242,7 @@
       </c>
       <c r="C271" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R801</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="0">
@@ -49414,7 +49414,7 @@
     <row r="272">
       <c r="A272" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R2</t>
+          <t>08_Expansion/R802</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="0">
@@ -49424,7 +49424,7 @@
       </c>
       <c r="C272" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R802</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="0">
@@ -49596,7 +49596,7 @@
     <row r="273">
       <c r="A273" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R3</t>
+          <t>08_Expansion/R803</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="0">
@@ -49606,7 +49606,7 @@
       </c>
       <c r="C273" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R803</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="0">
@@ -49778,7 +49778,7 @@
     <row r="274">
       <c r="A274" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R4</t>
+          <t>08_Expansion/R804</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="0">
@@ -49788,7 +49788,7 @@
       </c>
       <c r="C274" t="inlineStr" s="0">
         <is>
-          <t>R4</t>
+          <t>R804</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="0">
@@ -49960,7 +49960,7 @@
     <row r="275">
       <c r="A275" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R5</t>
+          <t>08_Expansion/R805</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="0">
@@ -49970,7 +49970,7 @@
       </c>
       <c r="C275" t="inlineStr" s="0">
         <is>
-          <t>R5</t>
+          <t>R805</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="0">
@@ -50142,7 +50142,7 @@
     <row r="276">
       <c r="A276" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP1</t>
+          <t>08_Expansion/TP801</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="0">
@@ -50152,7 +50152,7 @@
       </c>
       <c r="C276" t="inlineStr" s="0">
         <is>
-          <t>TP1</t>
+          <t>TP801</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="0">
@@ -50324,7 +50324,7 @@
     <row r="277">
       <c r="A277" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP2</t>
+          <t>08_Expansion/TP802</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="0">
@@ -50334,7 +50334,7 @@
       </c>
       <c r="C277" t="inlineStr" s="0">
         <is>
-          <t>TP2</t>
+          <t>TP802</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="0">
@@ -50506,7 +50506,7 @@
     <row r="278">
       <c r="A278" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP3</t>
+          <t>08_Expansion/TP803</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="0">
@@ -50516,7 +50516,7 @@
       </c>
       <c r="C278" t="inlineStr" s="0">
         <is>
-          <t>TP3</t>
+          <t>TP803</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="0">
@@ -50688,7 +50688,7 @@
     <row r="279">
       <c r="A279" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP4</t>
+          <t>08_Expansion/TP804</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="0">
@@ -50698,7 +50698,7 @@
       </c>
       <c r="C279" t="inlineStr" s="0">
         <is>
-          <t>TP4</t>
+          <t>TP804</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="0">
@@ -50870,7 +50870,7 @@
     <row r="280">
       <c r="A280" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP5</t>
+          <t>08_Expansion/TP805</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="0">
@@ -50880,7 +50880,7 @@
       </c>
       <c r="C280" t="inlineStr" s="0">
         <is>
-          <t>TP5</t>
+          <t>TP805</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="0">
@@ -51052,7 +51052,7 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP6</t>
+          <t>08_Expansion/TP806</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="0">
@@ -51062,7 +51062,7 @@
       </c>
       <c r="C281" t="inlineStr" s="0">
         <is>
-          <t>TP6</t>
+          <t>TP806</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="0">
@@ -51234,7 +51234,7 @@
     <row r="282">
       <c r="A282" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/U1</t>
+          <t>08_Expansion/U801</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="0">
@@ -51244,7 +51244,7 @@
       </c>
       <c r="C282" t="inlineStr" s="0">
         <is>
-          <t>U1</t>
+          <t>U801</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="0">
@@ -51416,7 +51416,7 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/U2</t>
+          <t>08_Expansion/U802</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="0">
@@ -51426,7 +51426,7 @@
       </c>
       <c r="C283" t="inlineStr" s="0">
         <is>
-          <t>U2</t>
+          <t>U802</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="0">
@@ -51598,7 +51598,7 @@
     <row r="284">
       <c r="A284" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/C1</t>
+          <t>09_Connectors_Test/C901</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="0">
@@ -51608,7 +51608,7 @@
       </c>
       <c r="C284" t="inlineStr" s="0">
         <is>
-          <t>C1</t>
+          <t>C901</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="0">
@@ -51780,7 +51780,7 @@
     <row r="285">
       <c r="A285" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/D1</t>
+          <t>09_Connectors_Test/D901</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="0">
@@ -51790,7 +51790,7 @@
       </c>
       <c r="C285" t="inlineStr" s="0">
         <is>
-          <t>D1</t>
+          <t>D901</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="0">
@@ -51962,7 +51962,7 @@
     <row r="286">
       <c r="A286" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/D2</t>
+          <t>09_Connectors_Test/D902</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="0">
@@ -51972,7 +51972,7 @@
       </c>
       <c r="C286" t="inlineStr" s="0">
         <is>
-          <t>D2</t>
+          <t>D902</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="0">
@@ -54510,7 +54510,7 @@
     <row r="300">
       <c r="A300" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/R1</t>
+          <t>09_Connectors_Test/R901</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="0">
@@ -54520,7 +54520,7 @@
       </c>
       <c r="C300" t="inlineStr" s="0">
         <is>
-          <t>R1</t>
+          <t>R901</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="0">
@@ -54692,7 +54692,7 @@
     <row r="301">
       <c r="A301" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/R2</t>
+          <t>09_Connectors_Test/R902</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="0">
@@ -54702,7 +54702,7 @@
       </c>
       <c r="C301" t="inlineStr" s="0">
         <is>
-          <t>R2</t>
+          <t>R902</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="0">
@@ -54874,7 +54874,7 @@
     <row r="302">
       <c r="A302" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/R3</t>
+          <t>09_Connectors_Test/R903</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="0">
@@ -54884,7 +54884,7 @@
       </c>
       <c r="C302" t="inlineStr" s="0">
         <is>
-          <t>R3</t>
+          <t>R903</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="0">

--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -20556,7 +20556,7 @@
       </c>
       <c r="F91" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="0">
@@ -20581,12 +20581,12 @@
       </c>
       <c r="K91" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="L91" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="M91" t="inlineStr" s="0">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AA91" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr" s="0">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="AL91" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr" s="0">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="AS91" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
     </row>
@@ -20783,7 +20783,7 @@
       </c>
       <c r="F92" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="0">
@@ -20808,12 +20808,12 @@
       </c>
       <c r="K92" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="L92" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="M92" t="inlineStr" s="0">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="AA92" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr" s="0">
@@ -20943,7 +20943,7 @@
       </c>
       <c r="AL92" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr" s="0">
@@ -20978,7 +20978,7 @@
       </c>
       <c r="AS92" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
     </row>
@@ -21010,7 +21010,7 @@
       </c>
       <c r="F93" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="0">
@@ -21035,12 +21035,12 @@
       </c>
       <c r="K93" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="L93" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 154..209 mA calculated</t>
+          <t>141 kΩ ±1%, ≤100 ppm/°C — TPS2553-Q1 ILIM; 162.8..222.4 mA worst case</t>
         </is>
       </c>
       <c r="M93" t="inlineStr" s="0">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="AA93" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr" s="0">
@@ -21170,7 +21170,7 @@
       </c>
       <c r="AL93" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr" s="0">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="AS93" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
     </row>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="F109" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high EXPANSION switch; 150 kΩ RILIM; OPTIONAL/DNP</t>
+          <t>TPS2553-Q1 active-high EXPANSION switch; 141 kΩ RILIM; 162.8..222.4 mA; OPTIONAL/DNP</t>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="0">
@@ -24667,12 +24667,12 @@
       </c>
       <c r="K109" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high EXPANSION switch; 150 kΩ RILIM; OPTIONAL/DNP</t>
+          <t>TPS2553-Q1 active-high EXPANSION switch; 141 kΩ RILIM; 162.8..222.4 mA; OPTIONAL/DNP</t>
         </is>
       </c>
       <c r="L109" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high EXPANSION switch; 150 kΩ RILIM; OPTIONAL/DNP</t>
+          <t>TPS2553-Q1 active-high EXPANSION switch; 141 kΩ RILIM; 162.8..222.4 mA; OPTIONAL/DNP</t>
         </is>
       </c>
       <c r="M109" t="inlineStr" s="0">
@@ -24747,7 +24747,7 @@
       </c>
       <c r="AA109" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr" s="0">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="AL109" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr" s="0">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="AS109" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
     </row>
@@ -25323,7 +25323,7 @@
       </c>
       <c r="F112" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high motor-logic switch; 150 kΩ RILIM; 154..209 mA</t>
+          <t>TPS2553-Q1 active-high motor-logic switch; 141 kΩ RILIM; 162.8..222.4 mA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="0">
@@ -25348,12 +25348,12 @@
       </c>
       <c r="K112" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high motor-logic switch; 150 kΩ RILIM; 154..209 mA</t>
+          <t>TPS2553-Q1 active-high motor-logic switch; 141 kΩ RILIM; 162.8..222.4 mA</t>
         </is>
       </c>
       <c r="L112" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high motor-logic switch; 150 kΩ RILIM; 154..209 mA</t>
+          <t>TPS2553-Q1 active-high motor-logic switch; 141 kΩ RILIM; 162.8..222.4 mA</t>
         </is>
       </c>
       <c r="M112" t="inlineStr" s="0">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="AA112" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr" s="0">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="AL112" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr" s="0">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="AS112" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
     </row>
@@ -25550,7 +25550,7 @@
       </c>
       <c r="F113" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high motor-logic switch; 150 kΩ RILIM; 154..209 mA</t>
+          <t>TPS2553-Q1 active-high motor-logic switch; 141 kΩ RILIM; 162.8..222.4 mA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="0">
@@ -25575,12 +25575,12 @@
       </c>
       <c r="K113" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high motor-logic switch; 150 kΩ RILIM; 154..209 mA</t>
+          <t>TPS2553-Q1 active-high motor-logic switch; 141 kΩ RILIM; 162.8..222.4 mA</t>
         </is>
       </c>
       <c r="L113" t="inlineStr" s="0">
         <is>
-          <t>TPS2553-Q1 active-high motor-logic switch; 150 kΩ RILIM; 154..209 mA</t>
+          <t>TPS2553-Q1 active-high motor-logic switch; 141 kΩ RILIM; 162.8..222.4 mA</t>
         </is>
       </c>
       <c r="M113" t="inlineStr" s="0">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="AA113" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr" s="0">
@@ -25710,7 +25710,7 @@
       </c>
       <c r="AL113" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr" s="0">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AS113" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 corrected each TPS2553-Q1 channel to an independent legal 150 kOhm RILIM with calculated 154..209 mA bounds; exact suffix/package, thermal, reverse-current, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
         </is>
       </c>
     </row>

--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -93,7 +93,7 @@
     <col min="40" max="40" width="34" customWidth="1"/>
     <col min="41" max="41" width="19" customWidth="1"/>
     <col min="42" max="42" width="48" customWidth="1"/>
-    <col min="43" max="43" width="28" customWidth="1"/>
+    <col min="43" max="43" width="36" customWidth="1"/>
     <col min="44" max="44" width="19" customWidth="1"/>
     <col min="45" max="45" width="48" customWidth="1"/>
   </cols>
@@ -685,7 +685,7 @@
       </c>
       <c r="AA3" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr" s="0">
@@ -730,7 +730,7 @@
       </c>
       <c r="AJ3" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr" s="0">
@@ -740,7 +740,7 @@
       </c>
       <c r="AL3" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr" s="0">
@@ -765,7 +765,7 @@
       </c>
       <c r="AQ3" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr" s="0">
@@ -775,7 +775,7 @@
       </c>
       <c r="AS3" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="AA4" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr" s="0">
@@ -957,7 +957,7 @@
       </c>
       <c r="AJ4" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr" s="0">
@@ -967,7 +967,7 @@
       </c>
       <c r="AL4" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr" s="0">
@@ -992,7 +992,7 @@
       </c>
       <c r="AQ4" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr" s="0">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AS4" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AA5" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr" s="0">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AJ5" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr" s="0">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AL5" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr" s="0">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AQ5" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr" s="0">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AS5" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AA10" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr" s="0">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AJ10" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr" s="0">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AL10" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr" s="0">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AQ10" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr" s="0">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AS10" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AA16" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” saturation, RMS current, DCR, hot loss, impedance/core loss, and surge evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Impedance/inductance, hot DCR, saturation and loss at protected-input waveform.</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr" s="0">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AJ16" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr" s="0">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AL16" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” saturation, RMS current, DCR, hot loss, impedance/core loss, and surge evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Impedance/inductance, hot DCR, saturation and loss at protected-input waveform.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr" s="0">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AQ16" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr" s="0">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AS16" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” saturation, RMS current, DCR, hot loss, impedance/core loss, and surge evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Impedance/inductance, hot DCR, saturation and loss at protected-input waveform.</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="AA37" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 WEBENCH input-capacitance and ripple solution.</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr" s="0">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="AJ37" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr" s="0">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AL37" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 WEBENCH input-capacitance and ripple solution.</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr" s="0">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="AQ37" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr" s="0">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AS37" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 WEBENCH input-capacitance and ripple solution.</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="AA38" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: TI requires 100 nF BOOT-to-SW; exact suffix and dielectric check.</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr" s="0">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="AJ38" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr" s="0">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="AL38" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: TI requires 100 nF BOOT-to-SW; exact suffix and dielectric check.</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr" s="0">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AQ38" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr" s="0">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AS38" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: TI requires 100 nF BOOT-to-SW; exact suffix and dielectric check.</t>
         </is>
       </c>
     </row>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="AA39" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr" s="0">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AJ39" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr" s="0">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AL39" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr" s="0">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="AQ39" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr" s="0">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="AS39" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="AA40" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr" s="0">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="AJ40" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr" s="0">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AL40" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr" s="0">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AQ40" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr" s="0">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="AS40" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="AA41" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Pin/function reconciliation: selected U201 has internal 4 ms soft start.</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr" s="0">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="AJ41" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr" s="0">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AL41" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Pin/function reconciliation: selected U201 has internal 4 ms soft start.</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr" s="0">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="AQ41" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr" s="0">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="AS41" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Pin/function reconciliation: selected U201 has internal 4 ms soft start.</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AA42" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U202 switchover plus U203 input transient model and exact DC-bias curve.</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr" s="0">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="AJ42" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr" s="0">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="AL42" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U202 switchover plus U203 input transient model and exact DC-bias curve.</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr" s="0">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="AQ42" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr" s="0">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="AS42" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U202 switchover plus U203 input transient model and exact DC-bias curve.</t>
         </is>
       </c>
     </row>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="AA44" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr" s="0">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="AJ44" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr" s="0">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="AL44" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr" s="0">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="AQ44" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr" s="0">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="AS44" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
         </is>
       </c>
     </row>
@@ -10219,7 +10219,7 @@
       </c>
       <c r="AA45" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr" s="0">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="AJ45" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr" s="0">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="AL45" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr" s="0">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AQ45" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr" s="0">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="AS45" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="AA46" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact soft-start equation and tolerance.</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr" s="0">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="AJ46" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr" s="0">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="AL46" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact soft-start equation and tolerance.</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr" s="0">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="AQ46" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr" s="0">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AS46" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact soft-start equation and tolerance.</t>
         </is>
       </c>
     </row>
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AA68" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 ripple/current/loss solution at selected PFM/FPWM suffix.</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr" s="0">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AJ68" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr" s="0">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="AL68" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 ripple/current/loss solution at selected PFM/FPWM suffix.</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr" s="0">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AQ68" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr" s="0">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AS68" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 ripple/current/loss solution at selected PFM/FPWM suffix.</t>
         </is>
       </c>
     </row>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="AA69" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact switching mode, ripple, saturation and loss solution.</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr" s="0">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="AJ69" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr" s="0">
@@ -15722,7 +15722,7 @@
       </c>
       <c r="AL69" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact switching mode, ripple, saturation and loss solution.</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr" s="0">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="AQ69" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr" s="0">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="AS69" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact switching mode, ripple, saturation and loss solution.</t>
         </is>
       </c>
     </row>
@@ -26790,7 +26790,7 @@
       </c>
       <c r="AA118" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” SCHEMATIC ECO REQUIRED. ECO â€” correct CT value/target before selection; required evidence: TPS3890-Q1 full CT tolerance stack and schematic value correction.</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr" s="0">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="AJ118" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr" s="0">
@@ -26845,7 +26845,7 @@
       </c>
       <c r="AL118" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” SCHEMATIC ECO REQUIRED. ECO â€” correct CT value/target before selection; required evidence: TPS3890-Q1 full CT tolerance stack and schematic value correction.</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr" s="0">
@@ -26870,7 +26870,7 @@
       </c>
       <c r="AQ118" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr" s="0">
@@ -26880,7 +26880,7 @@
       </c>
       <c r="AS118" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact dielectric, DC-bias effective capacitance, ripple/ESR, aging, and stability evidence are incomplete.</t>
+          <t>PAS-01R: BLOCKED â€” SCHEMATIC ECO REQUIRED. ECO â€” correct CT value/target before selection; required evidence: TPS3890-Q1 full CT tolerance stack and schematic value correction.</t>
         </is>
       </c>
     </row>
@@ -64472,7 +64472,7 @@
       </c>
       <c r="AA284" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U801 threshold/hysteresis/leakage full tolerance stack.</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr" s="0">
@@ -64517,7 +64517,7 @@
       </c>
       <c r="AJ284" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr" s="0">
@@ -64527,7 +64527,7 @@
       </c>
       <c r="AL284" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U801 threshold/hysteresis/leakage full tolerance stack.</t>
         </is>
       </c>
       <c r="AM284" t="inlineStr" s="0">
@@ -64552,7 +64552,7 @@
       </c>
       <c r="AQ284" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR284" t="inlineStr" s="0">
@@ -64562,7 +64562,7 @@
       </c>
       <c r="AS284" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U801 threshold/hysteresis/leakage full tolerance stack.</t>
         </is>
       </c>
     </row>

--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -63,10 +63,10 @@
     <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="48" customWidth="1"/>
     <col min="12" max="12" width="48" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="13" max="13" width="36" customWidth="1"/>
     <col min="14" max="14" width="30" customWidth="1"/>
     <col min="15" max="15" width="48" customWidth="1"/>
-    <col min="16" max="16" width="28" customWidth="1"/>
+    <col min="16" max="16" width="48" customWidth="1"/>
     <col min="17" max="17" width="48" customWidth="1"/>
     <col min="18" max="18" width="30" customWidth="1"/>
     <col min="19" max="19" width="31" customWidth="1"/>
@@ -26685,7 +26685,7 @@
       </c>
       <c r="F118" t="inlineStr" s="0">
         <is>
-          <t>10 nF CT — 100 ms target, verify suffix/equation</t>
+          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 C</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="0">
@@ -26710,17 +26710,17 @@
       </c>
       <c r="K118" t="inlineStr" s="0">
         <is>
-          <t>10 nF CT — 100 ms target, verify suffix/equation</t>
+          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 C</t>
         </is>
       </c>
       <c r="L118" t="inlineStr" s="0">
         <is>
-          <t>10 nF CT — 100 ms target, verify suffix/equation</t>
+          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 C</t>
         </is>
       </c>
       <c r="M118" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>UNRESOLVED - NO FOOTPRINT ASSIGNED</t>
         </is>
       </c>
       <c r="N118" t="inlineStr" s="0">
@@ -26730,22 +26730,22 @@
       </c>
       <c r="O118" t="inlineStr" s="0">
         <is>
-          <t>Requires exact-part review</t>
+          <t>â‰¥10 V rated; approximately 1.29 V maximum CT threshold</t>
         </is>
       </c>
       <c r="P118" t="inlineStr" s="0">
         <is>
-          <t>Requires exact-part review</t>
+          <t>1.35 ÂµA CT charge current maximum plus leakage</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr" s="0">
         <is>
-          <t>As captured where stated; package/derating unresolved</t>
+          <t>93.1 nF Â±1%; C0G/NP0; timing critical; leakage â‰¤10 nA</t>
         </is>
       </c>
       <c r="R118" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>-40 Â°C to +125 Â°C minimum</t>
         </is>
       </c>
       <c r="S118" t="inlineStr" s="0">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="AA118" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” SCHEMATIC ECO REQUIRED. ECO â€” correct CT value/target before selection; required evidence: TPS3890-Q1 full CT tolerance stack and schematic value correction.</t>
+          <t>ECO-009 nominal correction complete. BLOCKED pending exact U302 suffix and an accepted minimum/maximum reset-release window; manufacturer/device plus capacitor envelope is approximately 79.1..136.6 ms.</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr" s="0">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="AJ118" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
+          <t>ECO-009; PAS-01R; TPS3890-Q1 SBVS303B</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr" s="0">
@@ -26845,7 +26845,7 @@
       </c>
       <c r="AL118" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” SCHEMATIC ECO REQUIRED. ECO â€” correct CT value/target before selection; required evidence: TPS3890-Q1 full CT tolerance stack and schematic value correction.</t>
+          <t>ECO-009 nominal correction complete. BLOCKED pending exact U302 suffix and an accepted minimum/maximum reset-release window; manufacturer/device plus capacitor envelope is approximately 79.1..136.6 ms.</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr" s="0">
@@ -26865,12 +26865,12 @@
       </c>
       <c r="AP118" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://www.ti.com/lit/ds/symlink/tps3890-q1.pdf</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R evidence review 2026-07-31</t>
+          <t>SBVS303B; reviewed 2026-07-31</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr" s="0">
@@ -26880,7 +26880,7 @@
       </c>
       <c r="AS118" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” SCHEMATIC ECO REQUIRED. ECO â€” correct CT value/target before selection; required evidence: TPS3890-Q1 full CT tolerance stack and schematic value correction.</t>
+          <t>ECO-009 nominal correction complete. BLOCKED pending exact U302 suffix and an accepted minimum/maximum reset-release window; manufacturer/device plus capacitor envelope is approximately 79.1..136.6 ms.</t>
         </is>
       </c>
     </row>

--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -26685,7 +26685,7 @@
       </c>
       <c r="F118" t="inlineStr" s="0">
         <is>
-          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 C</t>
+          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 Â°C</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="0">
@@ -26710,12 +26710,12 @@
       </c>
       <c r="K118" t="inlineStr" s="0">
         <is>
-          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 C</t>
+          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 Â°C</t>
         </is>
       </c>
       <c r="L118" t="inlineStr" s="0">
         <is>
-          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 C</t>
+          <t>93.1 nF Â±1% C0G/NP0 â‰¥10 V; CT; 99.642 ms nominal; leakage â‰¤10 nA; -40..125 Â°C</t>
         </is>
       </c>
       <c r="M118" t="inlineStr" s="0">
@@ -26730,7 +26730,7 @@
       </c>
       <c r="O118" t="inlineStr" s="0">
         <is>
-          <t>â‰¥10 V rated; approximately 1.29 V maximum CT threshold</t>
+          <t>â‰¥10 V rated; CT node â‰¤1.29 V</t>
         </is>
       </c>
       <c r="P118" t="inlineStr" s="0">
@@ -26740,7 +26740,7 @@
       </c>
       <c r="Q118" t="inlineStr" s="0">
         <is>
-          <t>93.1 nF Â±1%; C0G/NP0; timing critical; leakage â‰¤10 nA</t>
+          <t>93.1 nF Â±1% maximum; C0G/NP0; â‰¥10 V; -40..125 Â°C minimum; â‰¤10 nA leakage; timing critical</t>
         </is>
       </c>
       <c r="R118" t="inlineStr" s="0">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="AA118" t="inlineStr" s="0">
         <is>
-          <t>ECO-009 nominal correction complete. BLOCKED pending exact U302 suffix and an accepted minimum/maximum reset-release window; manufacturer/device plus capacitor envelope is approximately 79.1..136.6 ms.</t>
+          <t>ECO-009R timing implementation verified: 79.1..136.6 ms satisfies QER-03. BLOCKED only for exact U302/C305 MPN, lifecycle, sourcing, and prototype confirmation in PACS-01.</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr" s="0">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="AJ118" t="inlineStr" s="0">
         <is>
-          <t>ECO-009; PAS-01R; TPS3890-Q1 SBVS303B</t>
+          <t>QER-03 QER-RST-01..08; ECO-009R; PAS-01R; TPS3890-Q1 SBVS303B</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr" s="0">
@@ -26845,7 +26845,7 @@
       </c>
       <c r="AL118" t="inlineStr" s="0">
         <is>
-          <t>ECO-009 nominal correction complete. BLOCKED pending exact U302 suffix and an accepted minimum/maximum reset-release window; manufacturer/device plus capacitor envelope is approximately 79.1..136.6 ms.</t>
+          <t>ECO-009R timing implementation verified: 79.1..136.6 ms satisfies QER-03. BLOCKED only for exact U302/C305 MPN, lifecycle, sourcing, and prototype confirmation in PACS-01.</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr" s="0">
@@ -26880,7 +26880,7 @@
       </c>
       <c r="AS118" t="inlineStr" s="0">
         <is>
-          <t>ECO-009 nominal correction complete. BLOCKED pending exact U302 suffix and an accepted minimum/maximum reset-release window; manufacturer/device plus capacitor envelope is approximately 79.1..136.6 ms.</t>
+          <t>ECO-009R timing implementation verified: 79.1..136.6 ms satisfies QER-03. BLOCKED only for exact U302/C305 MPN, lifecycle, sourcing, and prototype confirmation in PACS-01.</t>
         </is>
       </c>
     </row>

--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="EBOM" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -60,22 +60,22 @@
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="10" max="10" width="48" customWidth="1"/>
     <col min="11" max="11" width="48" customWidth="1"/>
     <col min="12" max="12" width="48" customWidth="1"/>
-    <col min="13" max="13" width="36" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="13" max="13" width="48" customWidth="1"/>
+    <col min="14" max="14" width="39" customWidth="1"/>
     <col min="15" max="15" width="48" customWidth="1"/>
     <col min="16" max="16" width="48" customWidth="1"/>
     <col min="17" max="17" width="48" customWidth="1"/>
     <col min="18" max="18" width="30" customWidth="1"/>
-    <col min="19" max="19" width="31" customWidth="1"/>
+    <col min="19" max="19" width="48" customWidth="1"/>
     <col min="20" max="20" width="48" customWidth="1"/>
     <col min="21" max="21" width="48" customWidth="1"/>
     <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="23" width="32" customWidth="1"/>
+    <col min="23" max="23" width="48" customWidth="1"/>
     <col min="24" max="24" width="30" customWidth="1"/>
-    <col min="25" max="25" width="32" customWidth="1"/>
+    <col min="25" max="25" width="48" customWidth="1"/>
     <col min="26" max="26" width="48" customWidth="1"/>
     <col min="27" max="27" width="48" customWidth="1"/>
     <col min="28" max="28" width="13" customWidth="1"/>
@@ -84,10 +84,10 @@
     <col min="31" max="31" width="15" customWidth="1"/>
     <col min="32" max="32" width="16" customWidth="1"/>
     <col min="33" max="33" width="10" customWidth="1"/>
-    <col min="34" max="34" width="30" customWidth="1"/>
+    <col min="34" max="34" width="35" customWidth="1"/>
     <col min="35" max="35" width="16" customWidth="1"/>
     <col min="36" max="36" width="48" customWidth="1"/>
-    <col min="37" max="37" width="16" customWidth="1"/>
+    <col min="37" max="37" width="32" customWidth="1"/>
     <col min="38" max="38" width="48" customWidth="1"/>
     <col min="39" max="39" width="48" customWidth="1"/>
     <col min="40" max="40" width="34" customWidth="1"/>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="I17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="J17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>IAUC100N08S5N034ATMA1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr" s="0">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="M17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>PG-TDSON-8 / SSO8 5x6</t>
         </is>
       </c>
       <c r="N17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O17" t="inlineStr" s="0">
@@ -3823,42 +3823,42 @@
       </c>
       <c r="S17" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="W17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>IAUC100N08S5N034ATMA1</t>
         </is>
       </c>
       <c r="X17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>BUK7J2R4-80M</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr" s="0">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AC17" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr" s="0">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="AG17" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr" s="0">
@@ -3908,44 +3908,44 @@
       </c>
       <c r="AJ17" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr" s="0">
+        <is>
+          <t>BUK7J2R4-80M</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR17" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AS17" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="I35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>UNRESOLVED - PACS-01 BLOCKED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>UNRESOLVED - CAPTURED TPS26630PWPR IS NOT ORDERABLE</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="0">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="M35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Captured 20-pin PWP conflicts with TPS26630 24-pin RGE</t>
         </is>
       </c>
       <c r="N35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O35" t="inlineStr" s="0">
@@ -7909,42 +7909,42 @@
       </c>
       <c r="S35" t="inlineStr" s="0">
         <is>
+          <t>NOT ORDERABLE / UNRESOLVED</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>UNAVAILABLE / UNRESOLVED</t>
         </is>
       </c>
       <c r="V35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="W35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>UNRESOLVED - CAPTURED TPS26630PWPR IS NOT ORDERABLE</t>
         </is>
       </c>
       <c r="X35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS26633PWPR requires controlled variant review</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr" s="0">
@@ -7994,44 +7994,44 @@
       </c>
       <c r="AJ35" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 BLOCKED - UNRESOLVED - CAPTURED TPS26630PWPR IS NOT ORDERABLE. No active-device freeze.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr" s="0">
+        <is>
+          <t>TPS26633PWPR requires controlled variant review</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR35" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="AS35" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 BLOCKED - UNRESOLVED - CAPTURED TPS26630PWPR IS NOT ORDERABLE. No active-device freeze.</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="I36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS259470LRPWR</t>
         </is>
       </c>
       <c r="K36" t="inlineStr" s="0">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="M36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>VQFN-HR-10 RPW</t>
         </is>
       </c>
       <c r="N36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O36" t="inlineStr" s="0">
@@ -8136,42 +8136,42 @@
       </c>
       <c r="S36" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS259470LRPWR</t>
         </is>
       </c>
       <c r="X36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS259470ARPWR (functional, auto-retry)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr" s="0">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AC36" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr" s="0">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="AG36" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr" s="0">
@@ -8221,44 +8221,44 @@
       </c>
       <c r="AJ36" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr" s="0">
+        <is>
+          <t>TPS259470ARPWR (functional, auto-retry)</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL36" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP36" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR36" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="AS36" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -22841,12 +22841,12 @@
       </c>
       <c r="I101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>LMR38020FSQDDARQ1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr" s="0">
@@ -22861,12 +22861,12 @@
       </c>
       <c r="M101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>HSOIC-8 PowerPAD DDA</t>
         </is>
       </c>
       <c r="N101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O101" t="inlineStr" s="0">
@@ -22891,42 +22891,42 @@
       </c>
       <c r="S101" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>LMR38020FSQDDARQ1</t>
         </is>
       </c>
       <c r="X101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>LMR38020SQDDARQ1 (functional, PFM)</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr" s="0">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="AC101" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr" s="0">
@@ -22961,12 +22961,12 @@
       </c>
       <c r="AG101" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr" s="0">
@@ -22976,44 +22976,44 @@
       </c>
       <c r="AJ101" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr" s="0">
+        <is>
+          <t>LMR38020SQDDARQ1 (functional, PFM)</t>
+        </is>
+      </c>
+      <c r="AN101" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL101" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP101" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR101" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="AS101" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -23068,12 +23068,12 @@
       </c>
       <c r="I102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2121RUXR</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="0">
@@ -23088,12 +23088,12 @@
       </c>
       <c r="M102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>VQFN-HR-12 RUX</t>
         </is>
       </c>
       <c r="N102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O102" t="inlineStr" s="0">
@@ -23118,42 +23118,42 @@
       </c>
       <c r="S102" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2121RUXR</t>
         </is>
       </c>
       <c r="X102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2121RUXT (same die, small reel)</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr" s="0">
@@ -23168,7 +23168,7 @@
       </c>
       <c r="AC102" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr" s="0">
@@ -23188,12 +23188,12 @@
       </c>
       <c r="AG102" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr" s="0">
@@ -23203,44 +23203,44 @@
       </c>
       <c r="AJ102" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr" s="0">
+        <is>
+          <t>TPS2121RUXT (same die, small reel)</t>
+        </is>
+      </c>
+      <c r="AN102" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP102" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR102" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -23248,7 +23248,7 @@
       </c>
       <c r="AS102" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -23295,12 +23295,12 @@
       </c>
       <c r="I103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS62135RGXR</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="0">
@@ -23315,12 +23315,12 @@
       </c>
       <c r="M103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>VQFN-HR-11 RGX</t>
         </is>
       </c>
       <c r="N103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O103" t="inlineStr" s="0">
@@ -23345,42 +23345,42 @@
       </c>
       <c r="S103" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS62135RGXR</t>
         </is>
       </c>
       <c r="X103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS621351RGXR (functional, no output discharge)</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr" s="0">
@@ -23395,7 +23395,7 @@
       </c>
       <c r="AC103" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr" s="0">
@@ -23415,12 +23415,12 @@
       </c>
       <c r="AG103" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr" s="0">
@@ -23430,44 +23430,44 @@
       </c>
       <c r="AJ103" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr" s="0">
+        <is>
+          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr" s="0">
+        <is>
+          <t>TPS621351RGXR (functional, no output discharge)</t>
+        </is>
+      </c>
+      <c r="AN103" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL103" t="inlineStr" s="0">
-        <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP103" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR103" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -23475,7 +23475,7 @@
       </c>
       <c r="AS103" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete.</t>
+          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -23522,12 +23522,12 @@
       </c>
       <c r="I104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SN74LVC1G08QDCKRQ1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="0">
@@ -23542,12 +23542,12 @@
       </c>
       <c r="M104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SC70-5 DCK</t>
         </is>
       </c>
       <c r="N104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O104" t="inlineStr" s="0">
@@ -23572,42 +23572,42 @@
       </c>
       <c r="S104" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SN74LVC1G08QDCKRQ1</t>
         </is>
       </c>
       <c r="X104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SN74LVC1G08QDRYRQ1 (functional, different package)</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr" s="0">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AC104" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr" s="0">
@@ -23642,12 +23642,12 @@
       </c>
       <c r="AG104" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr" s="0">
@@ -23657,44 +23657,44 @@
       </c>
       <c r="AJ104" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr" s="0">
+        <is>
+          <t>SN74LVC1G08QDRYRQ1 (functional, different package)</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL104" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP104" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR104" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AS104" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="I105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SN74LVC08AQPWRQ1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr" s="0">
@@ -23769,12 +23769,12 @@
       </c>
       <c r="M105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TSSOP-14 PW</t>
         </is>
       </c>
       <c r="N105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O105" t="inlineStr" s="0">
@@ -23799,42 +23799,42 @@
       </c>
       <c r="S105" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SN74LVC08AQPWRQ1</t>
         </is>
       </c>
       <c r="X105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SN74LVC08AQBQARQ1 (functional, different package)</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr" s="0">
@@ -23849,7 +23849,7 @@
       </c>
       <c r="AC105" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr" s="0">
@@ -23869,12 +23869,12 @@
       </c>
       <c r="AG105" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr" s="0">
@@ -23884,44 +23884,44 @@
       </c>
       <c r="AJ105" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr" s="0">
+        <is>
+          <t>SN74LVC08AQBQARQ1 (functional, different package)</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL105" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP105" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR105" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -23929,7 +23929,7 @@
       </c>
       <c r="AS105" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -23976,12 +23976,12 @@
       </c>
       <c r="I106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="0">
@@ -23996,12 +23996,12 @@
       </c>
       <c r="M106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SOT-23-6 DBV</t>
         </is>
       </c>
       <c r="N106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O106" t="inlineStr" s="0">
@@ -24026,42 +24026,42 @@
       </c>
       <c r="S106" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="X106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr" s="0">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="AC106" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr" s="0">
@@ -24096,12 +24096,12 @@
       </c>
       <c r="AG106" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr" s="0">
@@ -24111,44 +24111,44 @@
       </c>
       <c r="AJ106" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr" s="0">
+        <is>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL106" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP106" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR106" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="AS106" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -24203,12 +24203,12 @@
       </c>
       <c r="I107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="0">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="M107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SOT-23-6 DBV</t>
         </is>
       </c>
       <c r="N107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O107" t="inlineStr" s="0">
@@ -24253,42 +24253,42 @@
       </c>
       <c r="S107" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="X107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr" s="0">
@@ -24303,7 +24303,7 @@
       </c>
       <c r="AC107" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr" s="0">
@@ -24323,12 +24323,12 @@
       </c>
       <c r="AG107" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr" s="0">
@@ -24338,44 +24338,44 @@
       </c>
       <c r="AJ107" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr" s="0">
+        <is>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL107" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP107" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR107" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="AS107" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -24430,12 +24430,12 @@
       </c>
       <c r="I108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="0">
@@ -24450,12 +24450,12 @@
       </c>
       <c r="M108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SOT-23-6 DBV</t>
         </is>
       </c>
       <c r="N108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O108" t="inlineStr" s="0">
@@ -24480,42 +24480,42 @@
       </c>
       <c r="S108" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="X108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr" s="0">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="AC108" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr" s="0">
@@ -24550,12 +24550,12 @@
       </c>
       <c r="AG108" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr" s="0">
@@ -24565,44 +24565,44 @@
       </c>
       <c r="AJ108" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr" s="0">
+        <is>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
+        </is>
+      </c>
+      <c r="AN108" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL108" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP108" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR108" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -24610,7 +24610,7 @@
       </c>
       <c r="AS108" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -24657,12 +24657,12 @@
       </c>
       <c r="I109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2553QDBVRQ1</t>
         </is>
       </c>
       <c r="K109" t="inlineStr" s="0">
@@ -24677,12 +24677,12 @@
       </c>
       <c r="M109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SOT-23-6 DBV</t>
         </is>
       </c>
       <c r="N109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O109" t="inlineStr" s="0">
@@ -24707,42 +24707,42 @@
       </c>
       <c r="S109" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2553QDBVRQ1</t>
         </is>
       </c>
       <c r="X109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2551QDBVRQ1 (functional review required)</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr" s="0">
@@ -24757,7 +24757,7 @@
       </c>
       <c r="AC109" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr" s="0">
@@ -24777,12 +24777,12 @@
       </c>
       <c r="AG109" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr" s="0">
@@ -24792,44 +24792,44 @@
       </c>
       <c r="AJ109" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr" s="0">
+        <is>
+          <t>TPS2551QDBVRQ1 (functional review required)</t>
+        </is>
+      </c>
+      <c r="AN109" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL109" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP109" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR109" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="AS109" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -24884,12 +24884,12 @@
       </c>
       <c r="I110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="K110" t="inlineStr" s="0">
@@ -24904,12 +24904,12 @@
       </c>
       <c r="M110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SOT-23-6 DBV</t>
         </is>
       </c>
       <c r="N110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O110" t="inlineStr" s="0">
@@ -24934,42 +24934,42 @@
       </c>
       <c r="S110" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="X110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr" s="0">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AC110" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr" s="0">
@@ -25004,12 +25004,12 @@
       </c>
       <c r="AG110" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr" s="0">
@@ -25019,44 +25019,44 @@
       </c>
       <c r="AJ110" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr" s="0">
+        <is>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL110" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR110" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -25064,7 +25064,7 @@
       </c>
       <c r="AS110" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -25111,12 +25111,12 @@
       </c>
       <c r="I111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="K111" t="inlineStr" s="0">
@@ -25131,12 +25131,12 @@
       </c>
       <c r="M111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SOT-23-6 DBV</t>
         </is>
       </c>
       <c r="N111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O111" t="inlineStr" s="0">
@@ -25161,42 +25161,42 @@
       </c>
       <c r="S111" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="X111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr" s="0">
@@ -25211,7 +25211,7 @@
       </c>
       <c r="AC111" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr" s="0">
@@ -25231,12 +25231,12 @@
       </c>
       <c r="AG111" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr" s="0">
@@ -25246,44 +25246,44 @@
       </c>
       <c r="AJ111" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr" s="0">
+        <is>
+          <t>TPS22995H-Q1 (functional, different pinout)</t>
+        </is>
+      </c>
+      <c r="AN111" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL111" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP111" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR111" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -25291,7 +25291,7 @@
       </c>
       <c r="AS111" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -25338,12 +25338,12 @@
       </c>
       <c r="I112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2553QDBVRQ1</t>
         </is>
       </c>
       <c r="K112" t="inlineStr" s="0">
@@ -25358,12 +25358,12 @@
       </c>
       <c r="M112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SOT-23-6 DBV</t>
         </is>
       </c>
       <c r="N112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O112" t="inlineStr" s="0">
@@ -25388,42 +25388,42 @@
       </c>
       <c r="S112" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2553QDBVRQ1</t>
         </is>
       </c>
       <c r="X112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2551QDBVRQ1 (functional review required)</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr" s="0">
@@ -25438,7 +25438,7 @@
       </c>
       <c r="AC112" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr" s="0">
@@ -25458,12 +25458,12 @@
       </c>
       <c r="AG112" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr" s="0">
@@ -25473,44 +25473,44 @@
       </c>
       <c r="AJ112" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr" s="0">
+        <is>
+          <t>TPS2551QDBVRQ1 (functional review required)</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL112" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR112" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -25518,7 +25518,7 @@
       </c>
       <c r="AS112" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -25565,12 +25565,12 @@
       </c>
       <c r="I113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2553QDBVRQ1</t>
         </is>
       </c>
       <c r="K113" t="inlineStr" s="0">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="M113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>SOT-23-6 DBV</t>
         </is>
       </c>
       <c r="N113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O113" t="inlineStr" s="0">
@@ -25615,42 +25615,42 @@
       </c>
       <c r="S113" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2553QDBVRQ1</t>
         </is>
       </c>
       <c r="X113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS2551QDBVRQ1 (functional review required)</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr" s="0">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="AC113" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr" s="0">
@@ -25685,12 +25685,12 @@
       </c>
       <c r="AG113" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH113" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr" s="0">
@@ -25700,44 +25700,44 @@
       </c>
       <c r="AJ113" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr" s="0">
+        <is>
+          <t>TPS2551QDBVRQ1 (functional review required)</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL113" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP113" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR113" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AS113" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -28970,12 +28970,12 @@
       </c>
       <c r="I128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS389030QDSERQ1</t>
         </is>
       </c>
       <c r="K128" t="inlineStr" s="0">
@@ -28990,12 +28990,12 @@
       </c>
       <c r="M128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>WSON-6 DSE</t>
         </is>
       </c>
       <c r="N128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O128" t="inlineStr" s="0">
@@ -29020,42 +29020,42 @@
       </c>
       <c r="S128" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U128" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TPS389030QDSERQ1</t>
         </is>
       </c>
       <c r="X128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NONE - threshold/timing/pin exactness required</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr" s="0">
@@ -29070,7 +29070,7 @@
       </c>
       <c r="AC128" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr" s="0">
@@ -29090,12 +29090,12 @@
       </c>
       <c r="AG128" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr" s="0">
@@ -29105,44 +29105,44 @@
       </c>
       <c r="AJ128" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr" s="0">
+        <is>
+          <t>NONE - threshold/timing/pin exactness required</t>
+        </is>
+      </c>
+      <c r="AN128" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL128" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP128" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR128" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AS128" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -60750,12 +60750,12 @@
       </c>
       <c r="I268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TCA9517ADGKR</t>
         </is>
       </c>
       <c r="K268" t="inlineStr" s="0">
@@ -60770,12 +60770,12 @@
       </c>
       <c r="M268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>VSSOP-8 DGK</t>
         </is>
       </c>
       <c r="N268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O268" t="inlineStr" s="0">
@@ -60800,42 +60800,42 @@
       </c>
       <c r="S268" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T268" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U268" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TCA9517ADGKR</t>
         </is>
       </c>
       <c r="X268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>PCA9517ADGKR (functional review required)</t>
         </is>
       </c>
       <c r="Z268" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr" s="0">
@@ -60850,7 +60850,7 @@
       </c>
       <c r="AC268" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AD268" t="inlineStr" s="0">
@@ -60870,12 +60870,12 @@
       </c>
       <c r="AG268" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH268" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI268" t="inlineStr" s="0">
@@ -60885,44 +60885,44 @@
       </c>
       <c r="AJ268" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL268" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM268" t="inlineStr" s="0">
+        <is>
+          <t>PCA9517ADGKR (functional review required)</t>
+        </is>
+      </c>
+      <c r="AN268" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL268" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN268" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO268" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP268" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR268" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -60930,7 +60930,7 @@
       </c>
       <c r="AS268" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -60977,12 +60977,12 @@
       </c>
       <c r="I269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TCA9517ADGKR</t>
         </is>
       </c>
       <c r="K269" t="inlineStr" s="0">
@@ -60997,12 +60997,12 @@
       </c>
       <c r="M269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>VSSOP-8 DGK</t>
         </is>
       </c>
       <c r="N269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O269" t="inlineStr" s="0">
@@ -61027,42 +61027,42 @@
       </c>
       <c r="S269" t="inlineStr" s="0">
         <is>
+          <t>ACTIVE / PRODUCTION - manufacturer review 2026-07-31</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T269" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U269" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>Manufacturer orderable; distributor snapshot requires PO revalidation</t>
         </is>
       </c>
       <c r="V269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>TCA9517ADGKR</t>
         </is>
       </c>
       <c r="X269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>PCA9517ADGKR (functional review required)</t>
         </is>
       </c>
       <c r="Z269" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr" s="0">
@@ -61077,7 +61077,7 @@
       </c>
       <c r="AC269" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr" s="0">
@@ -61097,12 +61097,12 @@
       </c>
       <c r="AG269" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH269" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31 budgetary web snapshot</t>
         </is>
       </c>
       <c r="AI269" t="inlineStr" s="0">
@@ -61112,44 +61112,44 @@
       </c>
       <c r="AJ269" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL269" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr" s="0">
+        <is>
+          <t>PCA9517ADGKR (functional review required)</t>
+        </is>
+      </c>
+      <c r="AN269" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL269" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending.</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN269" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO269" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP269" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR269" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -61157,7 +61157,7 @@
       </c>
       <c r="AS269" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
         </is>
       </c>
     </row>
@@ -65971,12 +65971,12 @@
       </c>
       <c r="I291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>UNRESOLVED - PACS-01 BLOCKED</t>
         </is>
       </c>
       <c r="J291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NO ACTIVE ORDERABLE TLV841SCPH27YBHR FOUND</t>
         </is>
       </c>
       <c r="K291" t="inlineStr" s="0">
@@ -65991,12 +65991,12 @@
       </c>
       <c r="M291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Required DSBGA-4 YBH combination not listed as production OPN</t>
         </is>
       </c>
       <c r="N291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O291" t="inlineStr" s="0">
@@ -66021,42 +66021,42 @@
       </c>
       <c r="S291" t="inlineStr" s="0">
         <is>
+          <t>NOT ORDERABLE / UNRESOLVED</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr" s="0">
+        <is>
           <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
-      <c r="T291" t="inlineStr" s="0">
-        <is>
-          <t>NOT REVIEWED - BLOCKED</t>
-        </is>
-      </c>
       <c r="U291" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>UNAVAILABLE / UNRESOLVED</t>
         </is>
       </c>
       <c r="V291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="W291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NO ACTIVE ORDERABLE TLV841SCPH27YBHR FOUND</t>
         </is>
       </c>
       <c r="X291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>Architecture-compatible alternate not demonstrated</t>
         </is>
       </c>
       <c r="Z291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr" s="0">
@@ -66106,44 +66106,44 @@
       </c>
       <c r="AJ291" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AL291" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 BLOCKED - NO ACTIVE ORDERABLE TLV841SCPH27YBHR FOUND. No active-device freeze.</t>
+        </is>
+      </c>
+      <c r="AM291" t="inlineStr" s="0">
+        <is>
+          <t>Architecture-compatible alternate not demonstrated</t>
+        </is>
+      </c>
+      <c r="AN291" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO291" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL291" t="inlineStr" s="0">
-        <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
-        </is>
-      </c>
-      <c r="AM291" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN291" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO291" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP291" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ291" t="inlineStr" s="0">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
       <c r="AR291" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -66151,7 +66151,7 @@
       </c>
       <c r="AS291" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 BLOCKED - NO ACTIVE ORDERABLE TLV841SCPH27YBHR FOUND. No active-device freeze.</t>
         </is>
       </c>
     </row>

--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -49,7 +49,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS311"/>
+  <dimension ref="A1:AS314"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -60,10 +60,10 @@
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="48" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="48" customWidth="1"/>
     <col min="12" max="12" width="48" customWidth="1"/>
-    <col min="13" max="13" width="48" customWidth="1"/>
+    <col min="13" max="13" width="39" customWidth="1"/>
     <col min="14" max="14" width="39" customWidth="1"/>
     <col min="15" max="15" width="48" customWidth="1"/>
     <col min="16" max="16" width="48" customWidth="1"/>
@@ -73,7 +73,7 @@
     <col min="20" max="20" width="48" customWidth="1"/>
     <col min="21" max="21" width="48" customWidth="1"/>
     <col min="22" max="22" width="30" customWidth="1"/>
-    <col min="23" max="23" width="48" customWidth="1"/>
+    <col min="23" max="23" width="32" customWidth="1"/>
     <col min="24" max="24" width="30" customWidth="1"/>
     <col min="25" max="25" width="48" customWidth="1"/>
     <col min="26" max="26" width="48" customWidth="1"/>
@@ -87,7 +87,7 @@
     <col min="34" max="34" width="35" customWidth="1"/>
     <col min="35" max="35" width="16" customWidth="1"/>
     <col min="36" max="36" width="48" customWidth="1"/>
-    <col min="37" max="37" width="32" customWidth="1"/>
+    <col min="37" max="37" width="40" customWidth="1"/>
     <col min="38" max="38" width="48" customWidth="1"/>
     <col min="39" max="39" width="48" customWidth="1"/>
     <col min="40" max="40" width="34" customWidth="1"/>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="AK17" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr" s="0">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="F35" t="inlineStr" s="0">
         <is>
-          <t>TPS26630PWPR (provisional)</t>
+          <t>TPS26631PWPR 60 V eFuse; 20-pin PWP; adjustable OVP; 2x pulse support</t>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="0">
         <is>
-          <t>IPC100:TPS26630</t>
+          <t>IPC100:TPS26631_PWP</t>
         </is>
       </c>
       <c r="H35" t="inlineStr" s="0">
@@ -7859,27 +7859,27 @@
       </c>
       <c r="I35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - PACS-01 BLOCKED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CAPTURED TPS26630PWPR IS NOT ORDERABLE</t>
+          <t>TPS26631PWPR</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="0">
         <is>
-          <t>TPS26630PWPR (provisional)</t>
+          <t>TPS26631PWPR 60 V eFuse; 20-pin PWP; adjustable OVP; 2x pulse support</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="0">
         <is>
-          <t>TPS26630PWPR (provisional)</t>
+          <t>TPS26631PWPR 60 V eFuse; 20-pin PWP; adjustable OVP; 2x pulse support</t>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="0">
         <is>
-          <t>Captured 20-pin PWP conflicts with TPS26630 24-pin RGE</t>
+          <t>HTSSOP-20 PWP; footprint not assigned</t>
         </is>
       </c>
       <c r="N35" t="inlineStr" s="0">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="S35" t="inlineStr" s="0">
         <is>
-          <t>NOT ORDERABLE / UNRESOLVED</t>
+          <t>ACTIVE - TI review 2026-07-31</t>
         </is>
       </c>
       <c r="T35" t="inlineStr" s="0">
@@ -7919,17 +7919,17 @@
       </c>
       <c r="U35" t="inlineStr" s="0">
         <is>
-          <t>UNAVAILABLE / UNRESOLVED</t>
+          <t>Orderable; stock requires PO revalidation</t>
         </is>
       </c>
       <c r="V35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W35" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CAPTURED TPS26630PWPR IS NOT ORDERABLE</t>
+          <t>TPS26631PWPR</t>
         </is>
       </c>
       <c r="X35" t="inlineStr" s="0">
@@ -7994,17 +7994,17 @@
       </c>
       <c r="AJ35" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>ECO-010; PACS-01R</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 BLOCKED - UNRESOLVED - CAPTURED TPS26630PWPR IS NOT ORDERABLE. No active-device freeze.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr" s="0">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="AS35" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 BLOCKED - UNRESOLVED - CAPTURED TPS26630PWPR IS NOT ORDERABLE. No active-device freeze.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release.</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="AK36" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr" s="0">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="AK101" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr" s="0">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="AK102" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr" s="0">
@@ -23435,7 +23435,7 @@
       </c>
       <c r="AK103" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr" s="0">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="AK104" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr" s="0">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="AK105" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr" s="0">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="AK106" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr" s="0">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="AK107" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr" s="0">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="AK108" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr" s="0">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="AK109" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr" s="0">
@@ -25024,7 +25024,7 @@
       </c>
       <c r="AK110" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr" s="0">
@@ -25251,7 +25251,7 @@
       </c>
       <c r="AK111" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr" s="0">
@@ -25478,7 +25478,7 @@
       </c>
       <c r="AK112" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr" s="0">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="AK113" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr" s="0">
@@ -29110,7 +29110,7 @@
       </c>
       <c r="AK128" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr" s="0">
@@ -60890,7 +60890,7 @@
       </c>
       <c r="AK268" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL268" t="inlineStr" s="0">
@@ -61117,7 +61117,7 @@
       </c>
       <c r="AK269" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL269" t="inlineStr" s="0">
@@ -62072,7 +62072,7 @@
     <row r="274">
       <c r="A274" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/D801</t>
+          <t>08_Expansion/C805</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="0">
@@ -62082,27 +62082,27 @@
       </c>
       <c r="C274" t="inlineStr" s="0">
         <is>
-          <t>D801</t>
+          <t>C805</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="0">
         <is>
-          <t>Protection</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="0">
         <is>
-          <t>OUTSIDE CSR-01A</t>
+          <t>CSR-01A POWER</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="0">
         <is>
-          <t>J10 SDA low-capacitance TVS provision; IEC 61000-4-2 target</t>
+          <t>10 nF Â±10% X7R - TPS3899 CTR; 6.2 ms nominal</t>
         </is>
       </c>
       <c r="G274" t="inlineStr" s="0">
         <is>
-          <t>IPC100:ESD_PROVISION</t>
+          <t>IPC100:C</t>
         </is>
       </c>
       <c r="H274" t="inlineStr" s="0">
@@ -62112,32 +62112,32 @@
       </c>
       <c r="I274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - PACS-01R</t>
         </is>
       </c>
       <c r="J274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - PACS-01R</t>
         </is>
       </c>
       <c r="K274" t="inlineStr" s="0">
         <is>
-          <t>J10 SDA low-capacitance TVS provision; IEC 61000-4-2 target</t>
+          <t>10 nF Â±10% X7R - TPS3899 CTR; 6.2 ms nominal</t>
         </is>
       </c>
       <c r="L274" t="inlineStr" s="0">
         <is>
-          <t>J10 SDA low-capacitance TVS provision; IEC 61000-4-2 target</t>
+          <t>10 nF Â±10% X7R - TPS3899 CTR; 6.2 ms nominal</t>
         </is>
       </c>
       <c r="M274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - NO FOOTPRINT ASSIGNED</t>
         </is>
       </c>
       <c r="N274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="O274" t="inlineStr" s="0">
@@ -62157,57 +62157,57 @@
       </c>
       <c r="R274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="S274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="T274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="U274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="V274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="W274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="X274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Y274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Z274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr" s="0">
         <is>
-          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
         </is>
       </c>
       <c r="AB274" t="inlineStr" s="0">
         <is>
-          <t>Major</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr" s="0">
@@ -62242,22 +62242,22 @@
       </c>
       <c r="AI274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AJ274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>ECO-010; PACS-01R</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL274" t="inlineStr" s="0">
         <is>
-          <t>Outside current package; do not source or assign a footprint.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
         </is>
       </c>
       <c r="AM274" t="inlineStr" s="0">
@@ -62282,7 +62282,7 @@
       </c>
       <c r="AQ274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AR274" t="inlineStr" s="0">
@@ -62292,14 +62292,14 @@
       </c>
       <c r="AS274" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/D802</t>
+          <t>08_Expansion/D801</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="0">
@@ -62309,7 +62309,7 @@
       </c>
       <c r="C275" t="inlineStr" s="0">
         <is>
-          <t>D802</t>
+          <t>D801</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="0">
@@ -62324,7 +62324,7 @@
       </c>
       <c r="F275" t="inlineStr" s="0">
         <is>
-          <t>J10 SCL low-capacitance TVS provision; IEC 61000-4-2 target</t>
+          <t>J10 SDA low-capacitance TVS provision; IEC 61000-4-2 target</t>
         </is>
       </c>
       <c r="G275" t="inlineStr" s="0">
@@ -62349,12 +62349,12 @@
       </c>
       <c r="K275" t="inlineStr" s="0">
         <is>
-          <t>J10 SCL low-capacitance TVS provision; IEC 61000-4-2 target</t>
+          <t>J10 SDA low-capacitance TVS provision; IEC 61000-4-2 target</t>
         </is>
       </c>
       <c r="L275" t="inlineStr" s="0">
         <is>
-          <t>J10 SCL low-capacitance TVS provision; IEC 61000-4-2 target</t>
+          <t>J10 SDA low-capacitance TVS provision; IEC 61000-4-2 target</t>
         </is>
       </c>
       <c r="M275" t="inlineStr" s="0">
@@ -62526,7 +62526,7 @@
     <row r="276">
       <c r="A276" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/D803</t>
+          <t>08_Expansion/D802</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="0">
@@ -62536,7 +62536,7 @@
       </c>
       <c r="C276" t="inlineStr" s="0">
         <is>
-          <t>D803</t>
+          <t>D802</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="0">
@@ -62546,12 +62546,12 @@
       </c>
       <c r="E276" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A POWER</t>
+          <t>OUTSIDE CSR-01A</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="0">
         <is>
-          <t>EXPANSION_VCC local ESD/reverse-injection provision; final part coordinated with Sheet 09</t>
+          <t>J10 SCL low-capacitance TVS provision; IEC 61000-4-2 target</t>
         </is>
       </c>
       <c r="G276" t="inlineStr" s="0">
@@ -62566,32 +62566,32 @@
       </c>
       <c r="I276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="J276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="K276" t="inlineStr" s="0">
         <is>
-          <t>EXPANSION_VCC local ESD/reverse-injection provision; final part coordinated with Sheet 09</t>
+          <t>J10 SCL low-capacitance TVS provision; IEC 61000-4-2 target</t>
         </is>
       </c>
       <c r="L276" t="inlineStr" s="0">
         <is>
-          <t>EXPANSION_VCC local ESD/reverse-injection provision; final part coordinated with Sheet 09</t>
+          <t>J10 SCL low-capacitance TVS provision; IEC 61000-4-2 target</t>
         </is>
       </c>
       <c r="M276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="N276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="O276" t="inlineStr" s="0">
@@ -62611,52 +62611,52 @@
       </c>
       <c r="R276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="S276" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="T276" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="U276" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="V276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="W276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="X276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Y276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Z276" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr" s="0">
         <is>
-          <t>TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
+          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
         </is>
       </c>
       <c r="AB276" t="inlineStr" s="0">
@@ -62696,22 +62696,22 @@
       </c>
       <c r="AI276" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AJ276" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AL276" t="inlineStr" s="0">
         <is>
-          <t>TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
+          <t>Outside current package; do not source or assign a footprint.</t>
         </is>
       </c>
       <c r="AM276" t="inlineStr" s="0">
@@ -62736,7 +62736,7 @@
       </c>
       <c r="AQ276" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AR276" t="inlineStr" s="0">
@@ -62746,14 +62746,14 @@
       </c>
       <c r="AS276" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
+          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/FB801</t>
+          <t>08_Expansion/D803</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="0">
@@ -62763,12 +62763,12 @@
       </c>
       <c r="C277" t="inlineStr" s="0">
         <is>
-          <t>FB801</t>
+          <t>D803</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="0">
         <is>
-          <t>Passives</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="0">
@@ -62778,12 +62778,12 @@
       </c>
       <c r="F277" t="inlineStr" s="0">
         <is>
-          <t>Accessory-bias filter bead — impedance/current rating pending protection part selection</t>
+          <t>EXPANSION_VCC local ESD/reverse-injection provision; final part coordinated with Sheet 09</t>
         </is>
       </c>
       <c r="G277" t="inlineStr" s="0">
         <is>
-          <t>IPC100:FERRITE</t>
+          <t>IPC100:ESD_PROVISION</t>
         </is>
       </c>
       <c r="H277" t="inlineStr" s="0">
@@ -62803,12 +62803,12 @@
       </c>
       <c r="K277" t="inlineStr" s="0">
         <is>
-          <t>Accessory-bias filter bead — impedance/current rating pending protection part selection</t>
+          <t>EXPANSION_VCC local ESD/reverse-injection provision; final part coordinated with Sheet 09</t>
         </is>
       </c>
       <c r="L277" t="inlineStr" s="0">
         <is>
-          <t>Accessory-bias filter bead — impedance/current rating pending protection part selection</t>
+          <t>EXPANSION_VCC local ESD/reverse-injection provision; final part coordinated with Sheet 09</t>
         </is>
       </c>
       <c r="M277" t="inlineStr" s="0">
@@ -62888,7 +62888,7 @@
       </c>
       <c r="AB277" t="inlineStr" s="0">
         <is>
-          <t>Normal</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr" s="0">
@@ -62980,7 +62980,7 @@
     <row r="278">
       <c r="A278" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R801</t>
+          <t>08_Expansion/FB801</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="0">
@@ -62990,7 +62990,7 @@
       </c>
       <c r="C278" t="inlineStr" s="0">
         <is>
-          <t>R801</t>
+          <t>FB801</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="0">
@@ -63005,12 +63005,12 @@
       </c>
       <c r="F278" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ ±1% segment-enable fail-low bias</t>
+          <t>Accessory-bias filter bead — impedance/current rating pending protection part selection</t>
         </is>
       </c>
       <c r="G278" t="inlineStr" s="0">
         <is>
-          <t>IPC100:R</t>
+          <t>IPC100:FERRITE</t>
         </is>
       </c>
       <c r="H278" t="inlineStr" s="0">
@@ -63020,97 +63020,97 @@
       </c>
       <c r="I278" t="inlineStr" s="0">
         <is>
-          <t>Panasonic Industry</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="J278" t="inlineStr" s="0">
         <is>
-          <t>ERJ-3EKF1003V</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="K278" t="inlineStr" s="0">
         <is>
-          <t>100 kÎ© Â±1% 0.1 W AEC-Q200 thick-film chip resistor</t>
+          <t>Accessory-bias filter bead — impedance/current rating pending protection part selection</t>
         </is>
       </c>
       <c r="L278" t="inlineStr" s="0">
         <is>
-          <t>100 kΩ ±1% segment-enable fail-low bias</t>
+          <t>Accessory-bias filter bead — impedance/current rating pending protection part selection</t>
         </is>
       </c>
       <c r="M278" t="inlineStr" s="0">
         <is>
-          <t>0603 (1608 metric)</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="N278" t="inlineStr" s="0">
         <is>
-          <t>Surface mount</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="O278" t="inlineStr" s="0">
         <is>
-          <t>75 V maximum working; 5.25 V maximum applied in reviewed circuits</t>
+          <t>Requires exact-part review</t>
         </is>
       </c>
       <c r="P278" t="inlineStr" s="0">
         <is>
-          <t>52.5 ÂµA at 5.25 V</t>
+          <t>Requires exact-part review</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr" s="0">
         <is>
-          <t>100 kÎ© Â±1%; Â±100 ppm/Â°C; 0.1 W</t>
+          <t>As captured where stated; package/derating unresolved</t>
         </is>
       </c>
       <c r="R278" t="inlineStr" s="0">
         <is>
-          <t>-55 Â°C to +155 Â°C</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="S278" t="inlineStr" s="0">
         <is>
-          <t>ACTIVE â€” checked 2026-07-31</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="T278" t="inlineStr" s="0">
         <is>
-          <t>COMPLIANT â€” manufacturer certificate available</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="U278" t="inlineStr" s="0">
         <is>
-          <t>DigiKey 943,271 in stock; Mouser regional listing over 357,000 in stock; checked 2026-07-31, not guaranteed</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="V278" t="inlineStr" s="0">
         <is>
-          <t>DigiKey</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="W278" t="inlineStr" s="0">
         <is>
-          <t>P100KHTR-ND / P100KHCT-ND</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="X278" t="inlineStr" s="0">
         <is>
-          <t>Mouser</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Y278" t="inlineStr" s="0">
         <is>
-          <t>667-ERJ-3EKF1003V</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Z278" t="inlineStr" s="0">
         <is>
-          <t>Vishay Dale RCG0603100KFKEA â€” ELECTRICALLY APPROVED; footprint confirmation deferred</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr" s="0">
         <is>
-          <t>QER-R-01/02/03/04: 5.25 V / 75 V = 7.0% voltage utilization; 0.276 mW / 100 mW = 0.28% power utilization; Â±1% and Â±100 ppm/Â°C meet general power-bias requirements; -55 to +155 Â°C exceeds environment.</t>
+          <t>TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
         </is>
       </c>
       <c r="AB278" t="inlineStr" s="0">
@@ -63120,62 +63120,62 @@
       </c>
       <c r="AC278" t="inlineStr" s="0">
         <is>
-          <t>0.100</t>
+          <t/>
         </is>
       </c>
       <c r="AD278" t="inlineStr" s="0">
         <is>
-          <t>0.039</t>
+          <t/>
         </is>
       </c>
       <c r="AE278" t="inlineStr" s="0">
         <is>
-          <t>0.0195</t>
+          <t/>
         </is>
       </c>
       <c r="AF278" t="inlineStr" s="0">
         <is>
-          <t>0.01131</t>
+          <t/>
         </is>
       </c>
       <c r="AG278" t="inlineStr" s="0">
         <is>
-          <t>USD</t>
+          <t/>
         </is>
       </c>
       <c r="AH278" t="inlineStr" s="0">
         <is>
-          <t>2026-07-31; DigiKey cut tape</t>
+          <t/>
         </is>
       </c>
       <c r="AI278" t="inlineStr" s="0">
         <is>
-          <t>FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AJ278" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R:QER-R-01,QER-R-02,QER-R-03,QER-R-04,QER-ENV-01</t>
+          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr" s="0">
         <is>
-          <t>LOW</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AL278" t="inlineStr" s="0">
         <is>
-          <t>Low electrical and sourcing risk; do not assign footprint until the footprint package.</t>
+          <t>TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
         </is>
       </c>
       <c r="AM278" t="inlineStr" s="0">
         <is>
-          <t>RCG0603100KFKEA â€” ELECTRICALLY APPROVED; FOOTPRINT MAY DIFFER</t>
+          <t/>
         </is>
       </c>
       <c r="AN278" t="inlineStr" s="0">
         <is>
-          <t>DigiKey 541-1788-1-ND (cut tape)</t>
+          <t/>
         </is>
       </c>
       <c r="AO278" t="inlineStr" s="0">
@@ -63185,12 +63185,12 @@
       </c>
       <c r="AP278" t="inlineStr" s="0">
         <is>
-          <t>https://industrial.panasonic.com/ww/products/pt/general-purpose-chip-resistors/models/ERJ3EKF1003V</t>
+          <t/>
         </is>
       </c>
       <c r="AQ278" t="inlineStr" s="0">
         <is>
-          <t>AOA0000C304; 29-May-2025</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr" s="0">
@@ -63200,14 +63200,14 @@
       </c>
       <c r="AS278" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R frozen exact electrical selection. Preferred and alternate sourcing checked 2026-07-31; stock and pricing are planning snapshots.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R802</t>
+          <t>08_Expansion/R801</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="0">
@@ -63217,7 +63217,7 @@
       </c>
       <c r="C279" t="inlineStr" s="0">
         <is>
-          <t>R802</t>
+          <t>R801</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="0">
@@ -63227,12 +63227,12 @@
       </c>
       <c r="E279" t="inlineStr" s="0">
         <is>
-          <t>OUTSIDE CSR-01A</t>
+          <t>CSR-01A POWER</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="0">
         <is>
-          <t>4.70 kΩ ±1% J10 SDA pull-up; Sheet 08 external-segment owner</t>
+          <t>100 kΩ ±1% segment-enable fail-low bias</t>
         </is>
       </c>
       <c r="G279" t="inlineStr" s="0">
@@ -63247,97 +63247,97 @@
       </c>
       <c r="I279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Panasonic Industry</t>
         </is>
       </c>
       <c r="J279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>ERJ-3EKF1003V</t>
         </is>
       </c>
       <c r="K279" t="inlineStr" s="0">
         <is>
-          <t>4.70 kΩ ±1% J10 SDA pull-up; Sheet 08 external-segment owner</t>
+          <t>100 kÎ© Â±1% 0.1 W AEC-Q200 thick-film chip resistor</t>
         </is>
       </c>
       <c r="L279" t="inlineStr" s="0">
         <is>
-          <t>4.70 kΩ ±1% J10 SDA pull-up; Sheet 08 external-segment owner</t>
+          <t>100 kΩ ±1% segment-enable fail-low bias</t>
         </is>
       </c>
       <c r="M279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>0603 (1608 metric)</t>
         </is>
       </c>
       <c r="N279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Surface mount</t>
         </is>
       </c>
       <c r="O279" t="inlineStr" s="0">
         <is>
-          <t>Requires exact-part review</t>
+          <t>75 V maximum working; 5.25 V maximum applied in reviewed circuits</t>
         </is>
       </c>
       <c r="P279" t="inlineStr" s="0">
         <is>
-          <t>Requires exact-part review</t>
+          <t>52.5 ÂµA at 5.25 V</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr" s="0">
         <is>
-          <t>As captured where stated; package/derating unresolved</t>
+          <t>100 kÎ© Â±1%; Â±100 ppm/Â°C; 0.1 W</t>
         </is>
       </c>
       <c r="R279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>-55 Â°C to +155 Â°C</t>
         </is>
       </c>
       <c r="S279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>ACTIVE â€” checked 2026-07-31</t>
         </is>
       </c>
       <c r="T279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>COMPLIANT â€” manufacturer certificate available</t>
         </is>
       </c>
       <c r="U279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>DigiKey 943,271 in stock; Mouser regional listing over 357,000 in stock; checked 2026-07-31, not guaranteed</t>
         </is>
       </c>
       <c r="V279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>DigiKey</t>
         </is>
       </c>
       <c r="W279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>P100KHTR-ND / P100KHCT-ND</t>
         </is>
       </c>
       <c r="X279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Mouser</t>
         </is>
       </c>
       <c r="Y279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>667-ERJ-3EKF1003V</t>
         </is>
       </c>
       <c r="Z279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Vishay Dale RCG0603100KFKEA â€” ELECTRICALLY APPROVED; footprint confirmation deferred</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr" s="0">
         <is>
-          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+          <t>QER-R-01/02/03/04: 5.25 V / 75 V = 7.0% voltage utilization; 0.276 mW / 100 mW = 0.28% power utilization; Â±1% and Â±100 ppm/Â°C meet general power-bias requirements; -55 to +155 Â°C exceeds environment.</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr" s="0">
@@ -63347,62 +63347,62 @@
       </c>
       <c r="AC279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.100</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.039</t>
         </is>
       </c>
       <c r="AE279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.0195</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>0.01131</t>
         </is>
       </c>
       <c r="AG279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>USD</t>
         </is>
       </c>
       <c r="AH279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-07-31; DigiKey cut tape</t>
         </is>
       </c>
       <c r="AI279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>FROZEN</t>
         </is>
       </c>
       <c r="AJ279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>CSR-01A-R:QER-R-01,QER-R-02,QER-R-03,QER-R-04,QER-ENV-01</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="AL279" t="inlineStr" s="0">
         <is>
-          <t>Outside current package; do not source or assign a footprint.</t>
+          <t>Low electrical and sourcing risk; do not assign footprint until the footprint package.</t>
         </is>
       </c>
       <c r="AM279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>RCG0603100KFKEA â€” ELECTRICALLY APPROVED; FOOTPRINT MAY DIFFER</t>
         </is>
       </c>
       <c r="AN279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>DigiKey 541-1788-1-ND (cut tape)</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr" s="0">
@@ -63412,12 +63412,12 @@
       </c>
       <c r="AP279" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>https://industrial.panasonic.com/ww/products/pt/general-purpose-chip-resistors/models/ERJ3EKF1003V</t>
         </is>
       </c>
       <c r="AQ279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>AOA0000C304; 29-May-2025</t>
         </is>
       </c>
       <c r="AR279" t="inlineStr" s="0">
@@ -63427,14 +63427,14 @@
       </c>
       <c r="AS279" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+          <t>CSR-01A-R frozen exact electrical selection. Preferred and alternate sourcing checked 2026-07-31; stock and pricing are planning snapshots.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R803</t>
+          <t>08_Expansion/R802</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="0">
@@ -63444,7 +63444,7 @@
       </c>
       <c r="C280" t="inlineStr" s="0">
         <is>
-          <t>R803</t>
+          <t>R802</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="0">
@@ -63459,7 +63459,7 @@
       </c>
       <c r="F280" t="inlineStr" s="0">
         <is>
-          <t>4.70 kΩ ±1% J10 SCL pull-up; Sheet 08 external-segment owner</t>
+          <t>4.70 kΩ ±1% J10 SDA pull-up; Sheet 08 external-segment owner</t>
         </is>
       </c>
       <c r="G280" t="inlineStr" s="0">
@@ -63484,12 +63484,12 @@
       </c>
       <c r="K280" t="inlineStr" s="0">
         <is>
-          <t>4.70 kΩ ±1% J10 SCL pull-up; Sheet 08 external-segment owner</t>
+          <t>4.70 kΩ ±1% J10 SDA pull-up; Sheet 08 external-segment owner</t>
         </is>
       </c>
       <c r="L280" t="inlineStr" s="0">
         <is>
-          <t>4.70 kΩ ±1% J10 SCL pull-up; Sheet 08 external-segment owner</t>
+          <t>4.70 kΩ ±1% J10 SDA pull-up; Sheet 08 external-segment owner</t>
         </is>
       </c>
       <c r="M280" t="inlineStr" s="0">
@@ -63661,7 +63661,7 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R804</t>
+          <t>08_Expansion/R803</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="0">
@@ -63671,7 +63671,7 @@
       </c>
       <c r="C281" t="inlineStr" s="0">
         <is>
-          <t>R804</t>
+          <t>R803</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="0">
@@ -63686,7 +63686,7 @@
       </c>
       <c r="F281" t="inlineStr" s="0">
         <is>
-          <t>47 Ω J10 SDA series damping; final 33–100 Ω by SI verification</t>
+          <t>4.70 kΩ ±1% J10 SCL pull-up; Sheet 08 external-segment owner</t>
         </is>
       </c>
       <c r="G281" t="inlineStr" s="0">
@@ -63711,12 +63711,12 @@
       </c>
       <c r="K281" t="inlineStr" s="0">
         <is>
-          <t>47 Ω J10 SDA series damping; final 33–100 Ω by SI verification</t>
+          <t>4.70 kΩ ±1% J10 SCL pull-up; Sheet 08 external-segment owner</t>
         </is>
       </c>
       <c r="L281" t="inlineStr" s="0">
         <is>
-          <t>47 Ω J10 SDA series damping; final 33–100 Ω by SI verification</t>
+          <t>4.70 kΩ ±1% J10 SCL pull-up; Sheet 08 external-segment owner</t>
         </is>
       </c>
       <c r="M281" t="inlineStr" s="0">
@@ -63888,7 +63888,7 @@
     <row r="282">
       <c r="A282" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R805</t>
+          <t>08_Expansion/R804</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="0">
@@ -63898,7 +63898,7 @@
       </c>
       <c r="C282" t="inlineStr" s="0">
         <is>
-          <t>R805</t>
+          <t>R804</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="0">
@@ -63913,7 +63913,7 @@
       </c>
       <c r="F282" t="inlineStr" s="0">
         <is>
-          <t>47 Ω J10 SCL series damping; final 33–100 Ω by SI verification</t>
+          <t>47 Ω J10 SDA series damping; final 33–100 Ω by SI verification</t>
         </is>
       </c>
       <c r="G282" t="inlineStr" s="0">
@@ -63938,12 +63938,12 @@
       </c>
       <c r="K282" t="inlineStr" s="0">
         <is>
-          <t>47 Ω J10 SCL series damping; final 33–100 Ω by SI verification</t>
+          <t>47 Ω J10 SDA series damping; final 33–100 Ω by SI verification</t>
         </is>
       </c>
       <c r="L282" t="inlineStr" s="0">
         <is>
-          <t>47 Ω J10 SCL series damping; final 33–100 Ω by SI verification</t>
+          <t>47 Ω J10 SDA series damping; final 33–100 Ω by SI verification</t>
         </is>
       </c>
       <c r="M282" t="inlineStr" s="0">
@@ -64115,7 +64115,7 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R806</t>
+          <t>08_Expansion/R805</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="0">
@@ -64125,7 +64125,7 @@
       </c>
       <c r="C283" t="inlineStr" s="0">
         <is>
-          <t>R806</t>
+          <t>R805</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="0">
@@ -64135,12 +64135,12 @@
       </c>
       <c r="E283" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A POWER</t>
+          <t>OUTSIDE CSR-01A</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±0.1%, ≤25 ppm/°C — expansion-to-SENSE series resistor</t>
+          <t>47 Ω J10 SCL series damping; final 33–100 Ω by SI verification</t>
         </is>
       </c>
       <c r="G283" t="inlineStr" s="0">
@@ -64155,32 +64155,32 @@
       </c>
       <c r="I283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="J283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="K283" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±0.1%, ≤25 ppm/°C — expansion-to-SENSE series resistor</t>
+          <t>47 Ω J10 SCL series damping; final 33–100 Ω by SI verification</t>
         </is>
       </c>
       <c r="L283" t="inlineStr" s="0">
         <is>
-          <t>150 kΩ ±0.1%, ≤25 ppm/°C — expansion-to-SENSE series resistor</t>
+          <t>47 Ω J10 SCL series damping; final 33–100 Ω by SI verification</t>
         </is>
       </c>
       <c r="M283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="N283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="O283" t="inlineStr" s="0">
@@ -64200,52 +64200,52 @@
       </c>
       <c r="R283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="S283" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="T283" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="U283" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="V283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="W283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="X283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Y283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Z283" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr" s="0">
@@ -64285,22 +64285,22 @@
       </c>
       <c r="AI283" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AJ283" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AL283" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>Outside current package; do not source or assign a footprint.</t>
         </is>
       </c>
       <c r="AM283" t="inlineStr" s="0">
@@ -64325,7 +64325,7 @@
       </c>
       <c r="AQ283" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AR283" t="inlineStr" s="0">
@@ -64335,14 +64335,14 @@
       </c>
       <c r="AS283" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/R808</t>
+          <t>08_Expansion/R806</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="0">
@@ -64352,7 +64352,7 @@
       </c>
       <c r="C284" t="inlineStr" s="0">
         <is>
-          <t>R808</t>
+          <t>R806</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="0">
@@ -64367,7 +64367,7 @@
       </c>
       <c r="F284" t="inlineStr" s="0">
         <is>
-          <t>4.47 MΩ ±0.1%, ≤25 ppm/°C — valid-output hysteresis feedback</t>
+          <t>150 kÎ© Â±0.1%, â‰¤25 ppm/Â°C - expansion-to-SENSE upper divider</t>
         </is>
       </c>
       <c r="G284" t="inlineStr" s="0">
@@ -64392,12 +64392,12 @@
       </c>
       <c r="K284" t="inlineStr" s="0">
         <is>
-          <t>4.47 MΩ ±0.1%, ≤25 ppm/°C — valid-output hysteresis feedback</t>
+          <t>150 kÎ© Â±0.1%, â‰¤25 ppm/Â°C - expansion-to-SENSE upper divider</t>
         </is>
       </c>
       <c r="L284" t="inlineStr" s="0">
         <is>
-          <t>4.47 MΩ ±0.1%, ≤25 ppm/°C — valid-output hysteresis feedback</t>
+          <t>150 kÎ© Â±0.1%, â‰¤25 ppm/Â°C - expansion-to-SENSE upper divider</t>
         </is>
       </c>
       <c r="M284" t="inlineStr" s="0">
@@ -64472,7 +64472,7 @@
       </c>
       <c r="AA284" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U801 threshold/hysteresis/leakage full tolerance stack.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
         </is>
       </c>
       <c r="AB284" t="inlineStr" s="0">
@@ -64517,44 +64517,44 @@
       </c>
       <c r="AJ284" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R; QER-01; PPQ-01; PPQ-02</t>
+          <t>ECO-010; PACS-01R</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr" s="0">
         <is>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+        </is>
+      </c>
+      <c r="AL284" t="inlineStr" s="0">
+        <is>
+          <t>ANALYSIS INCOMPLETE - ECO-007 threshold-network evidence superseded by ECO-010; exact passive selection and PACS-01R system revalidation remain required.</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN284" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr" s="0">
+        <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="AL284" t="inlineStr" s="0">
-        <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U801 threshold/hysteresis/leakage full tolerance stack.</t>
-        </is>
-      </c>
-      <c r="AM284" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN284" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO284" t="inlineStr" s="0">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AP284" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ284" t="inlineStr" s="0">
-        <is>
-          <t>PAS-01R evidence review 2026-07-31</t>
-        </is>
-      </c>
       <c r="AR284" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
@@ -64562,14 +64562,14 @@
       </c>
       <c r="AS284" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U801 threshold/hysteresis/leakage full tolerance stack.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 threshold-network evidence superseded by ECO-010; exact passive selection and PACS-01R system revalidation remain required.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP801</t>
+          <t>08_Expansion/R807</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="0">
@@ -64579,27 +64579,27 @@
       </c>
       <c r="C285" t="inlineStr" s="0">
         <is>
-          <t>TP801</t>
+          <t>R807</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="0">
         <is>
-          <t>Test</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="0">
         <is>
-          <t>OUTSIDE CSR-01A</t>
+          <t>CSR-01A POWER</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="0">
         <is>
-          <t>EXPANSION_VCC DFT</t>
+          <t>31.6 kÎ© Â±0.1%, â‰¤25 ppm/Â°C - TPS3899 SENSE lower divider</t>
         </is>
       </c>
       <c r="G285" t="inlineStr" s="0">
         <is>
-          <t>IPC100:TEST_NODE</t>
+          <t>IPC100:R</t>
         </is>
       </c>
       <c r="H285" t="inlineStr" s="0">
@@ -64609,32 +64609,32 @@
       </c>
       <c r="I285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - PACS-01R</t>
         </is>
       </c>
       <c r="J285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - PACS-01R</t>
         </is>
       </c>
       <c r="K285" t="inlineStr" s="0">
         <is>
-          <t>EXPANSION_VCC DFT</t>
+          <t>31.6 kÎ© Â±0.1%, â‰¤25 ppm/Â°C - TPS3899 SENSE lower divider</t>
         </is>
       </c>
       <c r="L285" t="inlineStr" s="0">
         <is>
-          <t>EXPANSION_VCC DFT</t>
+          <t>31.6 kÎ© Â±0.1%, â‰¤25 ppm/Â°C - TPS3899 SENSE lower divider</t>
         </is>
       </c>
       <c r="M285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - NO FOOTPRINT ASSIGNED</t>
         </is>
       </c>
       <c r="N285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="O285" t="inlineStr" s="0">
@@ -64654,52 +64654,52 @@
       </c>
       <c r="R285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="S285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="T285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="U285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="V285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="W285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="X285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Y285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Z285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr" s="0">
         <is>
-          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
         </is>
       </c>
       <c r="AB285" t="inlineStr" s="0">
@@ -64739,22 +64739,22 @@
       </c>
       <c r="AI285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AJ285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>ECO-010; PACS-01R</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL285" t="inlineStr" s="0">
         <is>
-          <t>Outside current package; do not source or assign a footprint.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
         </is>
       </c>
       <c r="AM285" t="inlineStr" s="0">
@@ -64779,7 +64779,7 @@
       </c>
       <c r="AQ285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AR285" t="inlineStr" s="0">
@@ -64789,14 +64789,14 @@
       </c>
       <c r="AS285" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP802</t>
+          <t>08_Expansion/R808</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="0">
@@ -64806,27 +64806,27 @@
       </c>
       <c r="C286" t="inlineStr" s="0">
         <is>
-          <t>TP802</t>
+          <t>R808</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="0">
         <is>
-          <t>Test</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="0">
         <is>
-          <t>OUTSIDE CSR-01A</t>
+          <t>CSR-01A POWER</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="0">
         <is>
-          <t>SEGMENT_ENABLE DFT</t>
+          <t>1.30 MÎ© Â±0.1%, â‰¤25 ppm/Â°C - output-to-SENSE feedback</t>
         </is>
       </c>
       <c r="G286" t="inlineStr" s="0">
         <is>
-          <t>IPC100:TEST_NODE</t>
+          <t>IPC100:R</t>
         </is>
       </c>
       <c r="H286" t="inlineStr" s="0">
@@ -64836,32 +64836,32 @@
       </c>
       <c r="I286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="J286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="K286" t="inlineStr" s="0">
         <is>
-          <t>SEGMENT_ENABLE DFT</t>
+          <t>1.30 MÎ© Â±0.1%, â‰¤25 ppm/Â°C - output-to-SENSE feedback</t>
         </is>
       </c>
       <c r="L286" t="inlineStr" s="0">
         <is>
-          <t>SEGMENT_ENABLE DFT</t>
+          <t>1.30 MÎ© Â±0.1%, â‰¤25 ppm/Â°C - output-to-SENSE feedback</t>
         </is>
       </c>
       <c r="M286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="N286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="O286" t="inlineStr" s="0">
@@ -64881,52 +64881,52 @@
       </c>
       <c r="R286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="S286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="T286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="U286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="V286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="W286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="X286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Y286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Z286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr" s="0">
         <is>
-          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U801 threshold/hysteresis/leakage full tolerance stack.</t>
         </is>
       </c>
       <c r="AB286" t="inlineStr" s="0">
@@ -64966,22 +64966,22 @@
       </c>
       <c r="AI286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AJ286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>ECO-010; PACS-01R</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL286" t="inlineStr" s="0">
         <is>
-          <t>Outside current package; do not source or assign a footprint.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
         </is>
       </c>
       <c r="AM286" t="inlineStr" s="0">
@@ -65006,7 +65006,7 @@
       </c>
       <c r="AQ286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>PAS-01R evidence review 2026-07-31</t>
         </is>
       </c>
       <c r="AR286" t="inlineStr" s="0">
@@ -65016,14 +65016,14 @@
       </c>
       <c r="AS286" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP803</t>
+          <t>08_Expansion/R809</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="0">
@@ -65033,27 +65033,27 @@
       </c>
       <c r="C287" t="inlineStr" s="0">
         <is>
-          <t>TP803</t>
+          <t>R809</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="0">
         <is>
-          <t>Test</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="0">
         <is>
-          <t>OUTSIDE CSR-01A</t>
+          <t>CSR-01A POWER</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="0">
         <is>
-          <t>INTERNAL SDA DFT</t>
+          <t>4.70 kÎ© Â±1% - TPS3899 output pull-up</t>
         </is>
       </c>
       <c r="G287" t="inlineStr" s="0">
         <is>
-          <t>IPC100:TEST_NODE</t>
+          <t>IPC100:R</t>
         </is>
       </c>
       <c r="H287" t="inlineStr" s="0">
@@ -65063,32 +65063,32 @@
       </c>
       <c r="I287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - PACS-01R</t>
         </is>
       </c>
       <c r="J287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - PACS-01R</t>
         </is>
       </c>
       <c r="K287" t="inlineStr" s="0">
         <is>
-          <t>INTERNAL SDA DFT</t>
+          <t>4.70 kÎ© Â±1% - TPS3899 output pull-up</t>
         </is>
       </c>
       <c r="L287" t="inlineStr" s="0">
         <is>
-          <t>INTERNAL SDA DFT</t>
+          <t>4.70 kÎ© Â±1% - TPS3899 output pull-up</t>
         </is>
       </c>
       <c r="M287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - NO FOOTPRINT ASSIGNED</t>
         </is>
       </c>
       <c r="N287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="O287" t="inlineStr" s="0">
@@ -65108,52 +65108,52 @@
       </c>
       <c r="R287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="S287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="T287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="U287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="V287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="W287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="X287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Y287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Z287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr" s="0">
         <is>
-          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
         </is>
       </c>
       <c r="AB287" t="inlineStr" s="0">
@@ -65193,22 +65193,22 @@
       </c>
       <c r="AI287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AJ287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>ECO-010; PACS-01R</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL287" t="inlineStr" s="0">
         <is>
-          <t>Outside current package; do not source or assign a footprint.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
         </is>
       </c>
       <c r="AM287" t="inlineStr" s="0">
@@ -65233,7 +65233,7 @@
       </c>
       <c r="AQ287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AR287" t="inlineStr" s="0">
@@ -65243,14 +65243,14 @@
       </c>
       <c r="AS287" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP804</t>
+          <t>08_Expansion/TP801</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="0">
@@ -65260,7 +65260,7 @@
       </c>
       <c r="C288" t="inlineStr" s="0">
         <is>
-          <t>TP804</t>
+          <t>TP801</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="0">
@@ -65275,7 +65275,7 @@
       </c>
       <c r="F288" t="inlineStr" s="0">
         <is>
-          <t>INTERNAL SCL DFT</t>
+          <t>EXPANSION_VCC DFT</t>
         </is>
       </c>
       <c r="G288" t="inlineStr" s="0">
@@ -65300,12 +65300,12 @@
       </c>
       <c r="K288" t="inlineStr" s="0">
         <is>
-          <t>INTERNAL SCL DFT</t>
+          <t>EXPANSION_VCC DFT</t>
         </is>
       </c>
       <c r="L288" t="inlineStr" s="0">
         <is>
-          <t>INTERNAL SCL DFT</t>
+          <t>EXPANSION_VCC DFT</t>
         </is>
       </c>
       <c r="M288" t="inlineStr" s="0">
@@ -65477,7 +65477,7 @@
     <row r="289">
       <c r="A289" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP805</t>
+          <t>08_Expansion/TP802</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="0">
@@ -65487,7 +65487,7 @@
       </c>
       <c r="C289" t="inlineStr" s="0">
         <is>
-          <t>TP805</t>
+          <t>TP802</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="0">
@@ -65502,7 +65502,7 @@
       </c>
       <c r="F289" t="inlineStr" s="0">
         <is>
-          <t>J10 SDA DFT</t>
+          <t>SEGMENT_ENABLE DFT</t>
         </is>
       </c>
       <c r="G289" t="inlineStr" s="0">
@@ -65527,12 +65527,12 @@
       </c>
       <c r="K289" t="inlineStr" s="0">
         <is>
-          <t>J10 SDA DFT</t>
+          <t>SEGMENT_ENABLE DFT</t>
         </is>
       </c>
       <c r="L289" t="inlineStr" s="0">
         <is>
-          <t>J10 SDA DFT</t>
+          <t>SEGMENT_ENABLE DFT</t>
         </is>
       </c>
       <c r="M289" t="inlineStr" s="0">
@@ -65704,7 +65704,7 @@
     <row r="290">
       <c r="A290" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/TP806</t>
+          <t>08_Expansion/TP803</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="0">
@@ -65714,7 +65714,7 @@
       </c>
       <c r="C290" t="inlineStr" s="0">
         <is>
-          <t>TP806</t>
+          <t>TP803</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="0">
@@ -65729,7 +65729,7 @@
       </c>
       <c r="F290" t="inlineStr" s="0">
         <is>
-          <t>J10 SCL DFT</t>
+          <t>INTERNAL SDA DFT</t>
         </is>
       </c>
       <c r="G290" t="inlineStr" s="0">
@@ -65754,12 +65754,12 @@
       </c>
       <c r="K290" t="inlineStr" s="0">
         <is>
-          <t>J10 SCL DFT</t>
+          <t>INTERNAL SDA DFT</t>
         </is>
       </c>
       <c r="L290" t="inlineStr" s="0">
         <is>
-          <t>J10 SCL DFT</t>
+          <t>INTERNAL SDA DFT</t>
         </is>
       </c>
       <c r="M290" t="inlineStr" s="0">
@@ -65931,7 +65931,7 @@
     <row r="291">
       <c r="A291" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/U801</t>
+          <t>08_Expansion/TP804</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="0">
@@ -65941,27 +65941,27 @@
       </c>
       <c r="C291" t="inlineStr" s="0">
         <is>
-          <t>U801</t>
+          <t>TP804</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="0">
         <is>
-          <t>Logic</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A POWER</t>
+          <t>OUTSIDE CSR-01A</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="0">
         <is>
-          <t>TLV841S fixed 2.7 V; 10 ms delay; push-pull valid-high; external 2.930/2.680 V thresholds</t>
+          <t>INTERNAL SCL DFT</t>
         </is>
       </c>
       <c r="G291" t="inlineStr" s="0">
         <is>
-          <t>IPC100:TLV841S_2V7_VALID_HIGH</t>
+          <t>IPC100:TEST_NODE</t>
         </is>
       </c>
       <c r="H291" t="inlineStr" s="0">
@@ -65971,32 +65971,32 @@
       </c>
       <c r="I291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - PACS-01 BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="J291" t="inlineStr" s="0">
         <is>
-          <t>NO ACTIVE ORDERABLE TLV841SCPH27YBHR FOUND</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="K291" t="inlineStr" s="0">
         <is>
-          <t>TLV841S fixed 2.7 V; 10 ms delay; push-pull valid-high; external 2.930/2.680 V thresholds</t>
+          <t>INTERNAL SCL DFT</t>
         </is>
       </c>
       <c r="L291" t="inlineStr" s="0">
         <is>
-          <t>TLV841S fixed 2.7 V; 10 ms delay; push-pull valid-high; external 2.930/2.680 V thresholds</t>
+          <t>INTERNAL SCL DFT</t>
         </is>
       </c>
       <c r="M291" t="inlineStr" s="0">
         <is>
-          <t>Required DSBGA-4 YBH combination not listed as production OPN</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="N291" t="inlineStr" s="0">
         <is>
-          <t>Surface mount; footprint not assigned</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="O291" t="inlineStr" s="0">
@@ -66016,57 +66016,57 @@
       </c>
       <c r="R291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="S291" t="inlineStr" s="0">
         <is>
-          <t>NOT ORDERABLE / UNRESOLVED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="T291" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="U291" t="inlineStr" s="0">
         <is>
-          <t>UNAVAILABLE / UNRESOLVED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="V291" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="W291" t="inlineStr" s="0">
         <is>
-          <t>NO ACTIVE ORDERABLE TLV841SCPH27YBHR FOUND</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="X291" t="inlineStr" s="0">
         <is>
-          <t>Functional alternate only</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Y291" t="inlineStr" s="0">
         <is>
-          <t>Architecture-compatible alternate not demonstrated</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Z291" t="inlineStr" s="0">
         <is>
-          <t>No approved drop-in second source</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
+          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
         </is>
       </c>
       <c r="AB291" t="inlineStr" s="0">
         <is>
-          <t>Major</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr" s="0">
@@ -66101,27 +66101,27 @@
       </c>
       <c r="AI291" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AJ291" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01 NOT ACCEPTED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AL291" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 BLOCKED - NO ACTIVE ORDERABLE TLV841SCPH27YBHR FOUND. No active-device freeze.</t>
+          <t>Outside current package; do not source or assign a footprint.</t>
         </is>
       </c>
       <c r="AM291" t="inlineStr" s="0">
         <is>
-          <t>Architecture-compatible alternate not demonstrated</t>
+          <t/>
         </is>
       </c>
       <c r="AN291" t="inlineStr" s="0">
@@ -66141,7 +66141,7 @@
       </c>
       <c r="AQ291" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AR291" t="inlineStr" s="0">
@@ -66151,14 +66151,14 @@
       </c>
       <c r="AS291" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 BLOCKED - NO ACTIVE ORDERABLE TLV841SCPH27YBHR FOUND. No active-device freeze.</t>
+          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr" s="0">
         <is>
-          <t>08_Expansion/U802</t>
+          <t>08_Expansion/TP805</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="0">
@@ -66168,12 +66168,12 @@
       </c>
       <c r="C292" t="inlineStr" s="0">
         <is>
-          <t>U802</t>
+          <t>TP805</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="0">
         <is>
-          <t>I2C</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="0">
@@ -66183,12 +66183,12 @@
       </c>
       <c r="F292" t="inlineStr" s="0">
         <is>
-          <t>Dual-supply I2C hot-swap buffer; 100 kHz; fail-disabled; no clock stretching</t>
+          <t>J10 SDA DFT</t>
         </is>
       </c>
       <c r="G292" t="inlineStr" s="0">
         <is>
-          <t>IPC100:I2C_SEGMENT_BUFFER</t>
+          <t>IPC100:TEST_NODE</t>
         </is>
       </c>
       <c r="H292" t="inlineStr" s="0">
@@ -66208,12 +66208,12 @@
       </c>
       <c r="K292" t="inlineStr" s="0">
         <is>
-          <t>Dual-supply I2C hot-swap buffer; 100 kHz; fail-disabled; no clock stretching</t>
+          <t>J10 SDA DFT</t>
         </is>
       </c>
       <c r="L292" t="inlineStr" s="0">
         <is>
-          <t>Dual-supply I2C hot-swap buffer; 100 kHz; fail-disabled; no clock stretching</t>
+          <t>J10 SDA DFT</t>
         </is>
       </c>
       <c r="M292" t="inlineStr" s="0">
@@ -66385,22 +66385,22 @@
     <row r="293">
       <c r="A293" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/C901</t>
+          <t>08_Expansion/TP806</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test</t>
+          <t>08_Expansion</t>
         </is>
       </c>
       <c r="C293" t="inlineStr" s="0">
         <is>
-          <t>C901</t>
+          <t>TP806</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="0">
         <is>
-          <t>Passives</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="0">
@@ -66410,12 +66410,12 @@
       </c>
       <c r="F293" t="inlineStr" s="0">
         <is>
-          <t>DNP 1 nF &gt;=1 kV shield coupling option</t>
+          <t>J10 SCL DFT</t>
         </is>
       </c>
       <c r="G293" t="inlineStr" s="0">
         <is>
-          <t>IPC100:C</t>
+          <t>IPC100:TEST_NODE</t>
         </is>
       </c>
       <c r="H293" t="inlineStr" s="0">
@@ -66435,12 +66435,12 @@
       </c>
       <c r="K293" t="inlineStr" s="0">
         <is>
-          <t>DNP 1 nF &gt;=1 kV shield coupling option</t>
+          <t>J10 SCL DFT</t>
         </is>
       </c>
       <c r="L293" t="inlineStr" s="0">
         <is>
-          <t>DNP 1 nF &gt;=1 kV shield coupling option</t>
+          <t>J10 SCL DFT</t>
         </is>
       </c>
       <c r="M293" t="inlineStr" s="0">
@@ -66612,37 +66612,37 @@
     <row r="294">
       <c r="A294" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/D901</t>
+          <t>08_Expansion/U801</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test</t>
+          <t>08_Expansion</t>
         </is>
       </c>
       <c r="C294" t="inlineStr" s="0">
         <is>
-          <t>D901</t>
+          <t>U801</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="0">
         <is>
-          <t>Protection</t>
+          <t>Logic</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="0">
         <is>
-          <t>OUTSIDE CSR-01A</t>
+          <t>CSR-01A POWER</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="0">
         <is>
-          <t>USB2 ESD: &gt;=5.5V, IEC 61000-4-2, &lt;=1pF/ch, &lt;=100nA</t>
+          <t>TPS3899DL01 adjustable supervisor; OD active-low; external 2.9/2.7 V network; 6.2 ms</t>
         </is>
       </c>
       <c r="G294" t="inlineStr" s="0">
         <is>
-          <t>IPC100:USB_ESD2</t>
+          <t>IPC100:TPS3899DL01</t>
         </is>
       </c>
       <c r="H294" t="inlineStr" s="0">
@@ -66652,32 +66652,32 @@
       </c>
       <c r="I294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="J294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>TPS3899DL01DSER</t>
         </is>
       </c>
       <c r="K294" t="inlineStr" s="0">
         <is>
-          <t>USB2 ESD: &gt;=5.5V, IEC 61000-4-2, &lt;=1pF/ch, &lt;=100nA</t>
+          <t>TPS3899DL01 adjustable supervisor; OD active-low; external 2.9/2.7 V network; 6.2 ms</t>
         </is>
       </c>
       <c r="L294" t="inlineStr" s="0">
         <is>
-          <t>USB2 ESD: &gt;=5.5V, IEC 61000-4-2, &lt;=1pF/ch, &lt;=100nA</t>
+          <t>TPS3899DL01 adjustable supervisor; OD active-low; external 2.9/2.7 V network; 6.2 ms</t>
         </is>
       </c>
       <c r="M294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>WSON-6 DSE; footprint not assigned</t>
         </is>
       </c>
       <c r="N294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Surface mount; footprint not assigned</t>
         </is>
       </c>
       <c r="O294" t="inlineStr" s="0">
@@ -66697,52 +66697,52 @@
       </c>
       <c r="R294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="S294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>ACTIVE - TI review 2026-07-31</t>
         </is>
       </c>
       <c r="T294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="U294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Orderable; stock requires PO revalidation</t>
         </is>
       </c>
       <c r="V294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="W294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>TPS3899DL01DSER</t>
         </is>
       </c>
       <c r="X294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Functional alternate only</t>
         </is>
       </c>
       <c r="Y294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>Architecture-compatible alternate not demonstrated</t>
         </is>
       </c>
       <c r="Z294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>No approved drop-in second source</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr" s="0">
         <is>
-          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 physically implemented the fixed 2.7 V, 10 ms supervisor and external 2.930/2.680 V threshold network; exact suffix tolerance, leakage, package, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work.</t>
         </is>
       </c>
       <c r="AB294" t="inlineStr" s="0">
@@ -66782,27 +66782,27 @@
       </c>
       <c r="AI294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AJ294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>ECO-010; PACS-01R</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
         </is>
       </c>
       <c r="AL294" t="inlineStr" s="0">
         <is>
-          <t>Outside current package; do not source or assign a footprint.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release.</t>
         </is>
       </c>
       <c r="AM294" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Architecture-compatible alternate not demonstrated</t>
         </is>
       </c>
       <c r="AN294" t="inlineStr" s="0">
@@ -66822,7 +66822,7 @@
       </c>
       <c r="AQ294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AR294" t="inlineStr" s="0">
@@ -66832,44 +66832,44 @@
       </c>
       <c r="AS294" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/D902</t>
+          <t>08_Expansion/U802</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test</t>
+          <t>08_Expansion</t>
         </is>
       </c>
       <c r="C295" t="inlineStr" s="0">
         <is>
-          <t>D902</t>
+          <t>U802</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="0">
         <is>
-          <t>Protection</t>
+          <t>I2C</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A POWER</t>
+          <t>OUTSIDE CSR-01A</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="0">
         <is>
-          <t>VBUS ESD: 5V working, IEC 61000-4-2; no PD voltage assumed</t>
+          <t>Dual-supply I2C hot-swap buffer; 100 kHz; fail-disabled; no clock stretching</t>
         </is>
       </c>
       <c r="G295" t="inlineStr" s="0">
         <is>
-          <t>IPC100:VBUS_ESD</t>
+          <t>IPC100:I2C_SEGMENT_BUFFER</t>
         </is>
       </c>
       <c r="H295" t="inlineStr" s="0">
@@ -66879,32 +66879,32 @@
       </c>
       <c r="I295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="J295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="K295" t="inlineStr" s="0">
         <is>
-          <t>VBUS ESD: 5V working, IEC 61000-4-2; no PD voltage assumed</t>
+          <t>Dual-supply I2C hot-swap buffer; 100 kHz; fail-disabled; no clock stretching</t>
         </is>
       </c>
       <c r="L295" t="inlineStr" s="0">
         <is>
-          <t>VBUS ESD: 5V working, IEC 61000-4-2; no PD voltage assumed</t>
+          <t>Dual-supply I2C hot-swap buffer; 100 kHz; fail-disabled; no clock stretching</t>
         </is>
       </c>
       <c r="M295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="N295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="O295" t="inlineStr" s="0">
@@ -66924,57 +66924,57 @@
       </c>
       <c r="R295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="S295" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="T295" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="U295" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="V295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="W295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="X295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Y295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Z295" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr" s="0">
         <is>
-          <t>TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
+          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr" s="0">
         <is>
-          <t>Major</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr" s="0">
@@ -67009,22 +67009,22 @@
       </c>
       <c r="AI295" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AJ295" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AL295" t="inlineStr" s="0">
         <is>
-          <t>TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
+          <t>Outside current package; do not source or assign a footprint.</t>
         </is>
       </c>
       <c r="AM295" t="inlineStr" s="0">
@@ -67049,7 +67049,7 @@
       </c>
       <c r="AQ295" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AR295" t="inlineStr" s="0">
@@ -67059,14 +67059,14 @@
       </c>
       <c r="AS295" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
+          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/DFT1</t>
+          <t>09_Connectors_Test/C901</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="0">
@@ -67076,12 +67076,12 @@
       </c>
       <c r="C296" t="inlineStr" s="0">
         <is>
-          <t>DFT1</t>
+          <t>C901</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="0">
         <is>
-          <t>Test</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="0">
@@ -67091,12 +67091,12 @@
       </c>
       <c r="F296" t="inlineStr" s="0">
         <is>
-          <t>T1 factory pogo logical boundary; not populated</t>
+          <t>DNP 1 nF &gt;=1 kV shield coupling option</t>
         </is>
       </c>
       <c r="G296" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN6</t>
+          <t>IPC100:C</t>
         </is>
       </c>
       <c r="H296" t="inlineStr" s="0">
@@ -67116,12 +67116,12 @@
       </c>
       <c r="K296" t="inlineStr" s="0">
         <is>
-          <t>T1 factory pogo logical boundary; not populated</t>
+          <t>DNP 1 nF &gt;=1 kV shield coupling option</t>
         </is>
       </c>
       <c r="L296" t="inlineStr" s="0">
         <is>
-          <t>T1 factory pogo logical boundary; not populated</t>
+          <t>DNP 1 nF &gt;=1 kV shield coupling option</t>
         </is>
       </c>
       <c r="M296" t="inlineStr" s="0">
@@ -67293,7 +67293,7 @@
     <row r="297">
       <c r="A297" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J1</t>
+          <t>09_Connectors_Test/D901</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="0">
@@ -67303,27 +67303,27 @@
       </c>
       <c r="C297" t="inlineStr" s="0">
         <is>
-          <t>J1</t>
+          <t>D901</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="0">
         <is>
-          <t>Connectors</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A POWER</t>
+          <t>OUTSIDE CSR-01A</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="0">
         <is>
-          <t>P1/H01 controller input</t>
+          <t>USB2 ESD: &gt;=5.5V, IEC 61000-4-2, &lt;=1pF/ch, &lt;=100nA</t>
         </is>
       </c>
       <c r="G297" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN2</t>
+          <t>IPC100:USB_ESD2</t>
         </is>
       </c>
       <c r="H297" t="inlineStr" s="0">
@@ -67333,32 +67333,32 @@
       </c>
       <c r="I297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="J297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="K297" t="inlineStr" s="0">
         <is>
-          <t>P1/H01 controller input</t>
+          <t>USB2 ESD: &gt;=5.5V, IEC 61000-4-2, &lt;=1pF/ch, &lt;=100nA</t>
         </is>
       </c>
       <c r="L297" t="inlineStr" s="0">
         <is>
-          <t>P1/H01 controller input</t>
+          <t>USB2 ESD: &gt;=5.5V, IEC 61000-4-2, &lt;=1pF/ch, &lt;=100nA</t>
         </is>
       </c>
       <c r="M297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="N297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="O297" t="inlineStr" s="0">
@@ -67378,52 +67378,52 @@
       </c>
       <c r="R297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="S297" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="T297" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="U297" t="inlineStr" s="0">
         <is>
-          <t>NOT REVIEWED - BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="V297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="W297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="X297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Y297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="Z297" t="inlineStr" s="0">
         <is>
-          <t>UNRESOLVED - CSR-01A BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” MIR-01 released the physical interface, but housing/header/contact/tool order codes and qualification evidence were not frozen because CSR-01A-R2 stopped on electrical-network conflicts.</t>
+          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr" s="0">
@@ -67463,22 +67463,22 @@
       </c>
       <c r="AI297" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AJ297" t="inlineStr" s="0">
         <is>
-          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AL297" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” MIR-01 released the physical interface, but housing/header/contact/tool order codes and qualification evidence were not frozen because CSR-01A-R2 stopped on electrical-network conflicts.</t>
+          <t>Outside current package; do not source or assign a footprint.</t>
         </is>
       </c>
       <c r="AM297" t="inlineStr" s="0">
@@ -67503,7 +67503,7 @@
       </c>
       <c r="AQ297" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED</t>
+          <t>NOT YET FROZEN</t>
         </is>
       </c>
       <c r="AR297" t="inlineStr" s="0">
@@ -67513,14 +67513,14 @@
       </c>
       <c r="AS297" t="inlineStr" s="0">
         <is>
-          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” MIR-01 released the physical interface, but housing/header/contact/tool order codes and qualification evidence were not frozen because CSR-01A-R2 stopped on electrical-network conflicts.</t>
+          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J10</t>
+          <t>09_Connectors_Test/D902</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="0">
@@ -67530,27 +67530,27 @@
       </c>
       <c r="C298" t="inlineStr" s="0">
         <is>
-          <t>J10</t>
+          <t>D902</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="0">
         <is>
-          <t>Connectors</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="0">
         <is>
-          <t>OUTSIDE CSR-01A</t>
+          <t>CSR-01A POWER</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="0">
         <is>
-          <t>D1/H10 ICD-001 optional DNP; no live mate</t>
+          <t>VBUS ESD: 5V working, IEC 61000-4-2; no PD voltage assumed</t>
         </is>
       </c>
       <c r="G298" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN4</t>
+          <t>IPC100:VBUS_ESD</t>
         </is>
       </c>
       <c r="H298" t="inlineStr" s="0">
@@ -67560,32 +67560,32 @@
       </c>
       <c r="I298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="J298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="K298" t="inlineStr" s="0">
         <is>
-          <t>D1/H10 ICD-001 optional DNP; no live mate</t>
+          <t>VBUS ESD: 5V working, IEC 61000-4-2; no PD voltage assumed</t>
         </is>
       </c>
       <c r="L298" t="inlineStr" s="0">
         <is>
-          <t>D1/H10 ICD-001 optional DNP; no live mate</t>
+          <t>VBUS ESD: 5V working, IEC 61000-4-2; no PD voltage assumed</t>
         </is>
       </c>
       <c r="M298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="N298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="O298" t="inlineStr" s="0">
@@ -67605,52 +67605,52 @@
       </c>
       <c r="R298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="S298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="T298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="U298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="V298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="W298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="X298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Y298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Z298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr" s="0">
         <is>
-          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+          <t>TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr" s="0">
@@ -67690,22 +67690,22 @@
       </c>
       <c r="AI298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AJ298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AL298" t="inlineStr" s="0">
         <is>
-          <t>Outside current package; do not source or assign a footprint.</t>
+          <t>TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
         </is>
       </c>
       <c r="AM298" t="inlineStr" s="0">
@@ -67730,7 +67730,7 @@
       </c>
       <c r="AQ298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AR298" t="inlineStr" s="0">
@@ -67740,14 +67740,14 @@
       </c>
       <c r="AS298" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. TRANSIENT COORDINATION UNRESOLVED â€” clamp/current/energy/leakage/fault coordination and exact manufacturer evidence are incomplete.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J13</t>
+          <t>09_Connectors_Test/DFT1</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="0">
@@ -67757,12 +67757,12 @@
       </c>
       <c r="C299" t="inlineStr" s="0">
         <is>
-          <t>J13</t>
+          <t>DFT1</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="0">
         <is>
-          <t>Connectors</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="0">
@@ -67772,12 +67772,12 @@
       </c>
       <c r="F299" t="inlineStr" s="0">
         <is>
-          <t>U1/H13 USB2 device-UFP; full 24 contacts + shell</t>
+          <t>T1 factory pogo logical boundary; not populated</t>
         </is>
       </c>
       <c r="G299" t="inlineStr" s="0">
         <is>
-          <t>IPC100:USB_C_UFP_FULL</t>
+          <t>IPC100:CONN6</t>
         </is>
       </c>
       <c r="H299" t="inlineStr" s="0">
@@ -67797,12 +67797,12 @@
       </c>
       <c r="K299" t="inlineStr" s="0">
         <is>
-          <t>U1/H13 USB2 device-UFP; full 24 contacts + shell</t>
+          <t>T1 factory pogo logical boundary; not populated</t>
         </is>
       </c>
       <c r="L299" t="inlineStr" s="0">
         <is>
-          <t>U1/H13 USB2 device-UFP; full 24 contacts + shell</t>
+          <t>T1 factory pogo logical boundary; not populated</t>
         </is>
       </c>
       <c r="M299" t="inlineStr" s="0">
@@ -67882,7 +67882,7 @@
       </c>
       <c r="AB299" t="inlineStr" s="0">
         <is>
-          <t>Major</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr" s="0">
@@ -67974,7 +67974,7 @@
     <row r="300">
       <c r="A300" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J2</t>
+          <t>09_Connectors_Test/J1</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="0">
@@ -67984,7 +67984,7 @@
       </c>
       <c r="C300" t="inlineStr" s="0">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="0">
@@ -67994,17 +67994,17 @@
       </c>
       <c r="E300" t="inlineStr" s="0">
         <is>
-          <t>OUTSIDE CSR-01A</t>
+          <t>CSR-01A POWER</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="0">
         <is>
-          <t>M1/H02 Axis 1 logic</t>
+          <t>P1/H01 controller input</t>
         </is>
       </c>
       <c r="G300" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN6</t>
+          <t>IPC100:CONN2</t>
         </is>
       </c>
       <c r="H300" t="inlineStr" s="0">
@@ -68014,32 +68014,32 @@
       </c>
       <c r="I300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="J300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="K300" t="inlineStr" s="0">
         <is>
-          <t>M1/H02 Axis 1 logic</t>
+          <t>P1/H01 controller input</t>
         </is>
       </c>
       <c r="L300" t="inlineStr" s="0">
         <is>
-          <t>M1/H02 Axis 1 logic</t>
+          <t>P1/H01 controller input</t>
         </is>
       </c>
       <c r="M300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="N300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="O300" t="inlineStr" s="0">
@@ -68059,52 +68059,52 @@
       </c>
       <c r="R300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="S300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="T300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="U300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>NOT REVIEWED - BLOCKED</t>
         </is>
       </c>
       <c r="V300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="W300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="X300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Y300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="Z300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>UNRESOLVED - CSR-01A BLOCKED</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr" s="0">
         <is>
-          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+          <t>ANALYSIS INCOMPLETE â€” MIR-01 released the physical interface, but housing/header/contact/tool order codes and qualification evidence were not frozen because CSR-01A-R2 stopped on electrical-network conflicts.</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr" s="0">
@@ -68144,22 +68144,22 @@
       </c>
       <c r="AI300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AJ300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>QER-01; ECO-006; MIR-01 where applicable; CSR-01A-R2 disposition</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AL300" t="inlineStr" s="0">
         <is>
-          <t>Outside current package; do not source or assign a footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” MIR-01 released the physical interface, but housing/header/contact/tool order codes and qualification evidence were not frozen because CSR-01A-R2 stopped on electrical-network conflicts.</t>
         </is>
       </c>
       <c r="AM300" t="inlineStr" s="0">
@@ -68184,7 +68184,7 @@
       </c>
       <c r="AQ300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="AR300" t="inlineStr" s="0">
@@ -68194,14 +68194,14 @@
       </c>
       <c r="AS300" t="inlineStr" s="0">
         <is>
-          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+          <t>CSR-01A-R2 disposition: BLOCKED. ANALYSIS INCOMPLETE â€” MIR-01 released the physical interface, but housing/header/contact/tool order codes and qualification evidence were not frozen because CSR-01A-R2 stopped on electrical-network conflicts.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J3</t>
+          <t>09_Connectors_Test/J10</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="0">
@@ -68211,7 +68211,7 @@
       </c>
       <c r="C301" t="inlineStr" s="0">
         <is>
-          <t>J3</t>
+          <t>J10</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="0">
@@ -68226,12 +68226,12 @@
       </c>
       <c r="F301" t="inlineStr" s="0">
         <is>
-          <t>M1/H03 Axis 2 logic</t>
+          <t>D1/H10 ICD-001 optional DNP; no live mate</t>
         </is>
       </c>
       <c r="G301" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN6</t>
+          <t>IPC100:CONN4</t>
         </is>
       </c>
       <c r="H301" t="inlineStr" s="0">
@@ -68251,12 +68251,12 @@
       </c>
       <c r="K301" t="inlineStr" s="0">
         <is>
-          <t>M1/H03 Axis 2 logic</t>
+          <t>D1/H10 ICD-001 optional DNP; no live mate</t>
         </is>
       </c>
       <c r="L301" t="inlineStr" s="0">
         <is>
-          <t>M1/H03 Axis 2 logic</t>
+          <t>D1/H10 ICD-001 optional DNP; no live mate</t>
         </is>
       </c>
       <c r="M301" t="inlineStr" s="0">
@@ -68428,7 +68428,7 @@
     <row r="302">
       <c r="A302" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J4</t>
+          <t>09_Connectors_Test/J13</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="0">
@@ -68438,7 +68438,7 @@
       </c>
       <c r="C302" t="inlineStr" s="0">
         <is>
-          <t>J4</t>
+          <t>J13</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="0">
@@ -68453,12 +68453,12 @@
       </c>
       <c r="F302" t="inlineStr" s="0">
         <is>
-          <t>S1/H04 LEFT-RIGHT limits</t>
+          <t>U1/H13 USB2 device-UFP; full 24 contacts + shell</t>
         </is>
       </c>
       <c r="G302" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN4</t>
+          <t>IPC100:USB_C_UFP_FULL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr" s="0">
@@ -68478,12 +68478,12 @@
       </c>
       <c r="K302" t="inlineStr" s="0">
         <is>
-          <t>S1/H04 LEFT-RIGHT limits</t>
+          <t>U1/H13 USB2 device-UFP; full 24 contacts + shell</t>
         </is>
       </c>
       <c r="L302" t="inlineStr" s="0">
         <is>
-          <t>S1/H04 LEFT-RIGHT limits</t>
+          <t>U1/H13 USB2 device-UFP; full 24 contacts + shell</t>
         </is>
       </c>
       <c r="M302" t="inlineStr" s="0">
@@ -68655,7 +68655,7 @@
     <row r="303">
       <c r="A303" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J5</t>
+          <t>09_Connectors_Test/J2</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="0">
@@ -68665,7 +68665,7 @@
       </c>
       <c r="C303" t="inlineStr" s="0">
         <is>
-          <t>J5</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="0">
@@ -68680,12 +68680,12 @@
       </c>
       <c r="F303" t="inlineStr" s="0">
         <is>
-          <t>S1/H05 UP-DOWN limits</t>
+          <t>M1/H02 Axis 1 logic</t>
         </is>
       </c>
       <c r="G303" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN4</t>
+          <t>IPC100:CONN6</t>
         </is>
       </c>
       <c r="H303" t="inlineStr" s="0">
@@ -68705,12 +68705,12 @@
       </c>
       <c r="K303" t="inlineStr" s="0">
         <is>
-          <t>S1/H05 UP-DOWN limits</t>
+          <t>M1/H02 Axis 1 logic</t>
         </is>
       </c>
       <c r="L303" t="inlineStr" s="0">
         <is>
-          <t>S1/H05 UP-DOWN limits</t>
+          <t>M1/H02 Axis 1 logic</t>
         </is>
       </c>
       <c r="M303" t="inlineStr" s="0">
@@ -68882,7 +68882,7 @@
     <row r="304">
       <c r="A304" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J6</t>
+          <t>09_Connectors_Test/J3</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="0">
@@ -68892,7 +68892,7 @@
       </c>
       <c r="C304" t="inlineStr" s="0">
         <is>
-          <t>J6</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="0">
@@ -68907,12 +68907,12 @@
       </c>
       <c r="F304" t="inlineStr" s="0">
         <is>
-          <t>D1/H06 OLED; 0.20m; no live mate</t>
+          <t>M1/H03 Axis 2 logic</t>
         </is>
       </c>
       <c r="G304" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN5</t>
+          <t>IPC100:CONN6</t>
         </is>
       </c>
       <c r="H304" t="inlineStr" s="0">
@@ -68932,12 +68932,12 @@
       </c>
       <c r="K304" t="inlineStr" s="0">
         <is>
-          <t>D1/H06 OLED; 0.20m; no live mate</t>
+          <t>M1/H03 Axis 2 logic</t>
         </is>
       </c>
       <c r="L304" t="inlineStr" s="0">
         <is>
-          <t>D1/H06 OLED; 0.20m; no live mate</t>
+          <t>M1/H03 Axis 2 logic</t>
         </is>
       </c>
       <c r="M304" t="inlineStr" s="0">
@@ -69109,7 +69109,7 @@
     <row r="305">
       <c r="A305" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J7</t>
+          <t>09_Connectors_Test/J4</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="0">
@@ -69119,7 +69119,7 @@
       </c>
       <c r="C305" t="inlineStr" s="0">
         <is>
-          <t>J7</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="0">
@@ -69134,7 +69134,7 @@
       </c>
       <c r="F305" t="inlineStr" s="0">
         <is>
-          <t>D1/H07 BME280; 0.20m; no live mate</t>
+          <t>S1/H04 LEFT-RIGHT limits</t>
         </is>
       </c>
       <c r="G305" t="inlineStr" s="0">
@@ -69159,12 +69159,12 @@
       </c>
       <c r="K305" t="inlineStr" s="0">
         <is>
-          <t>D1/H07 BME280; 0.20m; no live mate</t>
+          <t>S1/H04 LEFT-RIGHT limits</t>
         </is>
       </c>
       <c r="L305" t="inlineStr" s="0">
         <is>
-          <t>D1/H07 BME280; 0.20m; no live mate</t>
+          <t>S1/H04 LEFT-RIGHT limits</t>
         </is>
       </c>
       <c r="M305" t="inlineStr" s="0">
@@ -69336,7 +69336,7 @@
     <row r="306">
       <c r="A306" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J8A</t>
+          <t>09_Connectors_Test/J5</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="0">
@@ -69346,7 +69346,7 @@
       </c>
       <c r="C306" t="inlineStr" s="0">
         <is>
-          <t>J8A</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="0">
@@ -69361,12 +69361,12 @@
       </c>
       <c r="F306" t="inlineStr" s="0">
         <is>
-          <t>S1/H08A dedicated STOP; unique key</t>
+          <t>S1/H05 UP-DOWN limits</t>
         </is>
       </c>
       <c r="G306" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN2</t>
+          <t>IPC100:CONN4</t>
         </is>
       </c>
       <c r="H306" t="inlineStr" s="0">
@@ -69386,12 +69386,12 @@
       </c>
       <c r="K306" t="inlineStr" s="0">
         <is>
-          <t>S1/H08A dedicated STOP; unique key</t>
+          <t>S1/H05 UP-DOWN limits</t>
         </is>
       </c>
       <c r="L306" t="inlineStr" s="0">
         <is>
-          <t>S1/H08A dedicated STOP; unique key</t>
+          <t>S1/H05 UP-DOWN limits</t>
         </is>
       </c>
       <c r="M306" t="inlineStr" s="0">
@@ -69563,7 +69563,7 @@
     <row r="307">
       <c r="A307" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J8B</t>
+          <t>09_Connectors_Test/J6</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="0">
@@ -69573,7 +69573,7 @@
       </c>
       <c r="C307" t="inlineStr" s="0">
         <is>
-          <t>J8B</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="0">
@@ -69588,12 +69588,12 @@
       </c>
       <c r="F307" t="inlineStr" s="0">
         <is>
-          <t>L1/H08B ordinary UI; incompatible with J8A</t>
+          <t>D1/H06 OLED; 0.20m; no live mate</t>
         </is>
       </c>
       <c r="G307" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN12</t>
+          <t>IPC100:CONN5</t>
         </is>
       </c>
       <c r="H307" t="inlineStr" s="0">
@@ -69613,12 +69613,12 @@
       </c>
       <c r="K307" t="inlineStr" s="0">
         <is>
-          <t>L1/H08B ordinary UI; incompatible with J8A</t>
+          <t>D1/H06 OLED; 0.20m; no live mate</t>
         </is>
       </c>
       <c r="L307" t="inlineStr" s="0">
         <is>
-          <t>L1/H08B ordinary UI; incompatible with J8A</t>
+          <t>D1/H06 OLED; 0.20m; no live mate</t>
         </is>
       </c>
       <c r="M307" t="inlineStr" s="0">
@@ -69790,7 +69790,7 @@
     <row r="308">
       <c r="A308" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/J9</t>
+          <t>09_Connectors_Test/J7</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="0">
@@ -69800,7 +69800,7 @@
       </c>
       <c r="C308" t="inlineStr" s="0">
         <is>
-          <t>J9</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="0">
@@ -69815,12 +69815,12 @@
       </c>
       <c r="F308" t="inlineStr" s="0">
         <is>
-          <t>R1/H09 SELV dry contact; 0-30VDC 1A</t>
+          <t>D1/H07 BME280; 0.20m; no live mate</t>
         </is>
       </c>
       <c r="G308" t="inlineStr" s="0">
         <is>
-          <t>IPC100:CONN3</t>
+          <t>IPC100:CONN4</t>
         </is>
       </c>
       <c r="H308" t="inlineStr" s="0">
@@ -69840,12 +69840,12 @@
       </c>
       <c r="K308" t="inlineStr" s="0">
         <is>
-          <t>R1/H09 SELV dry contact; 0-30VDC 1A</t>
+          <t>D1/H07 BME280; 0.20m; no live mate</t>
         </is>
       </c>
       <c r="L308" t="inlineStr" s="0">
         <is>
-          <t>R1/H09 SELV dry contact; 0-30VDC 1A</t>
+          <t>D1/H07 BME280; 0.20m; no live mate</t>
         </is>
       </c>
       <c r="M308" t="inlineStr" s="0">
@@ -70017,7 +70017,7 @@
     <row r="309">
       <c r="A309" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/R901</t>
+          <t>09_Connectors_Test/J8A</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="0">
@@ -70027,12 +70027,12 @@
       </c>
       <c r="C309" t="inlineStr" s="0">
         <is>
-          <t>R901</t>
+          <t>J8A</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="0">
         <is>
-          <t>Passives</t>
+          <t>Connectors</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="0">
@@ -70042,12 +70042,12 @@
       </c>
       <c r="F309" t="inlineStr" s="0">
         <is>
-          <t>5.1 kΩ ±1% CC1 Rd</t>
+          <t>S1/H08A dedicated STOP; unique key</t>
         </is>
       </c>
       <c r="G309" t="inlineStr" s="0">
         <is>
-          <t>IPC100:R</t>
+          <t>IPC100:CONN2</t>
         </is>
       </c>
       <c r="H309" t="inlineStr" s="0">
@@ -70067,12 +70067,12 @@
       </c>
       <c r="K309" t="inlineStr" s="0">
         <is>
-          <t>5.1 kΩ ±1% CC1 Rd</t>
+          <t>S1/H08A dedicated STOP; unique key</t>
         </is>
       </c>
       <c r="L309" t="inlineStr" s="0">
         <is>
-          <t>5.1 kΩ ±1% CC1 Rd</t>
+          <t>S1/H08A dedicated STOP; unique key</t>
         </is>
       </c>
       <c r="M309" t="inlineStr" s="0">
@@ -70152,7 +70152,7 @@
       </c>
       <c r="AB309" t="inlineStr" s="0">
         <is>
-          <t>Normal</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr" s="0">
@@ -70244,7 +70244,7 @@
     <row r="310">
       <c r="A310" t="inlineStr" s="0">
         <is>
-          <t>09_Connectors_Test/R902</t>
+          <t>09_Connectors_Test/J8B</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="0">
@@ -70254,12 +70254,12 @@
       </c>
       <c r="C310" t="inlineStr" s="0">
         <is>
-          <t>R902</t>
+          <t>J8B</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="0">
         <is>
-          <t>Passives</t>
+          <t>Connectors</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="0">
@@ -70269,12 +70269,12 @@
       </c>
       <c r="F310" t="inlineStr" s="0">
         <is>
-          <t>5.1 kΩ ±1% CC2 Rd</t>
+          <t>L1/H08B ordinary UI; incompatible with J8A</t>
         </is>
       </c>
       <c r="G310" t="inlineStr" s="0">
         <is>
-          <t>IPC100:R</t>
+          <t>IPC100:CONN12</t>
         </is>
       </c>
       <c r="H310" t="inlineStr" s="0">
@@ -70294,12 +70294,12 @@
       </c>
       <c r="K310" t="inlineStr" s="0">
         <is>
-          <t>5.1 kΩ ±1% CC2 Rd</t>
+          <t>L1/H08B ordinary UI; incompatible with J8A</t>
         </is>
       </c>
       <c r="L310" t="inlineStr" s="0">
         <is>
-          <t>5.1 kΩ ±1% CC2 Rd</t>
+          <t>L1/H08B ordinary UI; incompatible with J8A</t>
         </is>
       </c>
       <c r="M310" t="inlineStr" s="0">
@@ -70379,7 +70379,7 @@
       </c>
       <c r="AB310" t="inlineStr" s="0">
         <is>
-          <t>Normal</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr" s="0">
@@ -70471,231 +70471,912 @@
     <row r="311">
       <c r="A311" t="inlineStr" s="0">
         <is>
+          <t>09_Connectors_Test/J9</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="0">
+        <is>
+          <t>09_Connectors_Test</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="0">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="0">
+        <is>
+          <t>Connectors</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="0">
+        <is>
+          <t>OUTSIDE CSR-01A</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="0">
+        <is>
+          <t>R1/H09 SELV dry contact; 0-30VDC 1A</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr" s="0">
+        <is>
+          <t>IPC100:CONN3</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr" s="0">
+        <is>
+          <t>R1/H09 SELV dry contact; 0-30VDC 1A</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr" s="0">
+        <is>
+          <t>R1/H09 SELV dry contact; 0-30VDC 1A</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr" s="0">
+        <is>
+          <t>Requires exact-part review</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr" s="0">
+        <is>
+          <t>Requires exact-part review</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr" s="0">
+        <is>
+          <t>As captured where stated; package/derating unresolved</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr" s="0">
+        <is>
+          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+        </is>
+      </c>
+      <c r="AB311" t="inlineStr" s="0">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AL311" t="inlineStr" s="0">
+        <is>
+          <t>Outside current package; do not source or assign a footprint.</t>
+        </is>
+      </c>
+      <c r="AM311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO311" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP311" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AR311" t="inlineStr" s="0">
+        <is>
+          <t>Rev A</t>
+        </is>
+      </c>
+      <c r="AS311" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr" s="0">
+        <is>
+          <t>09_Connectors_Test/R901</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="0">
+        <is>
+          <t>09_Connectors_Test</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="0">
+        <is>
+          <t>R901</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="0">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="0">
+        <is>
+          <t>OUTSIDE CSR-01A</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="0">
+        <is>
+          <t>5.1 kΩ ±1% CC1 Rd</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr" s="0">
+        <is>
+          <t>IPC100:R</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr" s="0">
+        <is>
+          <t>5.1 kΩ ±1% CC1 Rd</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr" s="0">
+        <is>
+          <t>5.1 kΩ ±1% CC1 Rd</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr" s="0">
+        <is>
+          <t>Requires exact-part review</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr" s="0">
+        <is>
+          <t>Requires exact-part review</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr" s="0">
+        <is>
+          <t>As captured where stated; package/derating unresolved</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr" s="0">
+        <is>
+          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+        </is>
+      </c>
+      <c r="AB312" t="inlineStr" s="0">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AJ312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AK312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AL312" t="inlineStr" s="0">
+        <is>
+          <t>Outside current package; do not source or assign a footprint.</t>
+        </is>
+      </c>
+      <c r="AM312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO312" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP312" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AR312" t="inlineStr" s="0">
+        <is>
+          <t>Rev A</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr" s="0">
+        <is>
+          <t>09_Connectors_Test/R902</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="0">
+        <is>
+          <t>09_Connectors_Test</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="0">
+        <is>
+          <t>R902</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="0">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="0">
+        <is>
+          <t>OUTSIDE CSR-01A</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="0">
+        <is>
+          <t>5.1 kΩ ±1% CC2 Rd</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr" s="0">
+        <is>
+          <t>IPC100:R</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr" s="0">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr" s="0">
+        <is>
+          <t>5.1 kΩ ±1% CC2 Rd</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr" s="0">
+        <is>
+          <t>5.1 kΩ ±1% CC2 Rd</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr" s="0">
+        <is>
+          <t>Requires exact-part review</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr" s="0">
+        <is>
+          <t>Requires exact-part review</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr" s="0">
+        <is>
+          <t>As captured where stated; package/derating unresolved</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr" s="0">
+        <is>
+          <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr" s="0">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AJ313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AK313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AL313" t="inlineStr" s="0">
+        <is>
+          <t>Outside current package; do not source or assign a footprint.</t>
+        </is>
+      </c>
+      <c r="AM313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO313" t="inlineStr" s="0">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AR313" t="inlineStr" s="0">
+        <is>
+          <t>Rev A</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr" s="0">
+        <is>
           <t>09_Connectors_Test/R903</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr" s="0">
+      <c r="B314" t="inlineStr" s="0">
         <is>
           <t>09_Connectors_Test</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr" s="0">
+      <c r="C314" t="inlineStr" s="0">
         <is>
           <t>R903</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr" s="0">
+      <c r="D314" t="inlineStr" s="0">
         <is>
           <t>Passives</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr" s="0">
+      <c r="E314" t="inlineStr" s="0">
         <is>
           <t>OUTSIDE CSR-01A</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr" s="0">
+      <c r="F314" t="inlineStr" s="0">
         <is>
           <t>DNP 1 MOhm shield bleed option</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr" s="0">
+      <c r="G314" t="inlineStr" s="0">
         <is>
           <t>IPC100:R</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr" s="0">
+      <c r="H314" t="inlineStr" s="0">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr" s="0">
+      <c r="I314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr" s="0">
         <is>
           <t>DNP 1 MOhm shield bleed option</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr" s="0">
+      <c r="L314" t="inlineStr" s="0">
         <is>
           <t>DNP 1 MOhm shield bleed option</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="N311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="O311" t="inlineStr" s="0">
+      <c r="M314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr" s="0">
         <is>
           <t>Requires exact-part review</t>
         </is>
       </c>
-      <c r="P311" t="inlineStr" s="0">
+      <c r="P314" t="inlineStr" s="0">
         <is>
           <t>Requires exact-part review</t>
         </is>
       </c>
-      <c r="Q311" t="inlineStr" s="0">
+      <c r="Q314" t="inlineStr" s="0">
         <is>
           <t>As captured where stated; package/derating unresolved</t>
         </is>
       </c>
-      <c r="R311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="S311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="T311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="V311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="W311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="X311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="Y311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="Z311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="AA311" t="inlineStr" s="0">
+      <c r="R314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr" s="0">
         <is>
           <t>Outside CSR-01A-R; explicitly not yet frozen.</t>
         </is>
       </c>
-      <c r="AB311" t="inlineStr" s="0">
+      <c r="AB314" t="inlineStr" s="0">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="AC311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="AJ311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="AK311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="AL311" t="inlineStr" s="0">
+      <c r="AC314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AK314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AL314" t="inlineStr" s="0">
         <is>
           <t>Outside current package; do not source or assign a footprint.</t>
         </is>
       </c>
-      <c r="AM311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AN311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AO311" t="inlineStr" s="0">
+      <c r="AM314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr" s="0">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AP311" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AQ311" t="inlineStr" s="0">
-        <is>
-          <t>NOT YET FROZEN</t>
-        </is>
-      </c>
-      <c r="AR311" t="inlineStr" s="0">
+      <c r="AP314" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr" s="0">
+        <is>
+          <t>NOT YET FROZEN</t>
+        </is>
+      </c>
+      <c r="AR314" t="inlineStr" s="0">
         <is>
           <t>Rev A</t>
         </is>
       </c>
-      <c r="AS311" t="inlineStr" s="0">
+      <c r="AS314" t="inlineStr" s="0">
         <is>
           <t>NOT YET FROZEN; excluded from CSR-01A-R2.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS311"/>
+  <autoFilter ref="A1:AS314"/>
 </worksheet>
 </file>
--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -3908,17 +3908,17 @@
       </c>
       <c r="AJ17" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr" s="0">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AS17" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -7994,17 +7994,17 @@
       </c>
       <c r="AJ35" t="inlineStr" s="0">
         <is>
-          <t>ECO-010; PACS-01R</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr" s="0">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="AS35" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -8221,17 +8221,17 @@
       </c>
       <c r="AJ36" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr" s="0">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="AS36" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -22976,17 +22976,17 @@
       </c>
       <c r="AJ101" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr" s="0">
@@ -23021,7 +23021,7 @@
       </c>
       <c r="AS101" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -23203,17 +23203,17 @@
       </c>
       <c r="AJ102" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr" s="0">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="AS102" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -23430,17 +23430,17 @@
       </c>
       <c r="AJ103" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr" s="0">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="AS103" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -23657,17 +23657,17 @@
       </c>
       <c r="AJ104" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr" s="0">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AS104" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -23884,17 +23884,17 @@
       </c>
       <c r="AJ105" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr" s="0">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="AS105" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -24111,17 +24111,17 @@
       </c>
       <c r="AJ106" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr" s="0">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="AS106" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -24338,17 +24338,17 @@
       </c>
       <c r="AJ107" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr" s="0">
@@ -24383,7 +24383,7 @@
       </c>
       <c r="AS107" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -24565,17 +24565,17 @@
       </c>
       <c r="AJ108" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr" s="0">
@@ -24610,7 +24610,7 @@
       </c>
       <c r="AS108" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -24792,17 +24792,17 @@
       </c>
       <c r="AJ109" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr" s="0">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="AS109" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -25019,17 +25019,17 @@
       </c>
       <c r="AJ110" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr" s="0">
@@ -25064,7 +25064,7 @@
       </c>
       <c r="AS110" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -25246,17 +25246,17 @@
       </c>
       <c r="AJ111" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr" s="0">
@@ -25291,7 +25291,7 @@
       </c>
       <c r="AS111" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -25473,17 +25473,17 @@
       </c>
       <c r="AJ112" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr" s="0">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="AS112" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -25700,17 +25700,17 @@
       </c>
       <c r="AJ113" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr" s="0">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AS113" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -29105,17 +29105,17 @@
       </c>
       <c r="AJ128" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr" s="0">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AS128" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -60885,17 +60885,17 @@
       </c>
       <c r="AJ268" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL268" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM268" t="inlineStr" s="0">
@@ -60930,7 +60930,7 @@
       </c>
       <c r="AS268" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -61112,17 +61112,17 @@
       </c>
       <c r="AJ269" t="inlineStr" s="0">
         <is>
-          <t>PACS-01; QER-01/02/03; PPQ-01/02; applicable ECO</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL269" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM269" t="inlineStr" s="0">
@@ -61157,7 +61157,7 @@
       </c>
       <c r="AS269" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>
@@ -66787,17 +66787,17 @@
       </c>
       <c r="AJ294" t="inlineStr" s="0">
         <is>
-          <t>ECO-010; PACS-01R</t>
+          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R SYSTEM REVALIDATION</t>
+          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
         </is>
       </c>
       <c r="AL294" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
       <c r="AM294" t="inlineStr" s="0">
@@ -66832,7 +66832,7 @@
       </c>
       <c r="AS294" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
         </is>
       </c>
     </row>

--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="AL3" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr" s="0">
@@ -775,7 +775,7 @@
       </c>
       <c r="AS3" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="AL4" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr" s="0">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AS4" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AL5" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr" s="0">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AS5" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Ripple/ESR/lifetime at protected-input waveform.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AL10" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr" s="0">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AS10" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Exact DC-bias curve at 55 V after U101/PPC clamp selection.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AL16" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Impedance/inductance, hot DCR, saturation and loss at protected-input waveform.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr" s="0">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AS16" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Impedance/inductance, hot DCR, saturation and loss at protected-input waveform.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AL37" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 WEBENCH input-capacitance and ripple solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr" s="0">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="AS37" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 WEBENCH input-capacitance and ripple solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8685,7 @@
       </c>
       <c r="AL38" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: TI requires 100 nF BOOT-to-SW; exact suffix and dielectric check.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr" s="0">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AS38" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: TI requires 100 nF BOOT-to-SW; exact suffix and dielectric check.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AL39" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr" s="0">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="AS39" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AL40" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr" s="0">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="AS40" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 integrated-compensation output-capacitance/ESR solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AL41" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Pin/function reconciliation: selected U201 has internal 4 ms soft start.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr" s="0">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="AS41" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: Pin/function reconciliation: selected U201 has internal 4 ms soft start.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="AL42" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U202 switchover plus U203 input transient model and exact DC-bias curve.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr" s="0">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="AS42" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U202 switchover plus U203 input transient model and exact DC-bias curve.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="AL44" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr" s="0">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="AS44" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="AL45" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr" s="0">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="AS45" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 LC stability and effective-capacitance solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="AL46" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact soft-start equation and tolerance.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr" s="0">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AS46" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact soft-start equation and tolerance.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="AL68" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 ripple/current/loss solution at selected PFM/FPWM suffix.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr" s="0">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AS68" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U201 ripple/current/loss solution at selected PFM/FPWM suffix.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="AL69" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact switching mode, ripple, saturation and loss solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr" s="0">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="AS69" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. PACS-01 â€” freeze named active, then execute official tool/curve check; required evidence: U203 exact switching mode, ripple, saturation and loss solution.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -62257,7 +62257,7 @@
       </c>
       <c r="AL274" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM274" t="inlineStr" s="0">
@@ -62292,7 +62292,7 @@
       </c>
       <c r="AS274" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -64754,7 +64754,7 @@
       </c>
       <c r="AL285" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM285" t="inlineStr" s="0">
@@ -64789,7 +64789,7 @@
       </c>
       <c r="AS285" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -64981,7 +64981,7 @@
       </c>
       <c r="AL286" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM286" t="inlineStr" s="0">
@@ -65016,7 +65016,7 @@
       </c>
       <c r="AS286" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>
@@ -65208,7 +65208,7 @@
       </c>
       <c r="AL287" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
       <c r="AM287" t="inlineStr" s="0">
@@ -65243,7 +65243,7 @@
       </c>
       <c r="AS287" t="inlineStr" s="0">
         <is>
-          <t>PAS-01R: BLOCKED â€” ACTIVE DEVICE SELECTION REQUIRED. ECO-010 support element requires exact passive selection after PACS-01R.</t>
+          <t>PAS-01R: BLOCKED - exact active MPN selected; named manufacturer tool/curve, thermal, magnetic or threshold evidence remains under PACS-01R-A.</t>
         </is>
       </c>
     </row>

--- a/docs/bom/IPC100_RevA_EBOM.xlsx
+++ b/docs/bom/IPC100_RevA_EBOM.xlsx
@@ -87,7 +87,7 @@
     <col min="34" max="34" width="35" customWidth="1"/>
     <col min="35" max="35" width="16" customWidth="1"/>
     <col min="36" max="36" width="48" customWidth="1"/>
-    <col min="37" max="37" width="40" customWidth="1"/>
+    <col min="37" max="37" width="41" customWidth="1"/>
     <col min="38" max="38" width="48" customWidth="1"/>
     <col min="39" max="39" width="48" customWidth="1"/>
     <col min="40" max="40" width="34" customWidth="1"/>
@@ -3908,17 +3908,17 @@
       </c>
       <c r="AJ17" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr" s="0">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AS17" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 corrected the electrical class; exact manufacturer curve, tolerance, thermal/SOA, lifecycle, sourcing, and cost evidence remain pending after CSR-01A-R2 stopped on released-network conflicts. PACS-01 reviewed candidate IAUC100N08S5N034ATMA1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -7994,17 +7994,17 @@
       </c>
       <c r="AJ35" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr" s="0">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="AS35" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS26631PWPR; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -8221,17 +8221,17 @@
       </c>
       <c r="AJ36" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr" s="0">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="AS36" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS259470LRPWR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -22976,17 +22976,17 @@
       </c>
       <c r="AJ101" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr" s="0">
@@ -23021,7 +23021,7 @@
       </c>
       <c r="AS101" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-007 corrected the 400 kHz LMR38020F-Q1 RT/SYNC network to 64.9 kOhm; exact suffix, oscillator, loop, loss, thermal, lifecycle, sourcing, and cost evidence remain CSR-01A-R3 work. PACS-01 reviewed candidate LMR38020FSQDDARQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -23203,17 +23203,17 @@
       </c>
       <c r="AJ102" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr" s="0">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="AS102" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS2121RUXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -23430,17 +23430,17 @@
       </c>
       <c r="AJ103" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr" s="0">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="AS103" t="inlineStr" s="0">
         <is>
-          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>THERMAL/STABILITY EVIDENCE MISSING â€” vendor-tool, effective-capacitance, loop/stability, loss, and minimum-copper analysis are incomplete. PACS-01 reviewed candidate TPS62135RGXR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -23657,17 +23657,17 @@
       </c>
       <c r="AJ104" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr" s="0">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="AS104" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC1G08QDCKRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -23884,17 +23884,17 @@
       </c>
       <c r="AJ105" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr" s="0">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="AS105" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate SN74LVC08AQPWRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -24111,17 +24111,17 @@
       </c>
       <c r="AJ106" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr" s="0">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="AS106" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -24338,17 +24338,17 @@
       </c>
       <c r="AJ107" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr" s="0">
@@ -24383,7 +24383,7 @@
       </c>
       <c r="AS107" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -24565,17 +24565,17 @@
       </c>
       <c r="AJ108" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr" s="0">
@@ -24610,7 +24610,7 @@
       </c>
       <c r="AS108" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -24792,17 +24792,17 @@
       </c>
       <c r="AJ109" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr" s="0">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="AS109" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -25019,17 +25019,17 @@
       </c>
       <c r="AJ110" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr" s="0">
@@ -25064,7 +25064,7 @@
       </c>
       <c r="AS110" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -25246,17 +25246,17 @@
       </c>
       <c r="AJ111" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr" s="0">
@@ -25291,7 +25291,7 @@
       </c>
       <c r="AS111" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS22918TDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -25473,17 +25473,17 @@
       </c>
       <c r="AJ112" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr" s="0">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="AS112" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -25700,17 +25700,17 @@
       </c>
       <c r="AJ113" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr" s="0">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AS113" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - ECO-008R implements a generic 141 kOhm +/-1%, &lt;=100 ppm/degC RILIM with calculated 162.8..222.4 mA bounds under QER-02; exact MPN/suffix/package, thermal, reverse-current, lifecycle, sourcing, cost, and prototype evidence remain CSR-01A-R4 work. PACS-01 reviewed candidate TPS2553QDBVRQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -29105,17 +29105,17 @@
       </c>
       <c r="AJ128" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr" s="0">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AS128" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” exact suffix equations, pin mapping, thresholds, timing, partial-power, thermal, and fault behavior are not all closed. PACS-01 reviewed candidate TPS389030QDSERQ1; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -60885,17 +60885,17 @@
       </c>
       <c r="AJ268" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL268" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM268" t="inlineStr" s="0">
@@ -60930,7 +60930,7 @@
       </c>
       <c r="AS268" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -61112,17 +61112,17 @@
       </c>
       <c r="AJ269" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL269" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM269" t="inlineStr" s="0">
@@ -61157,7 +61157,7 @@
       </c>
       <c r="AS269" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE â€” ECO-006 physical class is defined and TCA9517A is a candidate; exact pin equivalence, offset-low compatibility, partial-power behavior, lifecycle, sourcing, and cost evidence remain pending. PACS-01 reviewed candidate TCA9517ADGKR; package rejected as a whole because U101 and U801 remain blocked. Do not procure or assign footprint. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
@@ -66787,17 +66787,17 @@
       </c>
       <c r="AJ294" t="inlineStr" s="0">
         <is>
-          <t>PACS-01R; PACS-01R-A; PPQ-02; applicable QER/ECO</t>
+          <t>PACS-01R-B1R-X; External_Evidence_Acquisition_Inventory</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr" s="0">
         <is>
-          <t>BLOCKED - PACS-01R-A EVIDENCE CLOSURE</t>
+          <t>BLOCKED - EXTERNAL EVIDENCE ACQUISITION</t>
         </is>
       </c>
       <c r="AL294" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
       <c r="AM294" t="inlineStr" s="0">
@@ -66832,7 +66832,7 @@
       </c>
       <c r="AS294" t="inlineStr" s="0">
         <is>
-          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required.</t>
+          <t>ANALYSIS INCOMPLETE - exact suffix/system revalidation remains required. ECO-010 selectable implementation TPS3899DL01DSER; BLOCKED - PACS-01R SYSTEM REVALIDATION; no footprint or procurement release. PACS-01R: BLOCKED - exact active candidate retained; thermal/tool, dependent-passive, prototype, alternate, and current commercial evidence closure required. PACS-01R-B1R-X: external tool, authoritative thermal and authenticated commercial artifacts remain open; see docs/evidence/External_Evidence_Acquisition_Inventory.csv.</t>
         </is>
       </c>
     </row>
